--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A79CB1-3D21-464F-8774-2FD73A7552B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A9DB9E-09D1-402E-A15A-F02531D7C5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$S$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$S$121</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="430">
   <si>
     <t>Nr</t>
   </si>
@@ -1320,6 +1320,12 @@
   </si>
   <si>
     <t>https://theeffectivestatistician.com/clarifying-confusions-around-interim-primary-final-and-other-analyses-in-clinical-trial/</t>
+  </si>
+  <si>
+    <t>Exhausting the type I error level in event-driven group-sequential designs with a closed testing procedure for progression-free and overall survival</t>
+  </si>
+  <si>
+    <t>Danzer, M.F., **Rufibach, K.**, Beyersmann, J., Schmidt, R.</t>
   </si>
 </sst>
 </file>
@@ -1771,7 +1777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T120"/>
+  <dimension ref="A1:T121"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -1859,21 +1865,21 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>370</v>
       </c>
       <c r="B2" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>420</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -1883,21 +1889,21 @@
       </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>370</v>
       </c>
       <c r="B3" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>420</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>149</v>
@@ -1905,403 +1911,374 @@
       <c r="G3" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="T3" s="2"/>
+    </row>
+    <row r="4" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B4" s="2">
+        <v>47</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>413</v>
-      </c>
-      <c r="T3" s="2"/>
-    </row>
-    <row r="4" spans="1:20" ht="40" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="2">
-        <v>46</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2025</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="H4" s="2">
-        <v>47</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="Q4" t="s">
         <v>413</v>
       </c>
-      <c r="R4" s="5" t="s">
-        <v>427</v>
-      </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="40" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B5" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>420</v>
+        <v>407</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2025</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>392</v>
+        <v>424</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>385</v>
+        <v>150</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
+      </c>
+      <c r="H5" s="2">
+        <v>47</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>426</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>398</v>
+        <v>408</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>413</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>427</v>
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B6" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>420</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>385</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>415</v>
+        <v>234</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B7" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>169</v>
+        <v>395</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>420</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>147</v>
+        <v>394</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>385</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>234</v>
+        <v>415</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B8" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2025</v>
+        <v>169</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>420</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>373</v>
+        <v>147</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>150</v>
+        <v>385</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H8" s="2">
-        <v>17</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>418</v>
+        <v>234</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="T8" s="2"/>
-    </row>
-    <row r="9" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B9" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="D9" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="H9" s="2">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>293</v>
+        <v>386</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>381</v>
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B10" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>176</v>
+        <v>383</v>
       </c>
       <c r="D10" s="2">
         <v>2024</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>146</v>
+        <v>382</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>380</v>
+        <v>238</v>
       </c>
       <c r="H10" s="2">
-        <v>15</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1223858</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>379</v>
+        <v>25</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>387</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="T10" s="2"/>
+    </row>
+    <row r="11" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B11" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D11" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>154</v>
+        <v>380</v>
       </c>
       <c r="H11" s="2">
-        <v>22</v>
-      </c>
-      <c r="I11" s="2">
-        <v>4</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>174</v>
+        <v>15</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1223858</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B12" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="D12" s="2">
         <v>2023</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H12" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I12" s="2">
         <v>4</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>290</v>
+        <v>160</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>291</v>
+        <v>181</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B13" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="D13" s="2">
         <v>2023</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>150</v>
@@ -2313,30 +2290,48 @@
         <v>15</v>
       </c>
       <c r="I13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B14" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="D14" s="2">
         <v>2023</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>150</v>
@@ -2348,118 +2343,121 @@
         <v>15</v>
       </c>
       <c r="I14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>159</v>
+        <v>371</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B15" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="D15" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="H15" s="2">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="I15" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B16" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D16" s="2">
         <v>2022</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="H16" s="2">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="I16" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B17" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D17" s="2">
         <v>2022</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H17" s="2">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="I17" s="2">
+        <v>5</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
@@ -2467,131 +2465,125 @@
         <v>175</v>
       </c>
       <c r="B18" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D18" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H18" s="2">
-        <v>22</v>
-      </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2">
-        <v>420</v>
+        <v>21</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>237</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B19" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D19" s="2">
         <v>2021</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H19" s="2">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="I19" s="2">
-        <v>4</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>243</v>
+        <v>1</v>
+      </c>
+      <c r="J19" s="2">
+        <v>420</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B20" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D20" s="2">
         <v>2021</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H20" s="2">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="I20" s="2">
+        <v>4</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2599,16 +2591,16 @@
         <v>175</v>
       </c>
       <c r="B21" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D21" s="2">
         <v>2021</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>150</v>
@@ -2620,92 +2612,98 @@
         <v>20</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B22" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D22" s="2">
         <v>2021</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="H22" s="2">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B23" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D23" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H23" s="2">
-        <v>4</v>
-      </c>
-      <c r="I23" s="2">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2713,116 +2711,110 @@
         <v>175</v>
       </c>
       <c r="B24" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="D24" s="2">
         <v>2020</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="H24" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I24" s="2">
-        <v>4</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>249</v>
+        <v>68</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B25" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="D25" s="2">
         <v>2020</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="H25" s="2">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="I25" s="2">
+        <v>4</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B26" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D26" s="2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="H26" s="2">
-        <v>62</v>
-      </c>
-      <c r="I26" s="2">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2830,34 +2822,37 @@
         <v>175</v>
       </c>
       <c r="B27" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D27" s="2">
         <v>2019</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="H27" s="2">
-        <v>38</v>
+        <v>62</v>
+      </c>
+      <c r="I27" s="2">
+        <v>3</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2865,34 +2860,34 @@
         <v>175</v>
       </c>
       <c r="B28" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D28" s="2">
         <v>2019</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H28" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2900,16 +2895,16 @@
         <v>175</v>
       </c>
       <c r="B29" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D29" s="2">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>150</v>
@@ -2918,19 +2913,16 @@
         <v>236</v>
       </c>
       <c r="H29" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2938,34 +2930,37 @@
         <v>175</v>
       </c>
       <c r="B30" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D30" s="2">
         <v>2016</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="H30" s="2">
-        <v>58</v>
-      </c>
-      <c r="I30" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2973,31 +2968,34 @@
         <v>175</v>
       </c>
       <c r="B31" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D31" s="2">
         <v>2016</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="H31" s="2">
-        <v>47</v>
+        <v>58</v>
+      </c>
+      <c r="I31" s="2">
+        <v>6</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -3005,37 +3003,31 @@
         <v>175</v>
       </c>
       <c r="B32" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D32" s="2">
         <v>2016</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H32" s="2">
-        <v>26</v>
-      </c>
-      <c r="I32" s="2">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3043,37 +3035,37 @@
         <v>175</v>
       </c>
       <c r="B33" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D33" s="2">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H33" s="2">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="I33" s="2">
+        <v>2</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3081,40 +3073,37 @@
         <v>175</v>
       </c>
       <c r="B34" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D34" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H34" s="2">
-        <v>75</v>
-      </c>
-      <c r="I34" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3122,41 +3111,40 @@
         <v>175</v>
       </c>
       <c r="B35" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D35" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H35" s="2">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="I35" s="2">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="str">
-        <f>"1-29"</f>
-        <v>1-29</v>
+        <v>4</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3164,40 +3152,41 @@
         <v>175</v>
       </c>
       <c r="B36" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>200</v>
       </c>
       <c r="D36" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="H36" s="2">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="I36" s="2">
-        <v>4</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>265</v>
+        <v>1</v>
+      </c>
+      <c r="J36" s="2" t="str">
+        <f>"1-29"</f>
+        <v>1-29</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3205,38 +3194,40 @@
         <v>175</v>
       </c>
       <c r="B37" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D37" s="2">
         <v>2011</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="H37" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="I37" s="2">
-        <v>6</v>
-      </c>
-      <c r="J37" s="2" t="str">
-        <f>"1-28"</f>
-        <v>1-28</v>
+        <v>4</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3244,34 +3235,38 @@
         <v>175</v>
       </c>
       <c r="B38" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D38" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H38" s="2">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="I38" s="2">
-        <v>4</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>268</v>
+        <v>6</v>
+      </c>
+      <c r="J38" s="2" t="str">
+        <f>"1-28"</f>
+        <v>1-28</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3279,40 +3274,34 @@
         <v>175</v>
       </c>
       <c r="B39" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D39" s="2">
         <v>2010</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H39" s="2">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I39" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3320,37 +3309,40 @@
         <v>175</v>
       </c>
       <c r="B40" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D40" s="2">
         <v>2010</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H40" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I40" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3358,37 +3350,37 @@
         <v>175</v>
       </c>
       <c r="B41" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D41" s="2">
         <v>2010</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H41" s="2">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3396,34 +3388,37 @@
         <v>175</v>
       </c>
       <c r="B42" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>200</v>
       </c>
       <c r="D42" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="H42" s="2">
-        <v>31</v>
-      </c>
-      <c r="I42" s="2">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>346</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3431,37 +3426,34 @@
         <v>175</v>
       </c>
       <c r="B43" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D43" s="2">
         <v>2009</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="H43" s="2">
-        <v>79</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>276</v>
+        <v>31</v>
+      </c>
+      <c r="I43" s="2">
+        <v>1</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3469,37 +3461,37 @@
         <v>175</v>
       </c>
       <c r="B44" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>289</v>
+        <v>212</v>
       </c>
       <c r="D44" s="2">
         <v>2009</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H44" s="2">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3507,34 +3499,34 @@
         <v>175</v>
       </c>
       <c r="B45" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>211</v>
+        <v>289</v>
       </c>
       <c r="D45" s="2">
         <v>2009</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H45" s="2">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>334</v>
@@ -3545,34 +3537,37 @@
         <v>175</v>
       </c>
       <c r="B46" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D46" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H46" s="2">
-        <v>78</v>
-      </c>
-      <c r="I46" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3580,16 +3575,16 @@
         <v>175</v>
       </c>
       <c r="B47" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D47" s="2">
         <v>2008</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>150</v>
@@ -3601,13 +3596,13 @@
         <v>78</v>
       </c>
       <c r="I47" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3615,156 +3610,156 @@
         <v>175</v>
       </c>
       <c r="B48" s="2">
+        <v>3</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2008</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H48" s="2">
+        <v>78</v>
+      </c>
+      <c r="I48" s="2">
         <v>2</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D48" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H48" s="2">
-        <v>77</v>
-      </c>
-      <c r="I48" s="2">
-        <v>7</v>
-      </c>
       <c r="J48" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="O48" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="20" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="D49" s="2">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H49" s="2">
-        <v>2001</v>
+        <v>77</v>
       </c>
       <c r="I49" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="20" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>360</v>
+        <v>175</v>
       </c>
       <c r="B50" s="2">
         <v>1</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2001</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H50" s="2">
+        <v>2001</v>
+      </c>
+      <c r="I50" s="2">
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B51" s="2">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D51" s="2">
         <v>2010</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G50" s="2" t="s">
+      <c r="F51" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H51" s="2">
         <v>72</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I51" s="2">
         <v>5</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="J51" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="20" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B51" s="2">
-        <v>3</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="D51" s="2">
-        <v>2023</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H51" s="2">
-        <v>15</v>
-      </c>
-      <c r="I51" s="2">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>362</v>
       </c>
       <c r="B52" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D52" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>150</v>
@@ -3773,250 +3768,268 @@
         <v>158</v>
       </c>
       <c r="H52" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I52" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="20" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>362</v>
       </c>
       <c r="B53" s="2">
+        <v>2</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2021</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H53" s="2">
+        <v>13</v>
+      </c>
+      <c r="I53" s="2">
+        <v>4</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B54" s="2">
         <v>1</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D54" s="2">
         <v>2010</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G53" s="2" t="s">
+      <c r="F54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H54" s="2">
         <v>63</v>
       </c>
-      <c r="I53" s="2">
+      <c r="I54" s="2">
         <v>8</v>
       </c>
-      <c r="J53" s="2" t="s">
+      <c r="J54" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="K53" s="2" t="s">
+      <c r="K54" s="2" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B54" s="2">
-        <v>2</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D54" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="50" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>365</v>
       </c>
       <c r="B55" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>368</v>
+        <v>208</v>
       </c>
       <c r="D55" s="2">
         <v>2007</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G55" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="50" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B56" s="2">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D56" s="2">
+        <v>2007</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="K56" s="2" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="20" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B56" s="2">
+    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="2">
         <v>60</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="20" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B57" s="2">
+      <c r="F57" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="2">
         <v>59</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="20" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B58" s="2">
-        <v>58</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="2">
+        <v>58</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B59" s="2">
+      <c r="F59" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="2">
         <v>57</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="20" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B60" s="2">
+      <c r="F60" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="2">
         <v>56</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="20" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B61" s="2">
+      <c r="F61" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="2">
         <v>55</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="20" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" s="2">
-        <v>54</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E62" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="2">
+        <v>54</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="20" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63" s="2">
+      <c r="F63" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="2">
         <v>53</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="20" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B64" s="2">
-        <v>52</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>150</v>
@@ -4027,47 +4040,47 @@
         <v>3</v>
       </c>
       <c r="B65" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="2">
+        <v>51</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B66" s="2">
+      <c r="F66" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="2">
         <v>50</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B67" s="2">
-        <v>49</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>150</v>
@@ -4078,47 +4091,47 @@
         <v>3</v>
       </c>
       <c r="B68" s="2">
+        <v>49</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="2">
         <v>48</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E69" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B69" s="2">
+      <c r="F69" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="2">
         <v>47</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" s="2">
-        <v>46</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>150</v>
@@ -4129,47 +4142,47 @@
         <v>3</v>
       </c>
       <c r="B71" s="2">
+        <v>46</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="2">
         <v>45</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" s="2">
+      <c r="F72" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="2">
         <v>44</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B73" s="2">
-        <v>43</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>150</v>
@@ -4180,13 +4193,13 @@
         <v>3</v>
       </c>
       <c r="B74" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>150</v>
@@ -4197,13 +4210,13 @@
         <v>3</v>
       </c>
       <c r="B75" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>150</v>
@@ -4214,13 +4227,13 @@
         <v>3</v>
       </c>
       <c r="B76" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>150</v>
@@ -4231,13 +4244,13 @@
         <v>3</v>
       </c>
       <c r="B77" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>150</v>
@@ -4248,30 +4261,30 @@
         <v>3</v>
       </c>
       <c r="B78" s="2">
+        <v>39</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="2">
         <v>38</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B79" s="2">
-        <v>37</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>150</v>
@@ -4282,64 +4295,64 @@
         <v>3</v>
       </c>
       <c r="B80" s="2">
+        <v>37</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="2">
         <v>36</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B81" s="2">
+      <c r="F81" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="2">
         <v>35</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F81" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B82" s="2">
+      <c r="F82" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="2">
         <v>34</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B83" s="2">
-        <v>33</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>150</v>
@@ -4350,30 +4363,30 @@
         <v>3</v>
       </c>
       <c r="B84" s="2">
+        <v>33</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="2">
         <v>32</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B85" s="2">
-        <v>31</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>150</v>
@@ -4384,30 +4397,30 @@
         <v>3</v>
       </c>
       <c r="B86" s="2">
+        <v>31</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="2">
         <v>30</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B87" s="2">
-        <v>29</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>150</v>
@@ -4418,36 +4431,36 @@
         <v>3</v>
       </c>
       <c r="B88" s="2">
+        <v>29</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="2">
         <v>28</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B89" s="2">
-        <v>27</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="F89" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -4455,10 +4468,10 @@
         <v>27</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>150</v>
@@ -4469,13 +4482,13 @@
         <v>3</v>
       </c>
       <c r="B91" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>150</v>
@@ -4486,47 +4499,47 @@
         <v>3</v>
       </c>
       <c r="B92" s="2">
+        <v>26</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="2">
         <v>25</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E93" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F92" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B93" s="2">
+      <c r="F93" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="2">
         <v>24</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E94" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B94" s="2">
-        <v>23</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>150</v>
@@ -4537,13 +4550,13 @@
         <v>3</v>
       </c>
       <c r="B95" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>150</v>
@@ -4554,13 +4567,13 @@
         <v>3</v>
       </c>
       <c r="B96" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>150</v>
@@ -4571,13 +4584,13 @@
         <v>3</v>
       </c>
       <c r="B97" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>150</v>
@@ -4588,13 +4601,13 @@
         <v>3</v>
       </c>
       <c r="B98" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>150</v>
@@ -4605,81 +4618,81 @@
         <v>3</v>
       </c>
       <c r="B99" s="2">
+        <v>19</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="2">
         <v>18</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F99" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B100" s="2">
+      <c r="F100" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="2">
         <v>17</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E101" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F100" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B101" s="2">
+      <c r="F101" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="2">
         <v>16</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F101" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B102" s="2">
+      <c r="F102" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="2">
         <v>15</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B103" s="2">
-        <v>14</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>150</v>
@@ -4690,13 +4703,13 @@
         <v>3</v>
       </c>
       <c r="B104" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>150</v>
@@ -4707,13 +4720,13 @@
         <v>3</v>
       </c>
       <c r="B105" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>150</v>
@@ -4724,13 +4737,13 @@
         <v>3</v>
       </c>
       <c r="B106" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>150</v>
@@ -4741,13 +4754,13 @@
         <v>3</v>
       </c>
       <c r="B107" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>150</v>
@@ -4758,47 +4771,47 @@
         <v>3</v>
       </c>
       <c r="B108" s="2">
+        <v>10</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="2">
         <v>9</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F108" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B109" s="2">
+      <c r="F109" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B110" s="2">
         <v>8</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B110" s="2">
-        <v>7</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>150</v>
@@ -4809,81 +4822,81 @@
         <v>3</v>
       </c>
       <c r="B111" s="2">
+        <v>7</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B112" s="2">
         <v>6</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E112" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F111" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B112" s="2">
+      <c r="F112" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" s="2">
         <v>5</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E113" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F112" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B113" s="2">
+      <c r="F113" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B114" s="2">
         <v>4</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E114" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F113" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B114" s="2">
-        <v>3</v>
-      </c>
-      <c r="C114" s="1" t="s">
+      <c r="F114" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" s="2">
+        <v>3</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B115" s="2">
-        <v>2</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>150</v>
@@ -4894,30 +4907,30 @@
         <v>3</v>
       </c>
       <c r="B116" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="B117" s="2">
         <v>1</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>150</v>
@@ -4925,67 +4938,84 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B118" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B119" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B120" s="2">
+        <v>2</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B121" s="2">
         <v>1</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="E121" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F120" s="2" t="s">
+      <c r="F121" s="2" t="s">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <hyperlinks>
-    <hyperlink ref="L19" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="L39" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="K42" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="L43" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="K11" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="O6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="M4" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
-    <hyperlink ref="Q6" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
-    <hyperlink ref="R4" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
+    <hyperlink ref="L20" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L40" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K43" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="L44" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K12" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M5" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
+    <hyperlink ref="Q7" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
+    <hyperlink ref="R5" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId10"/>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A9DB9E-09D1-402E-A15A-F02531D7C5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A981BCA1-D8FB-4899-A378-1E1AF1D21E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="431">
   <si>
     <t>Nr</t>
   </si>
@@ -1326,6 +1326,9 @@
   </si>
   <si>
     <t>Danzer, M.F., **Rufibach, K.**, Beyersmann, J., Schmidt, R.</t>
+  </si>
+  <si>
+    <t>903--914</t>
   </si>
 </sst>
 </file>
@@ -2038,10 +2041,19 @@
         <v>394</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>385</v>
+        <v>150</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>415</v>
+      </c>
+      <c r="H7" s="2">
+        <v>34</v>
+      </c>
+      <c r="I7" s="2">
+        <v>5</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>419</v>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A981BCA1-D8FB-4899-A378-1E1AF1D21E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29983FD-5EB8-4E59-BB31-43484EF2B262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="432">
   <si>
     <t>Nr</t>
   </si>
@@ -1329,6 +1329,9 @@
   </si>
   <si>
     <t>903--914</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2512.08658</t>
   </si>
 </sst>
 </file>
@@ -1781,32 +1784,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T121"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="25.81640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="29.54296875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.54296875" style="1"/>
+    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="29.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1868,7 +1871,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>370</v>
       </c>
@@ -1890,9 +1893,12 @@
       <c r="G2" s="2" t="s">
         <v>172</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>431</v>
+      </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>370</v>
       </c>
@@ -1916,7 +1922,7 @@
       </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>370</v>
       </c>
@@ -1946,7 +1952,7 @@
       </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="40" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>175</v>
       </c>
@@ -1994,7 +2000,7 @@
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>175</v>
       </c>
@@ -2024,7 +2030,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>175</v>
       </c>
@@ -2072,7 +2078,7 @@
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>175</v>
       </c>
@@ -2113,7 +2119,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>175</v>
       </c>
@@ -2152,7 +2158,7 @@
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>175</v>
       </c>
@@ -2200,7 +2206,7 @@
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>175</v>
       </c>
@@ -2235,7 +2241,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>175</v>
       </c>
@@ -2276,7 +2282,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>175</v>
       </c>
@@ -2329,7 +2335,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>175</v>
       </c>
@@ -2364,7 +2370,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>175</v>
       </c>
@@ -2399,7 +2405,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>175</v>
       </c>
@@ -2434,7 +2440,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>175</v>
       </c>
@@ -2472,7 +2478,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>175</v>
       </c>
@@ -2504,7 +2510,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>175</v>
       </c>
@@ -2554,7 +2560,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>175</v>
       </c>
@@ -2598,7 +2604,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>175</v>
       </c>
@@ -2636,7 +2642,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>175</v>
       </c>
@@ -2671,7 +2677,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>175</v>
       </c>
@@ -2718,7 +2724,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>175</v>
       </c>
@@ -2750,7 +2756,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>175</v>
       </c>
@@ -2791,7 +2797,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>175</v>
       </c>
@@ -2829,7 +2835,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>175</v>
       </c>
@@ -2867,7 +2873,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>175</v>
       </c>
@@ -2902,7 +2908,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>175</v>
       </c>
@@ -2937,7 +2943,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>175</v>
       </c>
@@ -2975,7 +2981,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>175</v>
       </c>
@@ -3010,7 +3016,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>175</v>
       </c>
@@ -3042,7 +3048,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>175</v>
       </c>
@@ -3080,7 +3086,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>175</v>
       </c>
@@ -3118,7 +3124,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>175</v>
       </c>
@@ -3159,7 +3165,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>175</v>
       </c>
@@ -3201,7 +3207,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>175</v>
       </c>
@@ -3242,7 +3248,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>175</v>
       </c>
@@ -3281,7 +3287,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>175</v>
       </c>
@@ -3316,7 +3322,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>175</v>
       </c>
@@ -3357,7 +3363,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>175</v>
       </c>
@@ -3395,7 +3401,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>175</v>
       </c>
@@ -3433,7 +3439,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>175</v>
       </c>
@@ -3468,7 +3474,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>175</v>
       </c>
@@ -3506,7 +3512,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>175</v>
       </c>
@@ -3544,7 +3550,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>175</v>
       </c>
@@ -3582,7 +3588,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>175</v>
       </c>
@@ -3617,7 +3623,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>175</v>
       </c>
@@ -3652,7 +3658,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>175</v>
       </c>
@@ -3690,7 +3696,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>175</v>
       </c>
@@ -3725,7 +3731,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>360</v>
       </c>
@@ -3757,7 +3763,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>362</v>
       </c>
@@ -3792,7 +3798,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>362</v>
       </c>
@@ -3827,7 +3833,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>362</v>
       </c>
@@ -3862,7 +3868,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>365</v>
       </c>
@@ -3885,7 +3891,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="50" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>365</v>
       </c>
@@ -3911,7 +3917,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>3</v>
       </c>
@@ -3928,7 +3934,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>3</v>
       </c>
@@ -3945,7 +3951,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>3</v>
       </c>
@@ -3962,7 +3968,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>3</v>
       </c>
@@ -3979,7 +3985,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>3</v>
       </c>
@@ -3996,7 +4002,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>3</v>
       </c>
@@ -4013,7 +4019,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>3</v>
       </c>
@@ -4030,7 +4036,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4047,7 +4053,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -4064,7 +4070,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -4081,7 +4087,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
@@ -4098,7 +4104,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4115,7 +4121,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -4132,7 +4138,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -4149,7 +4155,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
@@ -4166,7 +4172,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -4183,7 +4189,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -4200,7 +4206,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -4217,7 +4223,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -4234,7 +4240,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -4251,7 +4257,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -4268,7 +4274,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -4285,7 +4291,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -4302,7 +4308,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -4319,7 +4325,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -4336,7 +4342,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -4353,7 +4359,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -4370,7 +4376,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -4387,7 +4393,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -4404,7 +4410,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -4421,7 +4427,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -4438,7 +4444,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -4455,7 +4461,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -4472,7 +4478,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -4489,7 +4495,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -4506,7 +4512,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -4523,7 +4529,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -4540,7 +4546,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4557,7 +4563,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
@@ -4574,7 +4580,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -4591,7 +4597,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -4608,7 +4614,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
@@ -4625,7 +4631,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
@@ -4642,7 +4648,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
@@ -4659,7 +4665,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
@@ -4676,7 +4682,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
@@ -4693,7 +4699,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
@@ -4710,7 +4716,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
@@ -4727,7 +4733,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
@@ -4744,7 +4750,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
@@ -4761,7 +4767,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
@@ -4778,7 +4784,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
@@ -4795,7 +4801,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
@@ -4812,7 +4818,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
@@ -4829,7 +4835,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
@@ -4846,7 +4852,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -4863,7 +4869,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>3</v>
       </c>
@@ -4880,7 +4886,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
@@ -4897,7 +4903,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>3</v>
       </c>
@@ -4914,7 +4920,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
@@ -4931,7 +4937,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
@@ -4948,7 +4954,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>104</v>
       </c>
@@ -4965,7 +4971,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>97</v>
       </c>
@@ -4982,7 +4988,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>97</v>
       </c>
@@ -4999,7 +5005,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>97</v>
       </c>
@@ -5028,9 +5034,10 @@
     <hyperlink ref="M5" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
     <hyperlink ref="Q7" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
     <hyperlink ref="R5" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
+    <hyperlink ref="L2" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId11"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29983FD-5EB8-4E59-BB31-43484EF2B262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E518FC3-61C4-4233-A90B-B744E3815C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1166,9 +1166,6 @@
     <t>preprint</t>
   </si>
   <si>
-    <t>https://insightsengineering.github.io/simIDM/latest-tag/</t>
-  </si>
-  <si>
     <t>Hampson, L.V. and Degtyarev, E. and Tang, R., and Lin, J. and **Rufibach, K.** and Zheng, C.</t>
   </si>
   <si>
@@ -1332,6 +1329,9 @@
   </si>
   <si>
     <t>https://arxiv.org/abs/2512.08658</t>
+  </si>
+  <si>
+    <t>https://insightsengineering.github.io/simIDM/main/</t>
   </si>
 </sst>
 </file>
@@ -1879,13 +1879,13 @@
         <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -1894,7 +1894,7 @@
         <v>172</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="T2" s="2"/>
     </row>
@@ -1906,13 +1906,13 @@
         <v>48</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>149</v>
@@ -1930,13 +1930,13 @@
         <v>47</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>149</v>
@@ -1945,10 +1945,10 @@
         <v>172</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="T4" s="2"/>
     </row>
@@ -1960,13 +1960,13 @@
         <v>46</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D5" s="2">
         <v>2025</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>150</v>
@@ -1978,25 +1978,25 @@
         <v>47</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>412</v>
+      </c>
+      <c r="R5" s="5" t="s">
         <v>426</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>413</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>427</v>
       </c>
       <c r="T5" s="2"/>
     </row>
@@ -2008,25 +2008,25 @@
         <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>234</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="T6" s="2"/>
     </row>
@@ -2038,19 +2038,19 @@
         <v>44</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H7" s="2">
         <v>34</v>
@@ -2059,22 +2059,22 @@
         <v>5</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="T7" s="2"/>
     </row>
@@ -2089,25 +2089,25 @@
         <v>169</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>147</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>234</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>376</v>
+      <c r="M8" s="4" t="s">
+        <v>431</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>180</v>
@@ -2148,13 +2148,13 @@
         <v>1</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="T9" s="2"/>
     </row>
@@ -2166,13 +2166,13 @@
         <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D10" s="2">
         <v>2024</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>150</v>
@@ -2184,22 +2184,22 @@
         <v>25</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="N10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>293</v>
@@ -2226,7 +2226,7 @@
         <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H11" s="2">
         <v>15</v>
@@ -2235,7 +2235,7 @@
         <v>1223858</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>177</v>
@@ -2323,10 +2323,10 @@
         <v>292</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>293</v>
@@ -2551,10 +2551,10 @@
         <v>292</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>293</v>
@@ -2715,10 +2715,10 @@
         <v>292</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="R23" s="2" t="s">
         <v>293</v>
@@ -3771,7 +3771,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D52" s="2">
         <v>2023</v>
@@ -3795,7 +3795,7 @@
         <v>363</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3806,7 +3806,7 @@
         <v>2</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D53" s="2">
         <v>2021</v>
@@ -3830,7 +3830,7 @@
         <v>364</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3847,13 +3847,13 @@
         <v>2010</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="H54" s="2">
         <v>63</v>
@@ -3862,10 +3862,10 @@
         <v>8</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
@@ -3914,7 +3914,7 @@
         <v>367</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -5035,9 +5035,10 @@
     <hyperlink ref="Q7" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
     <hyperlink ref="R5" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
     <hyperlink ref="L2" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
+    <hyperlink ref="M8" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId12"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E518FC3-61C4-4233-A90B-B744E3815C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FBC77D-54E2-4761-923C-80F515AA1106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$S$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$S$123</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="440">
   <si>
     <t>Nr</t>
   </si>
@@ -1332,6 +1332,30 @@
   </si>
   <si>
     <t>https://insightsengineering.github.io/simIDM/main/</t>
+  </si>
+  <si>
+    <t>Estimands and causal inference</t>
+  </si>
+  <si>
+    <t>Estimands in Clinical Trials (J. Wei, L. Meng, F. Bretz, F. Chen and J. Wang, eds.)</t>
+  </si>
+  <si>
+    <t>Akacha, M., Bartlett, J., Bornkamp, B., Lyu, T., Michiels, H., **Rufibach, K.**</t>
+  </si>
+  <si>
+    <t>Qiu, J., Burger, H.U., Delmar, P., Degtyarev, E., Fletcher, C., Polverejan, E., Price, C., Ruberg, S.J., **Rufibach, K.**, Sfikas, N., Van Meter, L., Wang, S.</t>
+  </si>
+  <si>
+    <t>Global Initiatives Since the Release of ICH E9(R1)</t>
+  </si>
+  <si>
+    <t>Book chapters</t>
+  </si>
+  <si>
+    <t>Chapter 6, 91-111</t>
+  </si>
+  <si>
+    <t>Chapter 5, 69-89</t>
   </si>
 </sst>
 </file>
@@ -1783,33 +1807,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T121"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:T123"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="25.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="29.5703125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="97.90625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="43" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="25.81640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="29.54296875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1871,7 +1895,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>370</v>
       </c>
@@ -1898,7 +1922,7 @@
       </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>370</v>
       </c>
@@ -1922,7 +1946,7 @@
       </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>370</v>
       </c>
@@ -1952,7 +1976,7 @@
       </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="45" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" ht="40" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>175</v>
       </c>
@@ -2000,7 +2024,7 @@
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>175</v>
       </c>
@@ -2030,7 +2054,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>175</v>
       </c>
@@ -2078,7 +2102,7 @@
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>175</v>
       </c>
@@ -2119,7 +2143,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>175</v>
       </c>
@@ -2158,7 +2182,7 @@
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>175</v>
       </c>
@@ -2206,7 +2230,7 @@
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>175</v>
       </c>
@@ -2241,7 +2265,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>175</v>
       </c>
@@ -2282,7 +2306,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>175</v>
       </c>
@@ -2335,7 +2359,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>175</v>
       </c>
@@ -2370,7 +2394,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>175</v>
       </c>
@@ -2405,7 +2429,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>175</v>
       </c>
@@ -2440,7 +2464,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>175</v>
       </c>
@@ -2478,7 +2502,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>175</v>
       </c>
@@ -2510,7 +2534,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>175</v>
       </c>
@@ -2560,7 +2584,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>175</v>
       </c>
@@ -2604,7 +2628,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>175</v>
       </c>
@@ -2642,7 +2666,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>175</v>
       </c>
@@ -2677,7 +2701,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>175</v>
       </c>
@@ -2724,7 +2748,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>175</v>
       </c>
@@ -2756,7 +2780,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>175</v>
       </c>
@@ -2797,7 +2821,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>175</v>
       </c>
@@ -2835,7 +2859,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>175</v>
       </c>
@@ -2873,7 +2897,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>175</v>
       </c>
@@ -2908,7 +2932,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>175</v>
       </c>
@@ -2943,7 +2967,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>175</v>
       </c>
@@ -2981,7 +3005,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>175</v>
       </c>
@@ -3016,7 +3040,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>175</v>
       </c>
@@ -3048,7 +3072,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>175</v>
       </c>
@@ -3086,7 +3110,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>175</v>
       </c>
@@ -3124,7 +3148,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>175</v>
       </c>
@@ -3165,7 +3189,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>175</v>
       </c>
@@ -3207,7 +3231,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>175</v>
       </c>
@@ -3248,7 +3272,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>175</v>
       </c>
@@ -3287,7 +3311,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>175</v>
       </c>
@@ -3322,7 +3346,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>175</v>
       </c>
@@ -3363,7 +3387,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>175</v>
       </c>
@@ -3401,7 +3425,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>175</v>
       </c>
@@ -3439,7 +3463,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>175</v>
       </c>
@@ -3474,7 +3498,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>175</v>
       </c>
@@ -3512,7 +3536,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>175</v>
       </c>
@@ -3550,7 +3574,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>175</v>
       </c>
@@ -3588,7 +3612,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>175</v>
       </c>
@@ -3623,7 +3647,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>175</v>
       </c>
@@ -3658,7 +3682,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>175</v>
       </c>
@@ -3696,7 +3720,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>175</v>
       </c>
@@ -3731,1294 +3755,1346 @@
         <v>369</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B51" s="2">
+        <v>2</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B52" s="2">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B53" s="2">
         <v>1</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D53" s="2">
         <v>2010</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G51" s="2" t="s">
+      <c r="F53" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H53" s="2">
         <v>72</v>
       </c>
-      <c r="I51" s="2">
+      <c r="I53" s="2">
         <v>5</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="J53" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B52" s="2">
-        <v>3</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="D52" s="2">
-        <v>2023</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H52" s="2">
-        <v>15</v>
-      </c>
-      <c r="I52" s="2">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B53" s="2">
-        <v>2</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="D53" s="2">
-        <v>2021</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H53" s="2">
-        <v>13</v>
-      </c>
-      <c r="I53" s="2">
-        <v>4</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>362</v>
       </c>
       <c r="B54" s="2">
+        <v>3</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2023</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H54" s="2">
+        <v>15</v>
+      </c>
+      <c r="I54" s="2">
         <v>1</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D54" s="2">
-        <v>2010</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="H54" s="2">
-        <v>63</v>
-      </c>
-      <c r="I54" s="2">
-        <v>8</v>
-      </c>
       <c r="J54" s="2" t="s">
-        <v>401</v>
+        <v>363</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B55" s="2">
         <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>208</v>
+        <v>377</v>
       </c>
       <c r="D55" s="2">
-        <v>2007</v>
+        <v>2021</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" ht="67.5" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+      <c r="H55" s="2">
+        <v>13</v>
+      </c>
+      <c r="I55" s="2">
+        <v>4</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B56" s="2">
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D56" s="2">
+        <v>2010</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="H56" s="2">
+        <v>63</v>
+      </c>
+      <c r="I56" s="2">
+        <v>8</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B57" s="2">
+        <v>2</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2007</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="50" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B58" s="2">
+        <v>1</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D58" s="2">
         <v>2007</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G58" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="K58" s="2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B57" s="2">
+    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="2">
         <v>60</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B58" s="2">
+      <c r="F59" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="2">
         <v>59</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B59" s="2">
+      <c r="F60" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="2">
         <v>58</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B60" s="2">
+      <c r="F61" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="2">
         <v>57</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B61" s="2">
+      <c r="F62" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="2">
         <v>56</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F61" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" s="2">
+      <c r="F63" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="2">
         <v>55</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63" s="2">
+      <c r="F64" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="2">
         <v>54</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B64" s="2">
-        <v>53</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="2">
-        <v>52</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="2">
+        <v>53</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="2">
+        <v>52</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B66" s="2">
+      <c r="F67" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="2">
         <v>51</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B67" s="2">
-        <v>50</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B68" s="2">
-        <v>49</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="2">
+        <v>50</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="2">
+        <v>49</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B69" s="2">
+      <c r="F70" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="2">
         <v>48</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" s="2">
+      <c r="F71" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="2">
         <v>47</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" s="2">
+      <c r="F72" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="2">
         <v>46</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" s="2">
+      <c r="F73" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="2">
         <v>45</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B73" s="2">
+      <c r="F74" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="2">
         <v>44</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B74" s="2">
+      <c r="F75" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="2">
         <v>43</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="2">
+      <c r="F76" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="2">
         <v>42</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C77" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F75" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B76" s="2">
+      <c r="F77" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="2">
         <v>41</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B77" s="2">
+      <c r="F78" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="2">
         <v>40</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B78" s="2">
+      <c r="F79" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="2">
         <v>39</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B79" s="2">
+      <c r="F80" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="2">
         <v>38</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B80" s="2">
+      <c r="F81" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="2">
         <v>37</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B81" s="2">
+      <c r="F82" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="2">
         <v>36</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F81" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B82" s="2">
+      <c r="F83" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="2">
         <v>35</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B83" s="2">
+      <c r="F84" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="2">
         <v>34</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B84" s="2">
+      <c r="F85" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="2">
         <v>33</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F84" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B85" s="2">
+      <c r="F86" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="2">
         <v>32</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F85" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B86" s="2">
+      <c r="F87" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="2">
         <v>31</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B87" s="2">
+      <c r="F88" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="2">
         <v>30</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B88" s="2">
+      <c r="F89" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="2">
         <v>29</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B89" s="2">
+      <c r="F90" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="2">
         <v>28</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B90" s="2">
+      <c r="F91" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="2">
         <v>27</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E92" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B91" s="2">
+      <c r="F92" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="2">
         <v>27</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E93" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B92" s="2">
+      <c r="F93" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="2">
         <v>26</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E94" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F92" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B93" s="2">
+      <c r="F94" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" s="2">
         <v>25</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E95" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F93" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B94" s="2">
+      <c r="F95" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="2">
         <v>24</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B95" s="2">
+      <c r="F96" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="2">
         <v>23</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C97" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E97" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B96" s="2">
+      <c r="F97" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="2">
         <v>22</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F96" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B97" s="2">
+      <c r="F98" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="2">
         <v>21</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E99" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B98" s="2">
+      <c r="F99" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="2">
         <v>20</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F98" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B99" s="2">
+      <c r="F100" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="2">
         <v>19</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E101" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F99" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B100" s="2">
+      <c r="F101" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="2">
         <v>18</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F100" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B101" s="2">
+      <c r="F102" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="2">
         <v>17</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F101" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B102" s="2">
+      <c r="F103" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="2">
         <v>16</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E104" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F102" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B103" s="2">
+      <c r="F104" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="2">
         <v>15</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F103" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B104" s="2">
+      <c r="F105" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="2">
         <v>14</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F104" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B105" s="2">
+      <c r="F106" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="2">
         <v>13</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F105" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B106" s="2">
+      <c r="F107" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="2">
         <v>12</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B107" s="2">
-        <v>11</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B108" s="2">
-        <v>10</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="2">
+        <v>11</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B110" s="2">
+        <v>10</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F108" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B109" s="2">
+      <c r="F110" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B111" s="2">
         <v>9</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E111" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F109" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B110" s="2">
+      <c r="F111" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B112" s="2">
         <v>8</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="E112" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F110" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B111" s="2">
+      <c r="F112" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" s="2">
         <v>7</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E113" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F111" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B112" s="2">
+      <c r="F113" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B114" s="2">
         <v>6</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E114" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F112" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B113" s="2">
+      <c r="F114" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" s="2">
         <v>5</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F113" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B114" s="2">
+      <c r="F115" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" s="2">
         <v>4</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F114" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B115" s="2">
-        <v>3</v>
-      </c>
-      <c r="C115" s="1" t="s">
+      <c r="F116" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B117" s="2">
+        <v>3</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F115" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B116" s="2">
+      <c r="F117" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" s="2">
         <v>2</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C118" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F116" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B117" s="2">
+      <c r="F118" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B119" s="2">
         <v>1</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F117" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A118" s="1" t="s">
+      <c r="F119" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B120" s="2">
         <v>1</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C120" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F118" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A119" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B119" s="2">
-        <v>3</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A120" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B120" s="2">
-        <v>2</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="F120" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B121" s="2">
+        <v>3</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B122" s="2">
+        <v>2</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B123" s="2">
         <v>1</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C123" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="E123" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F121" s="2" t="s">
+      <c r="F123" s="2" t="s">
         <v>150</v>
       </c>
     </row>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FBC77D-54E2-4761-923C-80F515AA1106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBEA517C-A657-4865-9486-A29B1B8A0DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="441">
   <si>
     <t>Nr</t>
   </si>
@@ -1356,6 +1356,9 @@
   </si>
   <si>
     <t>Chapter 5, 69-89</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/book/10.1007/978-3-032-02192-2</t>
   </si>
 </sst>
 </file>
@@ -3780,8 +3783,11 @@
       <c r="J51" s="2" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K51" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>437</v>
       </c>
@@ -3805,6 +3811,9 @@
       </c>
       <c r="J52" s="2" t="s">
         <v>439</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3944,7 +3953,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>365</v>
       </c>
@@ -3967,7 +3976,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="50" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>365</v>
       </c>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBEA517C-A657-4865-9486-A29B1B8A0DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FDE3E4-7F9A-45B8-BA74-74B1BB81212A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$S$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$S$124</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="444">
   <si>
     <t>Nr</t>
   </si>
@@ -1359,6 +1359,15 @@
   </si>
   <si>
     <t>https://link.springer.com/book/10.1007/978-3-032-02192-2</t>
+  </si>
+  <si>
+    <t>2026+</t>
+  </si>
+  <si>
+    <t>Uncertainty intervals for covariate adjusted marginal treatment effects in randomized clinical trials with time-to-event endpoint</t>
+  </si>
+  <si>
+    <t>Götte, H., **Rufibach, K.**</t>
   </si>
 </sst>
 </file>
@@ -1810,7 +1819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T123"/>
+  <dimension ref="A1:T124"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -1898,21 +1907,21 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>370</v>
       </c>
       <c r="B2" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -1920,26 +1929,23 @@
       <c r="G2" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>430</v>
-      </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>370</v>
       </c>
       <c r="B3" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>419</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>149</v>
@@ -1947,23 +1953,26 @@
       <c r="G3" s="2" t="s">
         <v>172</v>
       </c>
+      <c r="L3" s="4" t="s">
+        <v>430</v>
+      </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>370</v>
       </c>
       <c r="B4" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>419</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>149</v>
@@ -1971,412 +1980,383 @@
       <c r="G4" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="T4" s="2"/>
+    </row>
+    <row r="5" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B5" s="2">
+        <v>47</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>412</v>
-      </c>
-      <c r="T4" s="2"/>
-    </row>
-    <row r="5" spans="1:20" ht="40" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B5" s="2">
-        <v>46</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2025</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="H5" s="2">
-        <v>47</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="Q5" t="s">
         <v>412</v>
       </c>
-      <c r="R5" s="5" t="s">
-        <v>426</v>
-      </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="40" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B6" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>419</v>
+        <v>406</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2025</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>391</v>
+        <v>423</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>384</v>
+        <v>150</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
+      </c>
+      <c r="H6" s="2">
+        <v>47</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>425</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>397</v>
+        <v>407</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>412</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>426</v>
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B7" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>419</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>150</v>
+        <v>384</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="H7" s="2">
-        <v>34</v>
-      </c>
-      <c r="I7" s="2">
-        <v>5</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>429</v>
+        <v>234</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B8" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>169</v>
+        <v>394</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>419</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>147</v>
+        <v>393</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>384</v>
+        <v>150</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>234</v>
+        <v>414</v>
+      </c>
+      <c r="H8" s="2">
+        <v>34</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>429</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="T8" s="2"/>
+    </row>
+    <row r="9" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B9" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D9" s="2">
-        <v>2025</v>
+        <v>169</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>419</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>373</v>
+        <v>147</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>150</v>
+        <v>384</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H9" s="2">
-        <v>17</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>417</v>
+        <v>234</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="T9" s="2"/>
-    </row>
-    <row r="10" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B10" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="D10" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="H10" s="2">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>293</v>
+        <v>385</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>380</v>
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B11" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>176</v>
+        <v>382</v>
       </c>
       <c r="D11" s="2">
         <v>2024</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>146</v>
+        <v>381</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>379</v>
+        <v>238</v>
       </c>
       <c r="H11" s="2">
-        <v>15</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1223858</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>378</v>
+        <v>25</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="T11" s="2"/>
+    </row>
+    <row r="12" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B12" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D12" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>154</v>
+        <v>379</v>
       </c>
       <c r="H12" s="2">
-        <v>22</v>
-      </c>
-      <c r="I12" s="2">
-        <v>4</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>174</v>
+        <v>15</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1223858</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B13" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="D13" s="2">
         <v>2023</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H13" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2">
         <v>4</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>290</v>
+        <v>160</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>291</v>
+        <v>181</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B14" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="D14" s="2">
         <v>2023</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>150</v>
@@ -2388,30 +2368,48 @@
         <v>15</v>
       </c>
       <c r="I14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B15" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="D15" s="2">
         <v>2023</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>150</v>
@@ -2423,118 +2421,121 @@
         <v>15</v>
       </c>
       <c r="I15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>159</v>
+        <v>371</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B16" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="D16" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="H16" s="2">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="I16" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B17" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D17" s="2">
         <v>2022</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="H17" s="2">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="I17" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B18" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D18" s="2">
         <v>2022</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H18" s="2">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="I18" s="2">
+        <v>5</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
@@ -2542,131 +2543,125 @@
         <v>175</v>
       </c>
       <c r="B19" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D19" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H19" s="2">
-        <v>22</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2">
-        <v>420</v>
+        <v>21</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>237</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B20" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D20" s="2">
         <v>2021</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H20" s="2">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="I20" s="2">
-        <v>4</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>243</v>
+        <v>1</v>
+      </c>
+      <c r="J20" s="2">
+        <v>420</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B21" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D21" s="2">
         <v>2021</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H21" s="2">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="I21" s="2">
+        <v>4</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2674,16 +2669,16 @@
         <v>175</v>
       </c>
       <c r="B22" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D22" s="2">
         <v>2021</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>150</v>
@@ -2695,92 +2690,98 @@
         <v>20</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B23" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D23" s="2">
         <v>2021</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="H23" s="2">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B24" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D24" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H24" s="2">
-        <v>4</v>
-      </c>
-      <c r="I24" s="2">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2788,116 +2789,110 @@
         <v>175</v>
       </c>
       <c r="B25" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="D25" s="2">
         <v>2020</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="H25" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I25" s="2">
-        <v>4</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>249</v>
+        <v>68</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B26" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="D26" s="2">
         <v>2020</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="H26" s="2">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="I26" s="2">
+        <v>4</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B27" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D27" s="2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="H27" s="2">
-        <v>62</v>
-      </c>
-      <c r="I27" s="2">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2905,34 +2900,37 @@
         <v>175</v>
       </c>
       <c r="B28" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D28" s="2">
         <v>2019</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="H28" s="2">
-        <v>38</v>
+        <v>62</v>
+      </c>
+      <c r="I28" s="2">
+        <v>3</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2940,34 +2938,34 @@
         <v>175</v>
       </c>
       <c r="B29" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D29" s="2">
         <v>2019</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H29" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -2975,16 +2973,16 @@
         <v>175</v>
       </c>
       <c r="B30" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D30" s="2">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>150</v>
@@ -2993,19 +2991,16 @@
         <v>236</v>
       </c>
       <c r="H30" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -3013,34 +3008,37 @@
         <v>175</v>
       </c>
       <c r="B31" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D31" s="2">
         <v>2016</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="H31" s="2">
-        <v>58</v>
-      </c>
-      <c r="I31" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
@@ -3048,31 +3046,34 @@
         <v>175</v>
       </c>
       <c r="B32" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D32" s="2">
         <v>2016</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="H32" s="2">
-        <v>47</v>
+        <v>58</v>
+      </c>
+      <c r="I32" s="2">
+        <v>6</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3080,37 +3081,31 @@
         <v>175</v>
       </c>
       <c r="B33" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D33" s="2">
         <v>2016</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H33" s="2">
-        <v>26</v>
-      </c>
-      <c r="I33" s="2">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3118,37 +3113,37 @@
         <v>175</v>
       </c>
       <c r="B34" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D34" s="2">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H34" s="2">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="I34" s="2">
+        <v>2</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3156,40 +3151,37 @@
         <v>175</v>
       </c>
       <c r="B35" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D35" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H35" s="2">
-        <v>75</v>
-      </c>
-      <c r="I35" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3197,41 +3189,40 @@
         <v>175</v>
       </c>
       <c r="B36" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D36" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H36" s="2">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="I36" s="2">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2" t="str">
-        <f>"1-29"</f>
-        <v>1-29</v>
+        <v>4</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3239,40 +3230,41 @@
         <v>175</v>
       </c>
       <c r="B37" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>200</v>
       </c>
       <c r="D37" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="H37" s="2">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="I37" s="2">
-        <v>4</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>265</v>
+        <v>1</v>
+      </c>
+      <c r="J37" s="2" t="str">
+        <f>"1-29"</f>
+        <v>1-29</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3280,38 +3272,40 @@
         <v>175</v>
       </c>
       <c r="B38" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D38" s="2">
         <v>2011</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="H38" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="I38" s="2">
-        <v>6</v>
-      </c>
-      <c r="J38" s="2" t="str">
-        <f>"1-28"</f>
-        <v>1-28</v>
+        <v>4</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3319,34 +3313,38 @@
         <v>175</v>
       </c>
       <c r="B39" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D39" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H39" s="2">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="I39" s="2">
-        <v>4</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>268</v>
+        <v>6</v>
+      </c>
+      <c r="J39" s="2" t="str">
+        <f>"1-28"</f>
+        <v>1-28</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3354,40 +3352,34 @@
         <v>175</v>
       </c>
       <c r="B40" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D40" s="2">
         <v>2010</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H40" s="2">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I40" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3395,37 +3387,40 @@
         <v>175</v>
       </c>
       <c r="B41" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D41" s="2">
         <v>2010</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H41" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I41" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3433,37 +3428,37 @@
         <v>175</v>
       </c>
       <c r="B42" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D42" s="2">
         <v>2010</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H42" s="2">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="I42" s="2">
+        <v>1</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3471,34 +3466,37 @@
         <v>175</v>
       </c>
       <c r="B43" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>200</v>
       </c>
       <c r="D43" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="H43" s="2">
-        <v>31</v>
-      </c>
-      <c r="I43" s="2">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>346</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3506,37 +3504,34 @@
         <v>175</v>
       </c>
       <c r="B44" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D44" s="2">
         <v>2009</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="H44" s="2">
-        <v>79</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>276</v>
+        <v>31</v>
+      </c>
+      <c r="I44" s="2">
+        <v>1</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3544,37 +3539,37 @@
         <v>175</v>
       </c>
       <c r="B45" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>289</v>
+        <v>212</v>
       </c>
       <c r="D45" s="2">
         <v>2009</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H45" s="2">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3582,34 +3577,34 @@
         <v>175</v>
       </c>
       <c r="B46" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>211</v>
+        <v>289</v>
       </c>
       <c r="D46" s="2">
         <v>2009</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H46" s="2">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>334</v>
@@ -3620,34 +3615,37 @@
         <v>175</v>
       </c>
       <c r="B47" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D47" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H47" s="2">
-        <v>78</v>
-      </c>
-      <c r="I47" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3655,16 +3653,16 @@
         <v>175</v>
       </c>
       <c r="B48" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D48" s="2">
         <v>2008</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>150</v>
@@ -3676,13 +3674,13 @@
         <v>78</v>
       </c>
       <c r="I48" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3690,37 +3688,34 @@
         <v>175</v>
       </c>
       <c r="B49" s="2">
+        <v>3</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2008</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H49" s="2">
+        <v>78</v>
+      </c>
+      <c r="I49" s="2">
         <v>2</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D49" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H49" s="2">
-        <v>77</v>
-      </c>
-      <c r="I49" s="2">
-        <v>7</v>
-      </c>
       <c r="J49" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3728,63 +3723,72 @@
         <v>175</v>
       </c>
       <c r="B50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="D50" s="2">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H50" s="2">
-        <v>2001</v>
+        <v>77</v>
       </c>
       <c r="I50" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>437</v>
+        <v>175</v>
       </c>
       <c r="B51" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>435</v>
+        <v>213</v>
       </c>
       <c r="D51" s="2">
-        <v>2026</v>
+        <v>2001</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>436</v>
+        <v>219</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>433</v>
+        <v>286</v>
+      </c>
+      <c r="H51" s="2">
+        <v>2001</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>438</v>
+        <v>287</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>440</v>
+        <v>369</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3792,16 +3796,16 @@
         <v>437</v>
       </c>
       <c r="B52" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D52" s="2">
         <v>2026</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>150</v>
@@ -3810,7 +3814,7 @@
         <v>433</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>440</v>
@@ -3818,69 +3822,63 @@
     </row>
     <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>360</v>
+        <v>437</v>
       </c>
       <c r="B53" s="2">
         <v>1</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>98</v>
+        <v>434</v>
       </c>
       <c r="D53" s="2">
-        <v>2010</v>
+        <v>2026</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>116</v>
+        <v>432</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H53" s="2">
-        <v>72</v>
-      </c>
-      <c r="I53" s="2">
-        <v>5</v>
+        <v>433</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>361</v>
+        <v>439</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B54" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>376</v>
+        <v>98</v>
       </c>
       <c r="D54" s="2">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="H54" s="2">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="I54" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>405</v>
+        <v>361</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3888,16 +3886,16 @@
         <v>362</v>
       </c>
       <c r="B55" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D55" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>150</v>
@@ -3906,16 +3904,16 @@
         <v>158</v>
       </c>
       <c r="H55" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I55" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3923,57 +3921,69 @@
         <v>362</v>
       </c>
       <c r="B56" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>200</v>
+        <v>377</v>
       </c>
       <c r="D56" s="2">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>399</v>
+        <v>139</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>400</v>
+        <v>158</v>
       </c>
       <c r="H56" s="2">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="I56" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B57" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D57" s="2">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>112</v>
+        <v>399</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>366</v>
+        <v>400</v>
+      </c>
+      <c r="H57" s="2">
+        <v>63</v>
+      </c>
+      <c r="I57" s="2">
+        <v>8</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -3981,42 +3991,48 @@
         <v>365</v>
       </c>
       <c r="B58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>368</v>
+        <v>208</v>
       </c>
       <c r="D58" s="2">
         <v>2007</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>402</v>
+        <v>366</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>3</v>
+        <v>365</v>
       </c>
       <c r="B59" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>136</v>
+        <v>368</v>
+      </c>
+      <c r="D59" s="2">
+        <v>2007</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
@@ -4024,13 +4040,13 @@
         <v>3</v>
       </c>
       <c r="B60" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>4</v>
+        <v>136</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>150</v>
@@ -4041,47 +4057,47 @@
         <v>3</v>
       </c>
       <c r="B61" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E61" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="2">
+        <v>58</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F61" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" s="2">
+      <c r="F62" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="2">
         <v>57</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63" s="2">
-        <v>56</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>150</v>
@@ -4092,13 +4108,13 @@
         <v>3</v>
       </c>
       <c r="B64" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>150</v>
@@ -4109,13 +4125,13 @@
         <v>3</v>
       </c>
       <c r="B65" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>150</v>
@@ -4126,13 +4142,13 @@
         <v>3</v>
       </c>
       <c r="B66" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>150</v>
@@ -4143,13 +4159,13 @@
         <v>3</v>
       </c>
       <c r="B67" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>150</v>
@@ -4160,47 +4176,47 @@
         <v>3</v>
       </c>
       <c r="B68" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="2">
+        <v>51</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B69" s="2">
+      <c r="F69" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="2">
         <v>50</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" s="2">
-        <v>49</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>150</v>
@@ -4211,47 +4227,47 @@
         <v>3</v>
       </c>
       <c r="B71" s="2">
+        <v>49</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="2">
         <v>48</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" s="2">
+      <c r="F72" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="2">
         <v>47</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B73" s="2">
-        <v>46</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>150</v>
@@ -4262,47 +4278,47 @@
         <v>3</v>
       </c>
       <c r="B74" s="2">
+        <v>46</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="2">
         <v>45</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="2">
+      <c r="F75" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="2">
         <v>44</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B76" s="2">
-        <v>43</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>150</v>
@@ -4313,13 +4329,13 @@
         <v>3</v>
       </c>
       <c r="B77" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>150</v>
@@ -4330,13 +4346,13 @@
         <v>3</v>
       </c>
       <c r="B78" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>150</v>
@@ -4347,13 +4363,13 @@
         <v>3</v>
       </c>
       <c r="B79" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>150</v>
@@ -4364,13 +4380,13 @@
         <v>3</v>
       </c>
       <c r="B80" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>150</v>
@@ -4381,30 +4397,30 @@
         <v>3</v>
       </c>
       <c r="B81" s="2">
+        <v>39</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="2">
         <v>38</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B82" s="2">
-        <v>37</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>150</v>
@@ -4415,64 +4431,64 @@
         <v>3</v>
       </c>
       <c r="B83" s="2">
+        <v>37</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="2">
         <v>36</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B84" s="2">
+      <c r="F84" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="2">
         <v>35</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F84" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B85" s="2">
+      <c r="F85" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="2">
         <v>34</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B86" s="2">
-        <v>33</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>150</v>
@@ -4483,30 +4499,30 @@
         <v>3</v>
       </c>
       <c r="B87" s="2">
+        <v>33</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="2">
         <v>32</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B88" s="2">
-        <v>31</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>150</v>
@@ -4517,30 +4533,30 @@
         <v>3</v>
       </c>
       <c r="B89" s="2">
+        <v>31</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="2">
         <v>30</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B90" s="2">
-        <v>29</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>150</v>
@@ -4551,36 +4567,36 @@
         <v>3</v>
       </c>
       <c r="B91" s="2">
+        <v>29</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="2">
         <v>28</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E92" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B92" s="2">
-        <v>27</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="F92" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -4588,10 +4604,10 @@
         <v>27</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>150</v>
@@ -4602,13 +4618,13 @@
         <v>3</v>
       </c>
       <c r="B94" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>150</v>
@@ -4619,47 +4635,47 @@
         <v>3</v>
       </c>
       <c r="B95" s="2">
+        <v>26</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="2">
         <v>25</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B96" s="2">
+      <c r="F96" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="2">
         <v>24</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C97" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E97" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B97" s="2">
-        <v>23</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>150</v>
@@ -4670,13 +4686,13 @@
         <v>3</v>
       </c>
       <c r="B98" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>150</v>
@@ -4687,13 +4703,13 @@
         <v>3</v>
       </c>
       <c r="B99" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>150</v>
@@ -4704,13 +4720,13 @@
         <v>3</v>
       </c>
       <c r="B100" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>150</v>
@@ -4721,13 +4737,13 @@
         <v>3</v>
       </c>
       <c r="B101" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>150</v>
@@ -4738,81 +4754,81 @@
         <v>3</v>
       </c>
       <c r="B102" s="2">
+        <v>19</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="2">
         <v>18</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F102" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B103" s="2">
+      <c r="F103" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="2">
         <v>17</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E104" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F103" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B104" s="2">
+      <c r="F104" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="2">
         <v>16</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F104" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B105" s="2">
+      <c r="F105" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="2">
         <v>15</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B106" s="2">
-        <v>14</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>150</v>
@@ -4823,13 +4839,13 @@
         <v>3</v>
       </c>
       <c r="B107" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>150</v>
@@ -4840,13 +4856,13 @@
         <v>3</v>
       </c>
       <c r="B108" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>150</v>
@@ -4857,13 +4873,13 @@
         <v>3</v>
       </c>
       <c r="B109" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>150</v>
@@ -4874,13 +4890,13 @@
         <v>3</v>
       </c>
       <c r="B110" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>150</v>
@@ -4891,47 +4907,47 @@
         <v>3</v>
       </c>
       <c r="B111" s="2">
+        <v>10</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B112" s="2">
         <v>9</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E112" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F111" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B112" s="2">
+      <c r="F112" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" s="2">
         <v>8</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E113" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B113" s="2">
-        <v>7</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>150</v>
@@ -4942,81 +4958,81 @@
         <v>3</v>
       </c>
       <c r="B114" s="2">
+        <v>7</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" s="2">
         <v>6</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F114" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B115" s="2">
+      <c r="F115" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" s="2">
         <v>5</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F115" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B116" s="2">
+      <c r="F116" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B117" s="2">
         <v>4</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F116" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B117" s="2">
-        <v>3</v>
-      </c>
-      <c r="C117" s="1" t="s">
+      <c r="F117" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" s="2">
+        <v>3</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B118" s="2">
-        <v>2</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>150</v>
@@ -5027,30 +5043,30 @@
         <v>3</v>
       </c>
       <c r="B119" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="B120" s="2">
         <v>1</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>150</v>
@@ -5058,69 +5074,86 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B121" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B122" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B123" s="2">
+        <v>2</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B124" s="2">
         <v>1</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C124" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="E124" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F123" s="2" t="s">
+      <c r="F124" s="2" t="s">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <hyperlinks>
-    <hyperlink ref="L20" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="L40" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="K43" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="L44" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="K12" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="O7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="M5" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
-    <hyperlink ref="Q7" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
-    <hyperlink ref="R5" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
-    <hyperlink ref="L2" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
-    <hyperlink ref="M8" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
+    <hyperlink ref="L21" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L41" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K44" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="L45" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K13" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M6" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
+    <hyperlink ref="Q8" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
+    <hyperlink ref="R6" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
+    <hyperlink ref="L3" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
+    <hyperlink ref="M9" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId12"/>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FDE3E4-7F9A-45B8-BA74-74B1BB81212A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92210FC-0756-4D24-B835-4FEB5F213840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="446">
   <si>
     <t>Nr</t>
   </si>
@@ -1368,6 +1368,12 @@
   </si>
   <si>
     <t>Götte, H., **Rufibach, K.**</t>
+  </si>
+  <si>
+    <t>e70101</t>
+  </si>
+  <si>
+    <t>e70017</t>
   </si>
 </sst>
 </file>
@@ -2070,8 +2076,8 @@
       <c r="C7" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>419</v>
+      <c r="D7" s="2">
+        <v>2025</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>391</v>
@@ -2081,6 +2087,12 @@
       </c>
       <c r="G7" s="2" t="s">
         <v>234</v>
+      </c>
+      <c r="H7" s="2">
+        <v>44</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>444</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>422</v>
@@ -2100,8 +2112,8 @@
       <c r="C8" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>419</v>
+      <c r="D8" s="2">
+        <v>2025</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>393</v>
@@ -2148,17 +2160,26 @@
       <c r="C9" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>419</v>
+      <c r="D9" s="2">
+        <v>2025</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>147</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>384</v>
+        <v>150</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
+      </c>
+      <c r="H9" s="2">
+        <v>67</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>445</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>415</v>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92210FC-0756-4D24-B835-4FEB5F213840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738A77F8-BB01-4B39-BE04-C0218C95F67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="446">
   <si>
     <t>Nr</t>
   </si>
@@ -1826,32 +1826,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T124"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="97.90625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.453125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="97.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="43" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="25.81640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="29.54296875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.54296875" style="1"/>
+    <col min="11" max="11" width="23.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="29.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>370</v>
       </c>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>370</v>
       </c>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>370</v>
       </c>
@@ -1988,9 +1988,9 @@
       </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>370</v>
+        <v>175</v>
       </c>
       <c r="B5" s="2">
         <v>47</v>
@@ -1998,17 +1998,17 @@
       <c r="C5" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>419</v>
+      <c r="D5" s="2">
+        <v>2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>408</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>149</v>
+        <v>384</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>409</v>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="40" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>175</v>
       </c>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>175</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>391</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>384</v>
+        <v>150</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>234</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>175</v>
       </c>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>175</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>175</v>
       </c>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>175</v>
       </c>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>175</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>175</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>175</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>175</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>175</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>175</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>175</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>175</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>175</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>175</v>
       </c>
@@ -2685,7 +2685,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>175</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>175</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>175</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>175</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>175</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>175</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>175</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>175</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>175</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>175</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>175</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>175</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>175</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>175</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>175</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>175</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>175</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>175</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>175</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>175</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>175</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>175</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>175</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>175</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>175</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>175</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>175</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>175</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>175</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>175</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>437</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>437</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>360</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>362</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>362</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>362</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>365</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>365</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>3</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>3</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>3</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>3</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -4226,7 +4226,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -4413,7 +4413,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -4430,7 +4430,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -4702,7 +4702,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -4957,7 +4957,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>3</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>3</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>3</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>3</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>3</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>104</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>97</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>97</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>97</v>
       </c>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738A77F8-BB01-4B39-BE04-C0218C95F67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C760ACE0-DD4D-4341-9AF9-FFDBA7C1EFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="447">
   <si>
     <t>Nr</t>
   </si>
@@ -1374,13 +1374,16 @@
   </si>
   <si>
     <t>e70017</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/19466315.2026.2637573</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1396,6 +1399,12 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333333"/>
+      <name val="Open Sans"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1420,7 +1429,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1435,6 +1444,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1826,32 +1836,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T124"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="97.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="97.81640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="43" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="25.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="29.5703125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.5703125" style="1"/>
+    <col min="11" max="11" width="23.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="25.81640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="29.54296875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1913,7 +1923,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>370</v>
       </c>
@@ -1937,7 +1947,7 @@
       </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>370</v>
       </c>
@@ -1964,7 +1974,7 @@
       </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>370</v>
       </c>
@@ -1988,7 +1998,7 @@
       </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" ht="20" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>175</v>
       </c>
@@ -2010,6 +2020,9 @@
       <c r="G5" s="2" t="s">
         <v>158</v>
       </c>
+      <c r="K5" s="6" t="s">
+        <v>446</v>
+      </c>
       <c r="L5" s="2" t="s">
         <v>409</v>
       </c>
@@ -2018,7 +2031,7 @@
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="45" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" ht="40" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>175</v>
       </c>
@@ -2066,7 +2079,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>175</v>
       </c>
@@ -2102,7 +2115,7 @@
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>175</v>
       </c>
@@ -2150,7 +2163,7 @@
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>175</v>
       </c>
@@ -2200,7 +2213,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>175</v>
       </c>
@@ -2239,7 +2252,7 @@
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>175</v>
       </c>
@@ -2287,7 +2300,7 @@
       </c>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>175</v>
       </c>
@@ -2322,7 +2335,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>175</v>
       </c>
@@ -2363,7 +2376,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>175</v>
       </c>
@@ -2416,7 +2429,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>175</v>
       </c>
@@ -2451,7 +2464,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>175</v>
       </c>
@@ -2486,7 +2499,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>175</v>
       </c>
@@ -2521,7 +2534,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>175</v>
       </c>
@@ -2559,7 +2572,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>175</v>
       </c>
@@ -2591,7 +2604,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>175</v>
       </c>
@@ -2641,7 +2654,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>175</v>
       </c>
@@ -2685,7 +2698,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>175</v>
       </c>
@@ -2723,7 +2736,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>175</v>
       </c>
@@ -2758,7 +2771,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>175</v>
       </c>
@@ -2805,7 +2818,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>175</v>
       </c>
@@ -2837,7 +2850,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>175</v>
       </c>
@@ -2878,7 +2891,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>175</v>
       </c>
@@ -2916,7 +2929,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>175</v>
       </c>
@@ -2954,7 +2967,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>175</v>
       </c>
@@ -2989,7 +3002,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>175</v>
       </c>
@@ -3024,7 +3037,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>175</v>
       </c>
@@ -3062,7 +3075,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>175</v>
       </c>
@@ -3097,7 +3110,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>175</v>
       </c>
@@ -3129,7 +3142,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>175</v>
       </c>
@@ -3167,7 +3180,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>175</v>
       </c>
@@ -3205,7 +3218,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>175</v>
       </c>
@@ -3246,7 +3259,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>175</v>
       </c>
@@ -3288,7 +3301,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>175</v>
       </c>
@@ -3329,7 +3342,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>175</v>
       </c>
@@ -3368,7 +3381,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>175</v>
       </c>
@@ -3403,7 +3416,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>175</v>
       </c>
@@ -3444,7 +3457,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>175</v>
       </c>
@@ -3482,7 +3495,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>175</v>
       </c>
@@ -3520,7 +3533,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>175</v>
       </c>
@@ -3555,7 +3568,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>175</v>
       </c>
@@ -3593,7 +3606,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>175</v>
       </c>
@@ -3631,7 +3644,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>175</v>
       </c>
@@ -3669,7 +3682,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>175</v>
       </c>
@@ -3704,7 +3717,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>175</v>
       </c>
@@ -3739,7 +3752,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>175</v>
       </c>
@@ -3777,7 +3790,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>175</v>
       </c>
@@ -3812,7 +3825,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>437</v>
       </c>
@@ -3841,7 +3854,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>437</v>
       </c>
@@ -3870,7 +3883,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>360</v>
       </c>
@@ -3902,7 +3915,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>362</v>
       </c>
@@ -3937,7 +3950,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>362</v>
       </c>
@@ -3972,7 +3985,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>362</v>
       </c>
@@ -4007,7 +4020,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>365</v>
       </c>
@@ -4030,7 +4043,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>365</v>
       </c>
@@ -4056,7 +4069,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>3</v>
       </c>
@@ -4073,7 +4086,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>3</v>
       </c>
@@ -4090,7 +4103,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>3</v>
       </c>
@@ -4107,7 +4120,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>3</v>
       </c>
@@ -4124,7 +4137,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4141,7 +4154,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -4158,7 +4171,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -4175,7 +4188,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
@@ -4192,7 +4205,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4209,7 +4222,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -4226,7 +4239,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -4243,7 +4256,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
@@ -4260,7 +4273,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -4277,7 +4290,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -4294,7 +4307,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -4311,7 +4324,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -4328,7 +4341,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -4345,7 +4358,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -4362,7 +4375,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -4379,7 +4392,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -4396,7 +4409,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -4413,7 +4426,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -4430,7 +4443,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -4447,7 +4460,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -4464,7 +4477,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -4481,7 +4494,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -4498,7 +4511,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -4515,7 +4528,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -4532,7 +4545,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -4549,7 +4562,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -4566,7 +4579,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -4583,7 +4596,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -4600,7 +4613,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -4617,7 +4630,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -4634,7 +4647,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4651,7 +4664,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
@@ -4668,7 +4681,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -4685,7 +4698,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -4702,7 +4715,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
@@ -4719,7 +4732,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
@@ -4736,7 +4749,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
@@ -4753,7 +4766,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
@@ -4770,7 +4783,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
@@ -4787,7 +4800,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
@@ -4804,7 +4817,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
@@ -4821,7 +4834,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
@@ -4838,7 +4851,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
@@ -4855,7 +4868,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
@@ -4872,7 +4885,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
@@ -4889,7 +4902,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
@@ -4906,7 +4919,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
@@ -4923,7 +4936,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
@@ -4940,7 +4953,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -4957,7 +4970,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>3</v>
       </c>
@@ -4974,7 +4987,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
@@ -4991,7 +5004,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>3</v>
       </c>
@@ -5008,7 +5021,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
@@ -5025,7 +5038,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
@@ -5042,7 +5055,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>3</v>
       </c>
@@ -5059,7 +5072,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>3</v>
       </c>
@@ -5076,7 +5089,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>3</v>
       </c>
@@ -5093,7 +5106,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>104</v>
       </c>
@@ -5110,7 +5123,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>97</v>
       </c>
@@ -5127,7 +5140,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>97</v>
       </c>
@@ -5144,7 +5157,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>97</v>
       </c>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C760ACE0-DD4D-4341-9AF9-FFDBA7C1EFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62012354-56D2-4CF3-A225-359CFBB8F0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -524,9 +524,6 @@
     <t>doi</t>
   </si>
   <si>
-    <t>markdown</t>
-  </si>
-  <si>
     <t>github</t>
   </si>
   <si>
@@ -1377,6 +1374,9 @@
   </si>
   <si>
     <t>https://doi.org/10.1080/19466315.2026.2637573</t>
+  </si>
+  <si>
+    <t>quarto</t>
   </si>
 </sst>
 </file>
@@ -1896,246 +1896,246 @@
         <v>161</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="T1" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B2" s="2">
         <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>442</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="T2" s="2"/>
     </row>
     <row r="3" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B3" s="2">
         <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="T3" s="2"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B4" s="2">
         <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="1:20" ht="20" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B5" s="2">
         <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D5" s="2">
         <v>2026</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>158</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="1:20" ht="40" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B6" s="2">
         <v>46</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D6" s="2">
         <v>2025</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H6" s="2">
         <v>47</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>411</v>
+      </c>
+      <c r="R6" s="5" t="s">
         <v>425</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>412</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>426</v>
       </c>
       <c r="T6" s="2"/>
     </row>
     <row r="7" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B7" s="2">
         <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D7" s="2">
         <v>2025</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H7" s="2">
         <v>44</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="T7" s="2"/>
     </row>
     <row r="8" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B8" s="2">
         <v>44</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D8" s="2">
         <v>2025</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H8" s="2">
         <v>34</v>
@@ -2144,34 +2144,34 @@
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="T8" s="2"/>
     </row>
     <row r="9" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B9" s="2">
         <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D9" s="2">
         <v>2025</v>
@@ -2183,7 +2183,7 @@
         <v>150</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H9" s="2">
         <v>67</v>
@@ -2192,42 +2192,42 @@
         <v>1</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B10" s="2">
         <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D10" s="2">
         <v>2025</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>150</v>
@@ -2242,73 +2242,73 @@
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="T10" s="2"/>
     </row>
     <row r="11" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B11" s="2">
         <v>41</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D11" s="2">
         <v>2024</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H11" s="2">
         <v>25</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K11" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O11" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="N11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="O11" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>389</v>
-      </c>
       <c r="R11" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T11" s="2"/>
     </row>
     <row r="12" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B12" s="2">
         <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D12" s="2">
         <v>2024</v>
@@ -2320,7 +2320,7 @@
         <v>150</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H12" s="2">
         <v>15</v>
@@ -2329,21 +2329,21 @@
         <v>1223858</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="2">
         <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D13" s="2">
         <v>2023</v>
@@ -2367,24 +2367,24 @@
         <v>160</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="M13" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B14" s="2">
         <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D14" s="2">
         <v>2023</v>
@@ -2405,39 +2405,39 @@
         <v>4</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K14" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="N14" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="R14" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="N14" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="T14" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B15" s="2">
         <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D15" s="2">
         <v>2023</v>
@@ -2458,21 +2458,21 @@
         <v>3</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B16" s="2">
         <v>36</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D16" s="2">
         <v>2023</v>
@@ -2496,18 +2496,18 @@
         <v>159</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B17" s="2">
         <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D17" s="2">
         <v>2022</v>
@@ -2519,7 +2519,7 @@
         <v>150</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H17" s="2">
         <v>112</v>
@@ -2528,21 +2528,21 @@
         <v>6</v>
       </c>
       <c r="J17" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B18" s="2">
         <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D18" s="2">
         <v>2022</v>
@@ -2554,7 +2554,7 @@
         <v>150</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H18" s="2">
         <v>41</v>
@@ -2563,24 +2563,24 @@
         <v>5</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K18" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B19" s="2">
         <v>33</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D19" s="2">
         <v>2022</v>
@@ -2592,27 +2592,27 @@
         <v>150</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H19" s="2">
         <v>21</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B20" s="2">
         <v>32</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D20" s="2">
         <v>2021</v>
@@ -2624,7 +2624,7 @@
         <v>150</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H20" s="2">
         <v>22</v>
@@ -2636,33 +2636,33 @@
         <v>420</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M20" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="R20" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B21" s="2">
         <v>31</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D21" s="2">
         <v>2021</v>
@@ -2674,7 +2674,7 @@
         <v>150</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H21" s="2">
         <v>75</v>
@@ -2683,30 +2683,30 @@
         <v>4</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K21" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B22" s="2">
         <v>30</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D22" s="2">
         <v>2021</v>
@@ -2718,33 +2718,33 @@
         <v>150</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H22" s="2">
         <v>20</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K22" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="M22" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B23" s="2">
         <v>29</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D23" s="2">
         <v>2021</v>
@@ -2756,30 +2756,30 @@
         <v>150</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H23" s="2">
         <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B24" s="2">
         <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D24" s="2">
         <v>2021</v>
@@ -2791,42 +2791,42 @@
         <v>150</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H24" s="2">
         <v>63</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M24" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="R24" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B25" s="2">
         <v>27</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D25" s="2">
         <v>2020</v>
@@ -2838,7 +2838,7 @@
         <v>150</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H25" s="2">
         <v>4</v>
@@ -2847,18 +2847,18 @@
         <v>68</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B26" s="2">
         <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D26" s="2">
         <v>2020</v>
@@ -2879,27 +2879,27 @@
         <v>4</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K26" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="L26" s="2" t="s">
-        <v>310</v>
-      </c>
       <c r="T26" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B27" s="2">
         <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D27" s="2">
         <v>2020</v>
@@ -2911,33 +2911,33 @@
         <v>150</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H27" s="2">
         <v>19</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K27" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="L27" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B28" s="2">
         <v>24</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D28" s="2">
         <v>2019</v>
@@ -2949,7 +2949,7 @@
         <v>150</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H28" s="2">
         <v>62</v>
@@ -2958,24 +2958,24 @@
         <v>3</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K28" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L28" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B29" s="2">
         <v>23</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D29" s="2">
         <v>2019</v>
@@ -2987,30 +2987,30 @@
         <v>150</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H29" s="2">
         <v>38</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B30" s="2">
         <v>22</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D30" s="2">
         <v>2019</v>
@@ -3022,30 +3022,30 @@
         <v>150</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H30" s="2">
         <v>18</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K30" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L30" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B31" s="2">
         <v>21</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D31" s="2">
         <v>2016</v>
@@ -3057,33 +3057,33 @@
         <v>150</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H31" s="2">
         <v>15</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K31" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="O31" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B32" s="2">
         <v>20</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D32" s="2">
         <v>2016</v>
@@ -3095,7 +3095,7 @@
         <v>150</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H32" s="2">
         <v>58</v>
@@ -3104,21 +3104,21 @@
         <v>6</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B33" s="2">
         <v>19</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D33" s="2">
         <v>2016</v>
@@ -3130,27 +3130,27 @@
         <v>150</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H33" s="2">
         <v>47</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B34" s="2">
         <v>18</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D34" s="2">
         <v>2016</v>
@@ -3162,7 +3162,7 @@
         <v>150</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H34" s="2">
         <v>26</v>
@@ -3171,24 +3171,24 @@
         <v>2</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B35" s="2">
         <v>17</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D35" s="2">
         <v>2014</v>
@@ -3200,33 +3200,33 @@
         <v>150</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H35" s="2">
         <v>8</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K35" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="O35" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B36" s="2">
         <v>16</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D36" s="2">
         <v>2013</v>
@@ -3238,7 +3238,7 @@
         <v>150</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H36" s="2">
         <v>75</v>
@@ -3247,39 +3247,39 @@
         <v>4</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K36" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="L36" s="2" t="s">
+      <c r="O36" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B37" s="2">
         <v>15</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D37" s="2">
         <v>2012</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H37" s="2">
         <v>8</v>
@@ -3292,36 +3292,36 @@
         <v>1-29</v>
       </c>
       <c r="K37" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="O37" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B38" s="2">
         <v>14</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D38" s="2">
         <v>2011</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H38" s="2">
         <v>53</v>
@@ -3330,39 +3330,39 @@
         <v>4</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K38" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="L38" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B39" s="2">
         <v>13</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D39" s="2">
         <v>2011</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H39" s="2">
         <v>39</v>
@@ -3375,33 +3375,33 @@
         <v>1-28</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B40" s="2">
         <v>12</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D40" s="2">
         <v>2010</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H40" s="2">
         <v>66</v>
@@ -3410,33 +3410,33 @@
         <v>4</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B41" s="2">
         <v>11</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D41" s="2">
         <v>2010</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H41" s="2">
         <v>22</v>
@@ -3445,39 +3445,39 @@
         <v>8</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K41" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L41" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="O41" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B42" s="2">
         <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D42" s="2">
         <v>2010</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H42" s="2">
         <v>19</v>
@@ -3486,74 +3486,74 @@
         <v>1</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K42" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="O42" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B43" s="2">
         <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D43" s="2">
         <v>2010</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H43" s="2">
         <v>54</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K43" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="O43" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B44" s="2">
         <v>8</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D44" s="2">
         <v>2009</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H44" s="2">
         <v>31</v>
@@ -3562,147 +3562,147 @@
         <v>1</v>
       </c>
       <c r="K44" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="O44" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B45" s="2">
         <v>7</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D45" s="2">
         <v>2009</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H45" s="2">
         <v>79</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K45" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="L45" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="L45" s="2" t="s">
+      <c r="O45" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B46" s="2">
         <v>6</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D46" s="2">
         <v>2009</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H46" s="2">
         <v>37</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K46" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="L46" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="L46" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="O46" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="2">
         <v>5</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D47" s="2">
         <v>2009</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H47" s="2">
         <v>15</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K47" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="L47" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="L47" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="O47" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B48" s="2">
         <v>4</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D48" s="2">
         <v>2008</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H48" s="2">
         <v>78</v>
@@ -3711,33 +3711,33 @@
         <v>12</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B49" s="2">
         <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D49" s="2">
         <v>2008</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H49" s="2">
         <v>78</v>
@@ -3746,33 +3746,33 @@
         <v>2</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B50" s="2">
         <v>2</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D50" s="2">
         <v>2007</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H50" s="2">
         <v>77</v>
@@ -3781,36 +3781,36 @@
         <v>7</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B51" s="2">
         <v>1</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D51" s="2">
         <v>2001</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H51" s="2">
         <v>2001</v>
@@ -3819,73 +3819,73 @@
         <v>1</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B52" s="2">
         <v>2</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D52" s="2">
         <v>2026</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B53" s="2">
         <v>1</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D53" s="2">
         <v>2026</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>433</v>
-      </c>
       <c r="J53" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="K53" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B54" s="2">
         <v>1</v>
@@ -3903,7 +3903,7 @@
         <v>150</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H54" s="2">
         <v>72</v>
@@ -3912,18 +3912,18 @@
         <v>5</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B55" s="2">
         <v>3</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D55" s="2">
         <v>2023</v>
@@ -3944,21 +3944,21 @@
         <v>1</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B56" s="2">
         <v>2</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D56" s="2">
         <v>2021</v>
@@ -3979,33 +3979,33 @@
         <v>4</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B57" s="2">
         <v>1</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D57" s="2">
         <v>2010</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="H57" s="2">
         <v>63</v>
@@ -4014,21 +4014,21 @@
         <v>8</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B58" s="2">
         <v>2</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D58" s="2">
         <v>2007</v>
@@ -4040,18 +4040,18 @@
         <v>149</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B59" s="2">
         <v>1</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D59" s="2">
         <v>2007</v>
@@ -4063,10 +4063,10 @@
         <v>149</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62012354-56D2-4CF3-A225-359CFBB8F0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E151056-3247-405C-9F0C-431414FACC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$S$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$S$125</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="449">
   <si>
     <t>Nr</t>
   </si>
@@ -1377,6 +1377,12 @@
   </si>
   <si>
     <t>quarto</t>
+  </si>
+  <si>
+    <t>Devenport, J., Mielke, T., Akacha, M., **Rufibach, K.**, Ocampo, A., Lanius, V., Vandemeulebroecke, M., Hougaard, P., Colin, P., Wright, D., Hummel, J\"urgen, Kunz, C.U., Krams, M.</t>
+  </si>
+  <si>
+    <t>Statistical Methodology Groups in the Pharmaceutical Industry</t>
   </si>
 </sst>
 </file>
@@ -1835,33 +1841,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T124"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T125"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="97.81640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.453125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="97.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="43" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="25.81640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="29.54296875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.54296875" style="1"/>
+    <col min="11" max="11" width="23.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="29.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1923,21 +1929,21 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B2" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>440</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -1947,21 +1953,21 @@
       </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B3" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>149</v>
@@ -1969,26 +1975,23 @@
       <c r="G3" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>429</v>
-      </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B4" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>418</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>149</v>
@@ -1996,454 +1999,428 @@
       <c r="G4" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="L4" s="4" t="s">
+        <v>429</v>
+      </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="B5" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2026</v>
+        <v>419</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>383</v>
+        <v>149</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>411</v>
+        <v>171</v>
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="40" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B6" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D6" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>150</v>
+        <v>383</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H6" s="2">
-        <v>47</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>423</v>
+        <v>158</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>445</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q6" t="s">
         <v>411</v>
       </c>
-      <c r="R6" s="5" t="s">
-        <v>425</v>
-      </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B7" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="D7" s="2">
         <v>2025</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H7" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>396</v>
+        <v>406</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>411</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>425</v>
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B8" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D8" s="2">
         <v>2025</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>413</v>
+        <v>233</v>
       </c>
       <c r="H8" s="2">
-        <v>34</v>
-      </c>
-      <c r="I8" s="2">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B9" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>168</v>
+        <v>393</v>
       </c>
       <c r="D9" s="2">
         <v>2025</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>147</v>
+        <v>392</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>245</v>
+        <v>413</v>
       </c>
       <c r="H9" s="2">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="I9" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="T9" s="2"/>
+    </row>
+    <row r="10" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B10" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>373</v>
+        <v>168</v>
       </c>
       <c r="D10" s="2">
         <v>2025</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>372</v>
+        <v>147</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>158</v>
+        <v>245</v>
       </c>
       <c r="H10" s="2">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="T10" s="2"/>
-    </row>
-    <row r="11" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B11" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="D11" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="H11" s="2">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>292</v>
+        <v>384</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B12" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>175</v>
+        <v>381</v>
       </c>
       <c r="D12" s="2">
         <v>2024</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>146</v>
+        <v>380</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>378</v>
+        <v>237</v>
       </c>
       <c r="H12" s="2">
-        <v>15</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1223858</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>377</v>
+        <v>25</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="T12" s="2"/>
+    </row>
+    <row r="13" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B13" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D13" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>154</v>
+        <v>378</v>
       </c>
       <c r="H13" s="2">
-        <v>22</v>
-      </c>
-      <c r="I13" s="2">
-        <v>4</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>173</v>
+        <v>15</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1223858</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>377</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B14" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="D14" s="2">
         <v>2023</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H14" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I14" s="2">
         <v>4</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>289</v>
+        <v>160</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>290</v>
+        <v>180</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B15" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="D15" s="2">
         <v>2023</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>150</v>
@@ -2455,30 +2432,48 @@
         <v>15</v>
       </c>
       <c r="I15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B16" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D16" s="2">
         <v>2023</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>150</v>
@@ -2490,267 +2485,264 @@
         <v>15</v>
       </c>
       <c r="I16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>159</v>
+        <v>370</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B17" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D17" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="H17" s="2">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="I17" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B18" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D18" s="2">
         <v>2022</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="H18" s="2">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="I18" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B19" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D19" s="2">
         <v>2022</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H19" s="2">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="I19" s="2">
+        <v>5</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B20" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D20" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H20" s="2">
-        <v>22</v>
-      </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2">
-        <v>420</v>
+        <v>21</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B21" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D21" s="2">
         <v>2021</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H21" s="2">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="I21" s="2">
-        <v>4</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>242</v>
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>420</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B22" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D22" s="2">
         <v>2021</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H22" s="2">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="I22" s="2">
+        <v>4</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B23" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D23" s="2">
         <v>2021</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>150</v>
@@ -2762,296 +2754,299 @@
         <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B24" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D24" s="2">
         <v>2021</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H24" s="2">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B25" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D25" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H25" s="2">
-        <v>4</v>
-      </c>
-      <c r="I25" s="2">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B26" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="D26" s="2">
         <v>2020</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>158</v>
+        <v>247</v>
       </c>
       <c r="H26" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I26" s="2">
-        <v>4</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>248</v>
+        <v>68</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B27" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="D27" s="2">
         <v>2020</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>235</v>
+        <v>158</v>
       </c>
       <c r="H27" s="2">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="I27" s="2">
+        <v>4</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B28" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D28" s="2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H28" s="2">
-        <v>62</v>
-      </c>
-      <c r="I28" s="2">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B29" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D29" s="2">
         <v>2019</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="H29" s="2">
-        <v>38</v>
+        <v>62</v>
+      </c>
+      <c r="I29" s="2">
+        <v>3</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B30" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D30" s="2">
         <v>2019</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H30" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B31" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D31" s="2">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>150</v>
@@ -3060,678 +3055,678 @@
         <v>235</v>
       </c>
       <c r="H31" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B32" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D32" s="2">
         <v>2016</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H32" s="2">
-        <v>58</v>
-      </c>
-      <c r="I32" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B33" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D33" s="2">
         <v>2016</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H33" s="2">
-        <v>47</v>
+        <v>58</v>
+      </c>
+      <c r="I33" s="2">
+        <v>6</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B34" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D34" s="2">
         <v>2016</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H34" s="2">
-        <v>26</v>
-      </c>
-      <c r="I34" s="2">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B35" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D35" s="2">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H35" s="2">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="I35" s="2">
+        <v>2</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B36" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D36" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H36" s="2">
-        <v>75</v>
-      </c>
-      <c r="I36" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B37" s="2">
+        <v>16</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2013</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H37" s="2">
+        <v>75</v>
+      </c>
+      <c r="I37" s="2">
+        <v>4</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38" s="2">
         <v>15</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D38" s="2">
         <v>2012</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G37" s="2" t="s">
+      <c r="F38" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H38" s="2">
         <v>8</v>
       </c>
-      <c r="I37" s="2">
+      <c r="I38" s="2">
         <v>1</v>
       </c>
-      <c r="J37" s="2" t="str">
+      <c r="J38" s="2" t="str">
         <f>"1-29"</f>
         <v>1-29</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="K38" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="L38" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="O37" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B38" s="2">
-        <v>14</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D38" s="2">
-        <v>2011</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="H38" s="2">
-        <v>53</v>
-      </c>
-      <c r="I38" s="2">
-        <v>4</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B39" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D39" s="2">
         <v>2011</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H39" s="2">
+        <v>53</v>
+      </c>
+      <c r="I39" s="2">
+        <v>4</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="2">
+        <v>13</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2011</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="F40" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H40" s="2">
         <v>39</v>
       </c>
-      <c r="I39" s="2">
+      <c r="I40" s="2">
         <v>6</v>
       </c>
-      <c r="J39" s="2" t="str">
+      <c r="J40" s="2" t="str">
         <f>"1-28"</f>
         <v>1-28</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="K40" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="O39" s="2" t="s">
+      <c r="O40" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B40" s="2">
-        <v>12</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D40" s="2">
-        <v>2010</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="H40" s="2">
-        <v>66</v>
-      </c>
-      <c r="I40" s="2">
-        <v>4</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B41" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D41" s="2">
         <v>2010</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H41" s="2">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I41" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B42" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D42" s="2">
         <v>2010</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H42" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I42" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>340</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B43" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D43" s="2">
         <v>2010</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H43" s="2">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="I43" s="2">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B44" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D44" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="H44" s="2">
-        <v>31</v>
-      </c>
-      <c r="I44" s="2">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B45" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D45" s="2">
         <v>2009</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="H45" s="2">
-        <v>79</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>275</v>
+        <v>31</v>
+      </c>
+      <c r="I45" s="2">
+        <v>1</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B46" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>288</v>
+        <v>211</v>
       </c>
       <c r="D46" s="2">
         <v>2009</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H46" s="2">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B47" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="D47" s="2">
         <v>2009</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H47" s="2">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B48" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D48" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H48" s="2">
-        <v>78</v>
-      </c>
-      <c r="I48" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B49" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D49" s="2">
         <v>2008</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>150</v>
@@ -3743,132 +3738,138 @@
         <v>78</v>
       </c>
       <c r="I49" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B50" s="2">
+        <v>3</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2008</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H50" s="2">
+        <v>78</v>
+      </c>
+      <c r="I50" s="2">
         <v>2</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D50" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="H50" s="2">
-        <v>77</v>
-      </c>
-      <c r="I50" s="2">
-        <v>7</v>
-      </c>
       <c r="J50" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="O50" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B51" s="2">
+        <v>2</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2007</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H51" s="2">
+        <v>77</v>
+      </c>
+      <c r="I51" s="2">
+        <v>7</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52" s="2">
         <v>1</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D52" s="2">
         <v>2001</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G51" s="2" t="s">
+      <c r="F52" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H52" s="2">
         <v>2001</v>
       </c>
-      <c r="I51" s="2">
+      <c r="I52" s="2">
         <v>1</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="J52" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="K52" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="B52" s="2">
-        <v>2</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="D52" s="2">
-        <v>2026</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>436</v>
       </c>
       <c r="B53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D53" s="2">
         <v>2026</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>150</v>
@@ -3877,94 +3878,88 @@
         <v>432</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>359</v>
+        <v>436</v>
       </c>
       <c r="B54" s="2">
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B55" s="2">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D55" s="2">
         <v>2010</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G54" s="2" t="s">
+      <c r="F55" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H55" s="2">
         <v>72</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I55" s="2">
         <v>5</v>
       </c>
-      <c r="J54" s="2" t="s">
+      <c r="J55" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B55" s="2">
-        <v>3</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D55" s="2">
-        <v>2023</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H55" s="2">
-        <v>15</v>
-      </c>
-      <c r="I55" s="2">
-        <v>1</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>361</v>
       </c>
       <c r="B56" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D56" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>150</v>
@@ -3973,681 +3968,699 @@
         <v>158</v>
       </c>
       <c r="H56" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I56" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>361</v>
       </c>
       <c r="B57" s="2">
+        <v>2</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2021</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H57" s="2">
+        <v>13</v>
+      </c>
+      <c r="I57" s="2">
+        <v>4</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B58" s="2">
         <v>1</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D58" s="2">
         <v>2010</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="F58" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H58" s="2">
         <v>63</v>
       </c>
-      <c r="I57" s="2">
+      <c r="I58" s="2">
         <v>8</v>
       </c>
-      <c r="J57" s="2" t="s">
+      <c r="J58" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="K57" s="2" t="s">
+      <c r="K58" s="2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B58" s="2">
-        <v>2</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D58" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>364</v>
       </c>
       <c r="B59" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>367</v>
+        <v>207</v>
       </c>
       <c r="D59" s="2">
         <v>2007</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G59" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B60" s="2">
+        <v>1</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D60" s="2">
+        <v>2007</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="K59" s="2" t="s">
+      <c r="K60" s="2" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B60" s="2">
+    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="2">
         <v>60</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B61" s="2">
+      <c r="F61" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="2">
         <v>59</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" s="2">
-        <v>58</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E62" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="2">
+        <v>58</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63" s="2">
+      <c r="F63" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="2">
         <v>57</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B64" s="2">
+      <c r="F64" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="2">
         <v>56</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="2">
+      <c r="F65" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="2">
         <v>55</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B66" s="2">
-        <v>54</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="2">
+        <v>54</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B67" s="2">
+      <c r="F67" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="2">
         <v>53</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B68" s="2">
+      <c r="F68" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="2">
         <v>52</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B69" s="2">
-        <v>51</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="2">
+        <v>51</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" s="2">
+      <c r="F70" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="2">
         <v>50</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" s="2">
+      <c r="F71" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="2">
         <v>49</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" s="2">
+      <c r="F72" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="2">
         <v>48</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B73" s="2">
+      <c r="F73" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="2">
         <v>47</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B74" s="2">
+      <c r="F74" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="2">
         <v>46</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="2">
+      <c r="F75" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="2">
         <v>45</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F75" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B76" s="2">
+      <c r="F76" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="2">
         <v>44</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C77" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B77" s="2">
+      <c r="F77" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="2">
         <v>43</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B78" s="2">
+      <c r="F78" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="2">
         <v>42</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B79" s="2">
+      <c r="F79" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="2">
         <v>41</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B80" s="2">
+      <c r="F80" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="2">
         <v>40</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B81" s="2">
+      <c r="F81" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="2">
         <v>39</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F81" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B82" s="2">
+      <c r="F82" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="2">
         <v>38</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B83" s="2">
+      <c r="F83" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="2">
         <v>37</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B84" s="2">
+      <c r="F84" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="2">
         <v>36</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F84" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B85" s="2">
+      <c r="F85" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="2">
         <v>35</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F85" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B86" s="2">
+      <c r="F86" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="2">
         <v>34</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F86" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B87" s="2">
+      <c r="F87" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="2">
         <v>33</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B88" s="2">
+      <c r="F88" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="2">
         <v>32</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B89" s="2">
+      <c r="F89" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="2">
         <v>31</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B90" s="2">
+      <c r="F90" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="2">
         <v>30</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B91" s="2">
+      <c r="F91" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="2">
         <v>29</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E92" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B92" s="2">
+      <c r="F92" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="2">
         <v>28</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E93" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F92" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B93" s="2">
-        <v>27</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="F93" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4655,539 +4668,556 @@
         <v>27</v>
       </c>
       <c r="C94" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" s="2">
+        <v>27</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E95" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B95" s="2">
+      <c r="F95" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="2">
         <v>26</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B96" s="2">
+      <c r="F96" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="2">
         <v>25</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C97" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E97" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F96" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B97" s="2">
+      <c r="F97" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="2">
         <v>24</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B98" s="2">
+      <c r="F98" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="2">
         <v>23</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E99" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F98" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B99" s="2">
+      <c r="F99" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="2">
         <v>22</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F99" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B100" s="2">
+      <c r="F100" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="2">
         <v>21</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E101" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F100" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B101" s="2">
+      <c r="F101" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="2">
         <v>20</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F101" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B102" s="2">
+      <c r="F102" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="2">
         <v>19</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F102" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B103" s="2">
+      <c r="F103" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="2">
         <v>18</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E104" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F103" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B104" s="2">
+      <c r="F104" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="2">
         <v>17</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F104" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B105" s="2">
+      <c r="F105" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="2">
         <v>16</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F105" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B106" s="2">
+      <c r="F106" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="2">
         <v>15</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B107" s="2">
+      <c r="F107" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="2">
         <v>14</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E108" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F107" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B108" s="2">
+      <c r="F108" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="2">
         <v>13</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F108" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B109" s="2">
+      <c r="F109" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B110" s="2">
         <v>12</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B110" s="2">
-        <v>11</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B111" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E111" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B112" s="2">
+        <v>10</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F111" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B112" s="2">
+      <c r="F112" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" s="2">
         <v>9</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E113" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F112" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B113" s="2">
+      <c r="F113" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B114" s="2">
         <v>8</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E114" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F113" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B114" s="2">
+      <c r="F114" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" s="2">
         <v>7</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F114" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B115" s="2">
+      <c r="F115" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" s="2">
         <v>6</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F115" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B116" s="2">
+      <c r="F116" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B117" s="2">
         <v>5</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F116" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B117" s="2">
+      <c r="F117" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" s="2">
         <v>4</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C118" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F117" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B118" s="2">
-        <v>3</v>
-      </c>
-      <c r="C118" s="1" t="s">
+      <c r="F118" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B119" s="2">
+        <v>3</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F118" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B119" s="2">
+      <c r="F119" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B120" s="2">
         <v>2</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C120" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F119" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B120" s="2">
-        <v>1</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="F120" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="B121" s="2">
         <v>1</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B122" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B123" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B124" s="2">
+        <v>2</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B125" s="2">
         <v>1</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C125" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="E125" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F124" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <hyperlinks>
-    <hyperlink ref="L21" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="L41" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="K44" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="L45" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="K13" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="O8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="M6" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
-    <hyperlink ref="Q8" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
-    <hyperlink ref="R6" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
-    <hyperlink ref="L3" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
-    <hyperlink ref="M9" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
+    <hyperlink ref="L22" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L42" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K45" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="L46" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M7" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
+    <hyperlink ref="Q9" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
+    <hyperlink ref="R7" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
+    <hyperlink ref="L4" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
+    <hyperlink ref="M10" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId12"/>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E151056-3247-405C-9F0C-431414FACC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829B63E2-8214-4B04-AD99-00864EBC6A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="454">
   <si>
     <t>Nr</t>
   </si>
@@ -1379,10 +1379,25 @@
     <t>quarto</t>
   </si>
   <si>
-    <t>Devenport, J., Mielke, T., Akacha, M., **Rufibach, K.**, Ocampo, A., Lanius, V., Vandemeulebroecke, M., Hougaard, P., Colin, P., Wright, D., Hummel, J\"urgen, Kunz, C.U., Krams, M.</t>
-  </si>
-  <si>
     <t>Statistical Methodology Groups in the Pharmaceutical Industry</t>
+  </si>
+  <si>
+    <t>Devenport, J., Mielke, T., Akacha, M., **Rufibach, K.**, Ocampo, A., Lanius, V., Vandemeulebroecke, M., Hougaard, P., Colin, P., Wright, D., Hummel, Jürgen, Kunz, C.U., Krams, M.</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2603.11240</t>
+  </si>
+  <si>
+    <t>https://arxim.org/abs/2603.11240</t>
+  </si>
+  <si>
+    <t>httpp://arxis.org/abp/2603.11240</t>
+  </si>
+  <si>
+    <t>httpp://arxif.org/abp/2603.11240</t>
+  </si>
+  <si>
+    <t>httpp://arxid.org/abp/2603.11240</t>
   </si>
 </sst>
 </file>
@@ -1842,32 +1857,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T125"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="97.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="97.81640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="43" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="25.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="29.5703125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.5703125" style="1"/>
+    <col min="11" max="11" width="23.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="25.81640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="29.54296875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1929,7 +1944,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>369</v>
       </c>
@@ -1937,13 +1952,13 @@
         <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>440</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -1951,9 +1966,13 @@
       <c r="G2" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="K2" s="3"/>
+      <c r="L2" s="4" t="s">
+        <v>449</v>
+      </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>369</v>
       </c>
@@ -1977,7 +1996,7 @@
       </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>369</v>
       </c>
@@ -2004,7 +2023,7 @@
       </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>369</v>
       </c>
@@ -2028,7 +2047,7 @@
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="20" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>174</v>
       </c>
@@ -2061,7 +2080,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="45" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" ht="40" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>174</v>
       </c>
@@ -2109,7 +2128,7 @@
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>174</v>
       </c>
@@ -2145,7 +2164,7 @@
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>174</v>
       </c>
@@ -2193,7 +2212,7 @@
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
@@ -2243,7 +2262,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
@@ -2282,7 +2301,7 @@
       </c>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -2330,7 +2349,7 @@
       </c>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
@@ -2365,7 +2384,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>174</v>
       </c>
@@ -2406,7 +2425,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
@@ -2459,7 +2478,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>174</v>
       </c>
@@ -2494,7 +2513,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
@@ -2529,7 +2548,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>174</v>
       </c>
@@ -2564,7 +2583,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
@@ -2602,7 +2621,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>174</v>
       </c>
@@ -2634,7 +2653,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>174</v>
       </c>
@@ -2684,7 +2703,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>174</v>
       </c>
@@ -2728,7 +2747,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>174</v>
       </c>
@@ -2766,7 +2785,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
@@ -2801,7 +2820,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>174</v>
       </c>
@@ -2848,7 +2867,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>174</v>
       </c>
@@ -2880,7 +2899,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>174</v>
       </c>
@@ -2921,7 +2940,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>174</v>
       </c>
@@ -2959,7 +2978,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>174</v>
       </c>
@@ -2997,7 +3016,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>174</v>
       </c>
@@ -3032,7 +3051,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>174</v>
       </c>
@@ -3067,7 +3086,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>174</v>
       </c>
@@ -3105,7 +3124,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>174</v>
       </c>
@@ -3140,7 +3159,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>174</v>
       </c>
@@ -3172,7 +3191,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>174</v>
       </c>
@@ -3210,7 +3229,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>174</v>
       </c>
@@ -3248,7 +3267,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>174</v>
       </c>
@@ -3289,7 +3308,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>174</v>
       </c>
@@ -3331,7 +3350,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>174</v>
       </c>
@@ -3372,7 +3391,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>174</v>
       </c>
@@ -3411,7 +3430,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>174</v>
       </c>
@@ -3446,7 +3465,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>174</v>
       </c>
@@ -3487,7 +3506,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>174</v>
       </c>
@@ -3525,7 +3544,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
@@ -3563,7 +3582,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>174</v>
       </c>
@@ -3598,7 +3617,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>174</v>
       </c>
@@ -3636,7 +3655,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>174</v>
       </c>
@@ -3674,7 +3693,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>174</v>
       </c>
@@ -3712,7 +3731,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>174</v>
       </c>
@@ -3747,7 +3766,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>174</v>
       </c>
@@ -3782,7 +3801,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>174</v>
       </c>
@@ -3820,7 +3839,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>174</v>
       </c>
@@ -3855,7 +3874,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>436</v>
       </c>
@@ -3884,7 +3903,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>436</v>
       </c>
@@ -3913,7 +3932,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>359</v>
       </c>
@@ -3945,7 +3964,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>361</v>
       </c>
@@ -3980,7 +3999,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>361</v>
       </c>
@@ -4015,7 +4034,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>361</v>
       </c>
@@ -4050,7 +4069,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>364</v>
       </c>
@@ -4073,7 +4092,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>364</v>
       </c>
@@ -4099,7 +4118,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>3</v>
       </c>
@@ -4116,7 +4135,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>3</v>
       </c>
@@ -4133,7 +4152,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>3</v>
       </c>
@@ -4150,7 +4169,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4167,7 +4186,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -4184,7 +4203,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -4201,7 +4220,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
@@ -4218,7 +4237,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4235,7 +4254,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -4252,7 +4271,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -4269,7 +4288,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
@@ -4286,7 +4305,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -4303,7 +4322,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -4320,7 +4339,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -4337,7 +4356,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -4354,7 +4373,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -4371,7 +4390,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -4388,7 +4407,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -4405,7 +4424,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -4422,7 +4441,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -4439,7 +4458,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -4456,7 +4475,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -4473,7 +4492,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -4490,7 +4509,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -4507,7 +4526,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -4524,7 +4543,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -4541,7 +4560,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -4558,7 +4577,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -4575,7 +4594,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -4592,7 +4611,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -4609,7 +4628,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -4626,7 +4645,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -4643,7 +4662,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -4660,7 +4679,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4677,7 +4696,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
@@ -4694,7 +4713,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -4711,7 +4730,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -4728,7 +4747,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
@@ -4745,7 +4764,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
@@ -4762,7 +4781,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
@@ -4779,7 +4798,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
@@ -4796,7 +4815,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
@@ -4813,7 +4832,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
@@ -4830,7 +4849,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
@@ -4847,7 +4866,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
@@ -4864,7 +4883,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
@@ -4881,7 +4900,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
@@ -4898,7 +4917,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
@@ -4915,7 +4934,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
@@ -4932,7 +4951,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
@@ -4949,7 +4968,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
@@ -4966,7 +4985,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -4983,7 +5002,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>3</v>
       </c>
@@ -5000,7 +5019,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
@@ -5017,7 +5036,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>3</v>
       </c>
@@ -5034,7 +5053,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
@@ -5051,7 +5070,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
@@ -5068,7 +5087,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>3</v>
       </c>
@@ -5085,7 +5104,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>3</v>
       </c>
@@ -5102,7 +5121,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>3</v>
       </c>
@@ -5119,7 +5138,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>3</v>
       </c>
@@ -5136,7 +5155,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>104</v>
       </c>
@@ -5153,7 +5172,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>97</v>
       </c>
@@ -5170,7 +5189,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>97</v>
       </c>
@@ -5187,7 +5206,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>97</v>
       </c>
@@ -5218,9 +5237,10 @@
     <hyperlink ref="R7" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
     <hyperlink ref="L4" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
     <hyperlink ref="M10" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
+    <hyperlink ref="L2" r:id="rId12" xr:uid="{28D0DE1C-48A6-42F2-8E88-DAC27E2438A1}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId12"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId13"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829B63E2-8214-4B04-AD99-00864EBC6A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885D7DEC-E8DD-4A1F-8238-7EAC62A7515C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="451">
   <si>
     <t>Nr</t>
   </si>
@@ -1388,16 +1388,7 @@
     <t>https://arxiv.org/abs/2603.11240</t>
   </si>
   <si>
-    <t>https://arxim.org/abs/2603.11240</t>
-  </si>
-  <si>
-    <t>httpp://arxis.org/abp/2603.11240</t>
-  </si>
-  <si>
-    <t>httpp://arxif.org/abp/2603.11240</t>
-  </si>
-  <si>
-    <t>httpp://arxid.org/abp/2603.11240</t>
+    <t>https://www.linkedin.com/posts/jenny-devenport-b1773b13_efspi-innovation-activity-7439183387484901376-ENnn?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
@@ -1857,32 +1848,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T125"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="97.81640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.453125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="97.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="43" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="25.81640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="29.54296875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.54296875" style="1"/>
+    <col min="11" max="11" width="23.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="29.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1944,7 +1935,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>369</v>
       </c>
@@ -1952,13 +1943,13 @@
         <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>440</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -1966,13 +1957,9 @@
       <c r="G2" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="4" t="s">
-        <v>449</v>
-      </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>369</v>
       </c>
@@ -1980,13 +1967,13 @@
         <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>149</v>
@@ -1994,9 +1981,12 @@
       <c r="G3" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="L3" s="4" t="s">
+        <v>429</v>
+      </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>369</v>
       </c>
@@ -2004,13 +1994,13 @@
         <v>49</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>418</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>149</v>
@@ -2018,36 +2008,40 @@
       <c r="G4" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>429</v>
-      </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="90" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>369</v>
+        <v>174</v>
       </c>
       <c r="B5" s="2">
         <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>419</v>
+        <v>448</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>149</v>
+        <v>383</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>171</v>
+        <v>158</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>174</v>
       </c>
@@ -2080,7 +2074,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="40" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>174</v>
       </c>
@@ -2128,7 +2122,7 @@
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>174</v>
       </c>
@@ -2164,7 +2158,7 @@
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>174</v>
       </c>
@@ -2212,7 +2206,7 @@
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
@@ -2262,7 +2256,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
@@ -2301,7 +2295,7 @@
       </c>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -2349,7 +2343,7 @@
       </c>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
@@ -2384,7 +2378,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>174</v>
       </c>
@@ -2425,7 +2419,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
@@ -2478,7 +2472,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>174</v>
       </c>
@@ -2513,7 +2507,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
@@ -2548,7 +2542,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>174</v>
       </c>
@@ -2583,7 +2577,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
@@ -2621,7 +2615,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>174</v>
       </c>
@@ -2653,7 +2647,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>174</v>
       </c>
@@ -2703,7 +2697,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>174</v>
       </c>
@@ -2747,7 +2741,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>174</v>
       </c>
@@ -2785,7 +2779,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
@@ -2820,7 +2814,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>174</v>
       </c>
@@ -2867,7 +2861,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>174</v>
       </c>
@@ -2899,7 +2893,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>174</v>
       </c>
@@ -2940,7 +2934,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>174</v>
       </c>
@@ -2978,7 +2972,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>174</v>
       </c>
@@ -3016,7 +3010,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>174</v>
       </c>
@@ -3051,7 +3045,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>174</v>
       </c>
@@ -3086,7 +3080,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>174</v>
       </c>
@@ -3124,7 +3118,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>174</v>
       </c>
@@ -3159,7 +3153,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>174</v>
       </c>
@@ -3191,7 +3185,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>174</v>
       </c>
@@ -3229,7 +3223,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>174</v>
       </c>
@@ -3267,7 +3261,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>174</v>
       </c>
@@ -3308,7 +3302,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>174</v>
       </c>
@@ -3350,7 +3344,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>174</v>
       </c>
@@ -3391,7 +3385,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>174</v>
       </c>
@@ -3430,7 +3424,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>174</v>
       </c>
@@ -3465,7 +3459,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>174</v>
       </c>
@@ -3506,7 +3500,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>174</v>
       </c>
@@ -3544,7 +3538,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
@@ -3582,7 +3576,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>174</v>
       </c>
@@ -3617,7 +3611,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>174</v>
       </c>
@@ -3655,7 +3649,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>174</v>
       </c>
@@ -3693,7 +3687,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>174</v>
       </c>
@@ -3731,7 +3725,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>174</v>
       </c>
@@ -3766,7 +3760,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>174</v>
       </c>
@@ -3801,7 +3795,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>174</v>
       </c>
@@ -3839,7 +3833,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>174</v>
       </c>
@@ -3874,7 +3868,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>436</v>
       </c>
@@ -3903,7 +3897,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>436</v>
       </c>
@@ -3932,7 +3926,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>359</v>
       </c>
@@ -3964,7 +3958,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>361</v>
       </c>
@@ -3999,7 +3993,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>361</v>
       </c>
@@ -4034,7 +4028,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>361</v>
       </c>
@@ -4069,7 +4063,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>364</v>
       </c>
@@ -4092,7 +4086,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>364</v>
       </c>
@@ -4118,7 +4112,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>3</v>
       </c>
@@ -4135,7 +4129,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>3</v>
       </c>
@@ -4152,7 +4146,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>3</v>
       </c>
@@ -4169,7 +4163,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4186,7 +4180,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -4203,7 +4197,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -4220,7 +4214,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
@@ -4237,7 +4231,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4254,7 +4248,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -4271,7 +4265,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -4288,7 +4282,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
@@ -4305,7 +4299,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -4322,7 +4316,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -4339,7 +4333,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -4356,7 +4350,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -4373,7 +4367,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -4390,7 +4384,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -4407,7 +4401,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -4424,7 +4418,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -4441,7 +4435,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -4458,7 +4452,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -4475,7 +4469,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -4492,7 +4486,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -4509,7 +4503,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -4526,7 +4520,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -4543,7 +4537,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -4560,7 +4554,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -4577,7 +4571,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -4594,7 +4588,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -4611,7 +4605,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -4628,7 +4622,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -4645,7 +4639,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -4662,7 +4656,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -4679,7 +4673,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4696,7 +4690,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
@@ -4713,7 +4707,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -4730,7 +4724,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -4747,7 +4741,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
@@ -4764,7 +4758,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
@@ -4781,7 +4775,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
@@ -4798,7 +4792,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
@@ -4815,7 +4809,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
@@ -4832,7 +4826,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
@@ -4849,7 +4843,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
@@ -4866,7 +4860,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
@@ -4883,7 +4877,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
@@ -4900,7 +4894,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
@@ -4917,7 +4911,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
@@ -4934,7 +4928,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
@@ -4951,7 +4945,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
@@ -4968,7 +4962,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
@@ -4985,7 +4979,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -5002,7 +4996,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>3</v>
       </c>
@@ -5019,7 +5013,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
@@ -5036,7 +5030,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>3</v>
       </c>
@@ -5053,7 +5047,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
@@ -5070,7 +5064,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
@@ -5087,7 +5081,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>3</v>
       </c>
@@ -5104,7 +5098,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>3</v>
       </c>
@@ -5121,7 +5115,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>3</v>
       </c>
@@ -5138,7 +5132,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>3</v>
       </c>
@@ -5155,7 +5149,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>104</v>
       </c>
@@ -5172,7 +5166,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>97</v>
       </c>
@@ -5189,7 +5183,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>97</v>
       </c>
@@ -5206,7 +5200,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>97</v>
       </c>
@@ -5235,9 +5229,9 @@
     <hyperlink ref="M7" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
     <hyperlink ref="Q9" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
     <hyperlink ref="R7" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
-    <hyperlink ref="L4" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
+    <hyperlink ref="L3" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
     <hyperlink ref="M10" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
-    <hyperlink ref="L2" r:id="rId12" xr:uid="{28D0DE1C-48A6-42F2-8E88-DAC27E2438A1}"/>
+    <hyperlink ref="L5" r:id="rId12" xr:uid="{28D0DE1C-48A6-42F2-8E88-DAC27E2438A1}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId13"/>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885D7DEC-E8DD-4A1F-8238-7EAC62A7515C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D1C9DC-0863-417B-930B-B437AE0F5887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$S$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$S$126</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="455">
   <si>
     <t>Nr</t>
   </si>
@@ -1389,6 +1389,18 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/jenny-devenport-b1773b13_efspi-innovation-activity-7439183387484901376-ENnn?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Communicating results in trials with multiple hypotheses or adaptive design features</t>
+  </si>
+  <si>
+    <t>Asikanius, E., Wolbers, M., Akacha, M., Brandt, A., Hofner, B., Häring, D.A., Roes, K.C.B., Vandemeulebroecke, M., Wright, D., Zinserling, J., **Rufibach, K.**</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2605.03554</t>
+  </si>
+  <si>
+    <t>https://oncoestimand.github.io/complex_designs_communication/complex_designs_communication.html</t>
   </si>
 </sst>
 </file>
@@ -1847,7 +1859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T125"/>
+  <dimension ref="A1:T126"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1935,21 +1947,21 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B2" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>440</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -1957,23 +1969,29 @@
       <c r="G2" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="L2" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B3" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>149</v>
@@ -1981,26 +1999,23 @@
       <c r="G3" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>429</v>
-      </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B4" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>418</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>149</v>
@@ -2008,54 +2023,50 @@
       <c r="G4" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="L4" s="4" t="s">
+        <v>429</v>
+      </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="90" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="B5" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>448</v>
+        <v>419</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>383</v>
+        <v>149</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>450</v>
+        <v>171</v>
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="90" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B6" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2026</v>
+        <v>448</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>440</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>383</v>
@@ -2063,430 +2074,408 @@
       <c r="G6" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>411</v>
+      <c r="K6" s="3"/>
+      <c r="L6" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="45" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B7" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D7" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>150</v>
+        <v>383</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H7" s="2">
-        <v>47</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>423</v>
+        <v>158</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>445</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q7" t="s">
         <v>411</v>
       </c>
-      <c r="R7" s="5" t="s">
-        <v>425</v>
-      </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B8" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="D8" s="2">
         <v>2025</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H8" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>396</v>
+        <v>406</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>411</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>425</v>
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B9" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D9" s="2">
         <v>2025</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>413</v>
+        <v>233</v>
       </c>
       <c r="H9" s="2">
-        <v>34</v>
-      </c>
-      <c r="I9" s="2">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B10" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>168</v>
+        <v>393</v>
       </c>
       <c r="D10" s="2">
         <v>2025</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>147</v>
+        <v>392</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>245</v>
+        <v>413</v>
       </c>
       <c r="H10" s="2">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="I10" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="T10" s="2"/>
+    </row>
+    <row r="11" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B11" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>373</v>
+        <v>168</v>
       </c>
       <c r="D11" s="2">
         <v>2025</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>372</v>
+        <v>147</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>158</v>
+        <v>245</v>
       </c>
       <c r="H11" s="2">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="T11" s="2"/>
-    </row>
-    <row r="12" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B12" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="D12" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="H12" s="2">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>292</v>
+        <v>384</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B13" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>175</v>
+        <v>381</v>
       </c>
       <c r="D13" s="2">
         <v>2024</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>146</v>
+        <v>380</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>378</v>
+        <v>237</v>
       </c>
       <c r="H13" s="2">
-        <v>15</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1223858</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>377</v>
+        <v>25</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+        <v>382</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="T13" s="2"/>
+    </row>
+    <row r="14" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B14" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D14" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>154</v>
+        <v>378</v>
       </c>
       <c r="H14" s="2">
-        <v>22</v>
-      </c>
-      <c r="I14" s="2">
-        <v>4</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>173</v>
+        <v>15</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1223858</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>377</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B15" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="D15" s="2">
         <v>2023</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H15" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I15" s="2">
         <v>4</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>289</v>
+        <v>160</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>290</v>
+        <v>180</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B16" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="D16" s="2">
         <v>2023</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>150</v>
@@ -2498,30 +2487,48 @@
         <v>15</v>
       </c>
       <c r="I16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+        <v>289</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B17" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D17" s="2">
         <v>2023</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>150</v>
@@ -2533,118 +2540,121 @@
         <v>15</v>
       </c>
       <c r="I17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>159</v>
+        <v>370</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B18" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D18" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="H18" s="2">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="I18" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B19" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D19" s="2">
         <v>2022</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="H19" s="2">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="I19" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B20" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D20" s="2">
         <v>2022</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H20" s="2">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="I20" s="2">
+        <v>5</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
@@ -2652,148 +2662,142 @@
         <v>174</v>
       </c>
       <c r="B21" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D21" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H21" s="2">
-        <v>22</v>
-      </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2">
-        <v>420</v>
+        <v>21</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B22" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D22" s="2">
         <v>2021</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H22" s="2">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="I22" s="2">
-        <v>4</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>242</v>
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>420</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+        <v>387</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B23" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D23" s="2">
         <v>2021</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H23" s="2">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="I23" s="2">
+        <v>4</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B24" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D24" s="2">
         <v>2021</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>150</v>
@@ -2805,92 +2809,98 @@
         <v>20</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B25" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D25" s="2">
         <v>2021</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H25" s="2">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B26" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D26" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H26" s="2">
-        <v>4</v>
-      </c>
-      <c r="I26" s="2">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
@@ -2898,116 +2908,110 @@
         <v>174</v>
       </c>
       <c r="B27" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="D27" s="2">
         <v>2020</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>158</v>
+        <v>247</v>
       </c>
       <c r="H27" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I27" s="2">
-        <v>4</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>248</v>
+        <v>68</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B28" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="D28" s="2">
         <v>2020</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>235</v>
+        <v>158</v>
       </c>
       <c r="H28" s="2">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="I28" s="2">
+        <v>4</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>309</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B29" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D29" s="2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H29" s="2">
-        <v>62</v>
-      </c>
-      <c r="I29" s="2">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
@@ -3015,34 +3019,37 @@
         <v>174</v>
       </c>
       <c r="B30" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D30" s="2">
         <v>2019</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="H30" s="2">
-        <v>38</v>
+        <v>62</v>
+      </c>
+      <c r="I30" s="2">
+        <v>3</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
@@ -3050,34 +3057,34 @@
         <v>174</v>
       </c>
       <c r="B31" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D31" s="2">
         <v>2019</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H31" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
@@ -3085,16 +3092,16 @@
         <v>174</v>
       </c>
       <c r="B32" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D32" s="2">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>150</v>
@@ -3103,19 +3110,16 @@
         <v>235</v>
       </c>
       <c r="H32" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3123,34 +3127,37 @@
         <v>174</v>
       </c>
       <c r="B33" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D33" s="2">
         <v>2016</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H33" s="2">
-        <v>58</v>
-      </c>
-      <c r="I33" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3158,31 +3165,34 @@
         <v>174</v>
       </c>
       <c r="B34" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D34" s="2">
         <v>2016</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H34" s="2">
-        <v>47</v>
+        <v>58</v>
+      </c>
+      <c r="I34" s="2">
+        <v>6</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3190,37 +3200,31 @@
         <v>174</v>
       </c>
       <c r="B35" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D35" s="2">
         <v>2016</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H35" s="2">
-        <v>26</v>
-      </c>
-      <c r="I35" s="2">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3228,37 +3232,37 @@
         <v>174</v>
       </c>
       <c r="B36" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D36" s="2">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H36" s="2">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="I36" s="2">
+        <v>2</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3266,40 +3270,37 @@
         <v>174</v>
       </c>
       <c r="B37" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D37" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H37" s="2">
-        <v>75</v>
-      </c>
-      <c r="I37" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3307,41 +3308,40 @@
         <v>174</v>
       </c>
       <c r="B38" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D38" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H38" s="2">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="I38" s="2">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="str">
-        <f>"1-29"</f>
-        <v>1-29</v>
+        <v>4</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3349,40 +3349,41 @@
         <v>174</v>
       </c>
       <c r="B39" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D39" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="H39" s="2">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="I39" s="2">
-        <v>4</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>264</v>
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="str">
+        <f>"1-29"</f>
+        <v>1-29</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3390,38 +3391,40 @@
         <v>174</v>
       </c>
       <c r="B40" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D40" s="2">
         <v>2011</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="H40" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="I40" s="2">
-        <v>6</v>
-      </c>
-      <c r="J40" s="2" t="str">
-        <f>"1-28"</f>
-        <v>1-28</v>
+        <v>4</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3429,34 +3432,38 @@
         <v>174</v>
       </c>
       <c r="B41" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D41" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H41" s="2">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="I41" s="2">
-        <v>4</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>267</v>
+        <v>6</v>
+      </c>
+      <c r="J41" s="2" t="str">
+        <f>"1-28"</f>
+        <v>1-28</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3464,40 +3471,34 @@
         <v>174</v>
       </c>
       <c r="B42" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D42" s="2">
         <v>2010</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H42" s="2">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I42" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3505,37 +3506,40 @@
         <v>174</v>
       </c>
       <c r="B43" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D43" s="2">
         <v>2010</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H43" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I43" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>340</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3543,37 +3547,37 @@
         <v>174</v>
       </c>
       <c r="B44" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D44" s="2">
         <v>2010</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H44" s="2">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="I44" s="2">
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3581,34 +3585,37 @@
         <v>174</v>
       </c>
       <c r="B45" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D45" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="H45" s="2">
-        <v>31</v>
-      </c>
-      <c r="I45" s="2">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3616,37 +3623,34 @@
         <v>174</v>
       </c>
       <c r="B46" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D46" s="2">
         <v>2009</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="H46" s="2">
-        <v>79</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>275</v>
+        <v>31</v>
+      </c>
+      <c r="I46" s="2">
+        <v>1</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3654,37 +3658,37 @@
         <v>174</v>
       </c>
       <c r="B47" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>288</v>
+        <v>211</v>
       </c>
       <c r="D47" s="2">
         <v>2009</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H47" s="2">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3692,34 +3696,34 @@
         <v>174</v>
       </c>
       <c r="B48" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="D48" s="2">
         <v>2009</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H48" s="2">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>333</v>
@@ -3730,34 +3734,37 @@
         <v>174</v>
       </c>
       <c r="B49" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D49" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H49" s="2">
-        <v>78</v>
-      </c>
-      <c r="I49" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3765,16 +3772,16 @@
         <v>174</v>
       </c>
       <c r="B50" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D50" s="2">
         <v>2008</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>150</v>
@@ -3786,13 +3793,13 @@
         <v>78</v>
       </c>
       <c r="I50" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3800,101 +3807,107 @@
         <v>174</v>
       </c>
       <c r="B51" s="2">
+        <v>3</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2008</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H51" s="2">
+        <v>78</v>
+      </c>
+      <c r="I51" s="2">
         <v>2</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D51" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="H51" s="2">
-        <v>77</v>
-      </c>
-      <c r="I51" s="2">
-        <v>7</v>
-      </c>
       <c r="J51" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="O51" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B52" s="2">
+        <v>2</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2007</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H52" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" s="2">
+        <v>7</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53" s="2">
         <v>1</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D53" s="2">
         <v>2001</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G52" s="2" t="s">
+      <c r="F53" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H53" s="2">
         <v>2001</v>
       </c>
-      <c r="I52" s="2">
+      <c r="I53" s="2">
         <v>1</v>
       </c>
-      <c r="J52" s="2" t="s">
+      <c r="J53" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="K53" s="2" t="s">
         <v>368</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="B53" s="2">
-        <v>2</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="D53" s="2">
-        <v>2026</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3902,16 +3915,16 @@
         <v>436</v>
       </c>
       <c r="B54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D54" s="2">
         <v>2026</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>150</v>
@@ -3920,77 +3933,71 @@
         <v>432</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>359</v>
+        <v>436</v>
       </c>
       <c r="B55" s="2">
         <v>1</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D55" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B56" s="2">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D56" s="2">
         <v>2010</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G55" s="2" t="s">
+      <c r="F56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H56" s="2">
         <v>72</v>
       </c>
-      <c r="I55" s="2">
+      <c r="I56" s="2">
         <v>5</v>
       </c>
-      <c r="J55" s="2" t="s">
+      <c r="J56" s="2" t="s">
         <v>360</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B56" s="2">
-        <v>3</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D56" s="2">
-        <v>2023</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H56" s="2">
-        <v>15</v>
-      </c>
-      <c r="I56" s="2">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3998,16 +4005,16 @@
         <v>361</v>
       </c>
       <c r="B57" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D57" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>150</v>
@@ -4016,16 +4023,16 @@
         <v>158</v>
       </c>
       <c r="H57" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I57" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -4033,57 +4040,69 @@
         <v>361</v>
       </c>
       <c r="B58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>199</v>
+        <v>376</v>
       </c>
       <c r="D58" s="2">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>398</v>
+        <v>139</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>399</v>
+        <v>158</v>
       </c>
       <c r="H58" s="2">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="I58" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D59" s="2">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>112</v>
+        <v>398</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>365</v>
+        <v>399</v>
+      </c>
+      <c r="H59" s="2">
+        <v>63</v>
+      </c>
+      <c r="I59" s="2">
+        <v>8</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -4091,42 +4110,48 @@
         <v>364</v>
       </c>
       <c r="B60" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>367</v>
+        <v>207</v>
       </c>
       <c r="D60" s="2">
         <v>2007</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>401</v>
+        <v>365</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>3</v>
+        <v>364</v>
       </c>
       <c r="B61" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>136</v>
+        <v>367</v>
+      </c>
+      <c r="D61" s="2">
+        <v>2007</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -4134,13 +4159,13 @@
         <v>3</v>
       </c>
       <c r="B62" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>4</v>
+        <v>136</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>150</v>
@@ -4151,47 +4176,47 @@
         <v>3</v>
       </c>
       <c r="B63" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E63" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="2">
+        <v>58</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B64" s="2">
+      <c r="F64" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="2">
         <v>57</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="2">
-        <v>56</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>150</v>
@@ -4202,13 +4227,13 @@
         <v>3</v>
       </c>
       <c r="B66" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>150</v>
@@ -4219,13 +4244,13 @@
         <v>3</v>
       </c>
       <c r="B67" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>150</v>
@@ -4236,13 +4261,13 @@
         <v>3</v>
       </c>
       <c r="B68" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>150</v>
@@ -4253,13 +4278,13 @@
         <v>3</v>
       </c>
       <c r="B69" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>150</v>
@@ -4270,47 +4295,47 @@
         <v>3</v>
       </c>
       <c r="B70" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="2">
+        <v>51</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" s="2">
+      <c r="F71" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="2">
         <v>50</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" s="2">
-        <v>49</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>150</v>
@@ -4321,47 +4346,47 @@
         <v>3</v>
       </c>
       <c r="B73" s="2">
+        <v>49</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="2">
         <v>48</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B74" s="2">
+      <c r="F74" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="2">
         <v>47</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="2">
-        <v>46</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>150</v>
@@ -4372,13 +4397,13 @@
         <v>3</v>
       </c>
       <c r="B76" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>150</v>
@@ -4389,13 +4414,13 @@
         <v>3</v>
       </c>
       <c r="B77" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>150</v>
@@ -4406,13 +4431,13 @@
         <v>3</v>
       </c>
       <c r="B78" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>150</v>
@@ -4423,13 +4448,13 @@
         <v>3</v>
       </c>
       <c r="B79" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>150</v>
@@ -4440,13 +4465,13 @@
         <v>3</v>
       </c>
       <c r="B80" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>150</v>
@@ -4457,13 +4482,13 @@
         <v>3</v>
       </c>
       <c r="B81" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>150</v>
@@ -4474,13 +4499,13 @@
         <v>3</v>
       </c>
       <c r="B82" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>150</v>
@@ -4491,30 +4516,30 @@
         <v>3</v>
       </c>
       <c r="B83" s="2">
+        <v>39</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="2">
         <v>38</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B84" s="2">
-        <v>37</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>150</v>
@@ -4525,64 +4550,64 @@
         <v>3</v>
       </c>
       <c r="B85" s="2">
+        <v>37</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="2">
         <v>36</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F85" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B86" s="2">
+      <c r="F86" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="2">
         <v>35</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F86" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B87" s="2">
+      <c r="F87" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="2">
         <v>34</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B88" s="2">
-        <v>33</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>150</v>
@@ -4593,47 +4618,47 @@
         <v>3</v>
       </c>
       <c r="B89" s="2">
+        <v>33</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="2">
         <v>32</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B90" s="2">
+      <c r="F90" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="2">
         <v>31</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B91" s="2">
-        <v>30</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>150</v>
@@ -4644,13 +4669,13 @@
         <v>3</v>
       </c>
       <c r="B92" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>150</v>
@@ -4661,13 +4686,13 @@
         <v>3</v>
       </c>
       <c r="B93" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>150</v>
@@ -4678,13 +4703,13 @@
         <v>3</v>
       </c>
       <c r="B94" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>150</v>
@@ -4698,44 +4723,44 @@
         <v>27</v>
       </c>
       <c r="C95" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="2">
+        <v>27</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B96" s="2">
+      <c r="F96" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="2">
         <v>26</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E97" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B97" s="2">
-        <v>25</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>150</v>
@@ -4746,13 +4771,13 @@
         <v>3</v>
       </c>
       <c r="B98" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>150</v>
@@ -4763,13 +4788,13 @@
         <v>3</v>
       </c>
       <c r="B99" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>150</v>
@@ -4780,13 +4805,13 @@
         <v>3</v>
       </c>
       <c r="B100" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>150</v>
@@ -4797,13 +4822,13 @@
         <v>3</v>
       </c>
       <c r="B101" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>150</v>
@@ -4814,13 +4839,13 @@
         <v>3</v>
       </c>
       <c r="B102" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>150</v>
@@ -4831,13 +4856,13 @@
         <v>3</v>
       </c>
       <c r="B103" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>150</v>
@@ -4848,98 +4873,98 @@
         <v>3</v>
       </c>
       <c r="B104" s="2">
+        <v>19</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="2">
         <v>18</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F104" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B105" s="2">
+      <c r="F105" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="2">
         <v>17</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F105" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B106" s="2">
+      <c r="F106" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="2">
         <v>16</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B107" s="2">
+      <c r="F107" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="2">
         <v>15</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E108" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F107" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B108" s="2">
+      <c r="F108" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="2">
         <v>14</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B109" s="2">
-        <v>13</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>150</v>
@@ -4950,13 +4975,13 @@
         <v>3</v>
       </c>
       <c r="B110" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>150</v>
@@ -4967,13 +4992,13 @@
         <v>3</v>
       </c>
       <c r="B111" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>150</v>
@@ -4984,13 +5009,13 @@
         <v>3</v>
       </c>
       <c r="B112" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>150</v>
@@ -5001,64 +5026,64 @@
         <v>3</v>
       </c>
       <c r="B113" s="2">
+        <v>10</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B114" s="2">
         <v>9</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E114" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F113" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B114" s="2">
+      <c r="F114" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" s="2">
         <v>8</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F114" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B115" s="2">
+      <c r="F115" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" s="2">
         <v>7</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B116" s="2">
-        <v>6</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>150</v>
@@ -5069,47 +5094,47 @@
         <v>3</v>
       </c>
       <c r="B117" s="2">
+        <v>6</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" s="2">
         <v>5</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C118" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F117" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B118" s="2">
+      <c r="F118" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B119" s="2">
         <v>4</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B119" s="2">
-        <v>3</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>150</v>
@@ -5120,47 +5145,47 @@
         <v>3</v>
       </c>
       <c r="B120" s="2">
+        <v>3</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B121" s="2">
         <v>2</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="E121" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F120" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B121" s="2">
-        <v>1</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="F121" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="B122" s="2">
         <v>1</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>150</v>
@@ -5168,33 +5193,33 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B123" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B124" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>150</v>
@@ -5205,33 +5230,50 @@
         <v>97</v>
       </c>
       <c r="B125" s="2">
+        <v>2</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B126" s="2">
         <v>1</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C126" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="E126" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="F126" s="2" t="s">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <hyperlinks>
-    <hyperlink ref="L22" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="L42" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="K45" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="L46" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="K14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="O9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="M7" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
-    <hyperlink ref="Q9" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
-    <hyperlink ref="R7" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
-    <hyperlink ref="L3" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
-    <hyperlink ref="M10" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
-    <hyperlink ref="L5" r:id="rId12" xr:uid="{28D0DE1C-48A6-42F2-8E88-DAC27E2438A1}"/>
+    <hyperlink ref="L23" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L43" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K46" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="L47" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K15" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O10" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M8" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
+    <hyperlink ref="Q10" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
+    <hyperlink ref="R8" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
+    <hyperlink ref="L4" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
+    <hyperlink ref="M11" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
+    <hyperlink ref="L6" r:id="rId12" xr:uid="{28D0DE1C-48A6-42F2-8E88-DAC27E2438A1}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId13"/>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D1C9DC-0863-417B-930B-B437AE0F5887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC59114C-F792-46C6-A483-5866E474E0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="510" yWindow="150" windowWidth="17730" windowHeight="20550" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$S$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$T$126</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="462">
   <si>
     <t>Nr</t>
   </si>
@@ -1401,6 +1401,27 @@
   </si>
   <si>
     <t>https://oncoestimand.github.io/complex_designs_communication/complex_designs_communication.html</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-inference-clinicaltrials-share-7457711254632079362-rNIo?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-illnessdeathmodel-oncology-activity-7404519700908482560-7cFJ?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/godwin-yung_i-am-excited-to-share-that-our-article-balancing-ugcPost-7340889926151938048-zIdp?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_innovation-biostatistics-estimand-activity-7128840875215855616-WxVA?utm_source=share&amp;utm_medium=member_desktop</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_oncology-estimand-working-group-activity-7046725113534132226-3uW5?utm_source=share&amp;utm_medium=member_desktop</t>
+  </si>
+  <si>
+    <t>Estimation of AE risk in RCTs</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/pulse/regulators-board-estimands-kaspar-rufibach/</t>
   </si>
 </sst>
 </file>
@@ -1860,32 +1881,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T126"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="97.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="43" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="25.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="29.5703125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.453125" style="2" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="97.81640625" style="2" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" style="2" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1796875" style="2" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="43" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="23.26953125" style="2" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" style="2" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="25.81640625" style="2" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="29.54296875" style="2" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="24.1796875" style="2" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="25.54296875" style="2" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1947,7 +1968,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>369</v>
       </c>
@@ -1975,9 +1996,12 @@
       <c r="M2" s="2" t="s">
         <v>454</v>
       </c>
+      <c r="Q2" t="s">
+        <v>455</v>
+      </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>369</v>
       </c>
@@ -2001,7 +2025,7 @@
       </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>369</v>
       </c>
@@ -2026,9 +2050,12 @@
       <c r="L4" s="4" t="s">
         <v>429</v>
       </c>
+      <c r="Q4" t="s">
+        <v>456</v>
+      </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>369</v>
       </c>
@@ -2052,7 +2079,7 @@
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="90" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" ht="70" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>174</v>
       </c>
@@ -2083,7 +2110,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="20" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>174</v>
       </c>
@@ -2116,7 +2143,7 @@
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ht="40" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>174</v>
       </c>
@@ -2164,7 +2191,7 @@
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>174</v>
       </c>
@@ -2198,9 +2225,12 @@
       <c r="L9" s="2" t="s">
         <v>396</v>
       </c>
+      <c r="Q9" s="2" t="s">
+        <v>457</v>
+      </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
@@ -2248,7 +2278,7 @@
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
@@ -2298,7 +2328,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -2335,9 +2365,12 @@
       <c r="L12" s="3" t="s">
         <v>379</v>
       </c>
+      <c r="Q12" t="s">
+        <v>458</v>
+      </c>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
@@ -2385,7 +2418,7 @@
       </c>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>174</v>
       </c>
@@ -2420,7 +2453,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
@@ -2460,8 +2493,11 @@
       <c r="M15" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="Q15" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>174</v>
       </c>
@@ -2507,6 +2543,9 @@
       <c r="O16" s="2" t="s">
         <v>386</v>
       </c>
+      <c r="Q16" t="s">
+        <v>388</v>
+      </c>
       <c r="R16" s="2" t="s">
         <v>292</v>
       </c>
@@ -2514,7 +2553,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
@@ -2548,8 +2587,11 @@
       <c r="K17" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>174</v>
       </c>
@@ -2584,7 +2626,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
@@ -2619,7 +2661,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>174</v>
       </c>
@@ -2657,7 +2699,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>174</v>
       </c>
@@ -2689,7 +2731,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>174</v>
       </c>
@@ -2735,11 +2777,14 @@
       <c r="O22" s="2" t="s">
         <v>386</v>
       </c>
+      <c r="Q22" t="s">
+        <v>460</v>
+      </c>
       <c r="R22" s="2" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>174</v>
       </c>
@@ -2783,7 +2828,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
@@ -2821,7 +2866,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>174</v>
       </c>
@@ -2856,7 +2901,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>174</v>
       </c>
@@ -2903,7 +2948,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>174</v>
       </c>
@@ -2935,7 +2980,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>174</v>
       </c>
@@ -2976,7 +3021,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>174</v>
       </c>
@@ -3014,7 +3059,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>174</v>
       </c>
@@ -3052,7 +3097,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>174</v>
       </c>
@@ -3087,7 +3132,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>174</v>
       </c>
@@ -3122,7 +3167,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>174</v>
       </c>
@@ -3160,7 +3205,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>174</v>
       </c>
@@ -3195,7 +3240,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>174</v>
       </c>
@@ -3227,7 +3272,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>174</v>
       </c>
@@ -3265,7 +3310,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>174</v>
       </c>
@@ -3303,7 +3348,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>174</v>
       </c>
@@ -3344,7 +3389,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>174</v>
       </c>
@@ -3386,7 +3431,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>174</v>
       </c>
@@ -3427,7 +3472,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>174</v>
       </c>
@@ -3466,7 +3511,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>174</v>
       </c>
@@ -3501,7 +3546,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>174</v>
       </c>
@@ -3542,7 +3587,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
@@ -3580,7 +3625,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>174</v>
       </c>
@@ -3618,7 +3663,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>174</v>
       </c>
@@ -3653,7 +3698,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>174</v>
       </c>
@@ -3691,7 +3736,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>174</v>
       </c>
@@ -3729,7 +3774,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>174</v>
       </c>
@@ -3767,7 +3812,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>174</v>
       </c>
@@ -3802,7 +3847,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>174</v>
       </c>
@@ -3837,7 +3882,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>174</v>
       </c>
@@ -3875,7 +3920,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>174</v>
       </c>
@@ -3910,7 +3955,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>436</v>
       </c>
@@ -3939,7 +3984,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>436</v>
       </c>
@@ -3968,7 +4013,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>359</v>
       </c>
@@ -4000,7 +4045,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>361</v>
       </c>
@@ -4035,7 +4080,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>361</v>
       </c>
@@ -4070,7 +4115,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>361</v>
       </c>
@@ -4105,7 +4150,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>364</v>
       </c>
@@ -4128,7 +4173,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>364</v>
       </c>
@@ -4154,7 +4199,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>3</v>
       </c>
@@ -4171,7 +4216,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>3</v>
       </c>
@@ -4188,7 +4233,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4205,7 +4250,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -4222,7 +4267,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -4239,7 +4284,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
@@ -4256,7 +4301,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4273,7 +4318,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -4290,7 +4335,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -4307,7 +4352,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
@@ -4324,7 +4369,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -4341,7 +4386,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -4358,7 +4403,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -4375,7 +4420,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -4392,7 +4437,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -4409,7 +4454,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -4426,7 +4471,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -4443,7 +4488,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -4460,7 +4505,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -4477,7 +4522,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -4494,7 +4539,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -4511,7 +4556,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -4528,7 +4573,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -4545,7 +4590,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -4562,7 +4607,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -4579,7 +4624,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -4596,7 +4641,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -4613,7 +4658,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -4630,7 +4675,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -4647,7 +4692,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -4664,7 +4709,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -4681,7 +4726,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -4698,7 +4743,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4715,7 +4760,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
@@ -4732,7 +4777,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -4749,7 +4794,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -4766,7 +4811,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
@@ -4783,7 +4828,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
@@ -4800,7 +4845,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
@@ -4817,7 +4862,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
@@ -4834,7 +4879,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
@@ -4851,7 +4896,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
@@ -4868,7 +4913,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
@@ -4885,7 +4930,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
@@ -4902,7 +4947,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
@@ -4919,7 +4964,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
@@ -4936,7 +4981,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
@@ -4953,7 +4998,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
@@ -4970,7 +5015,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
@@ -4987,7 +5032,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
@@ -5004,7 +5049,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -5021,7 +5066,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>3</v>
       </c>
@@ -5038,7 +5083,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
@@ -5055,7 +5100,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>3</v>
       </c>
@@ -5072,7 +5117,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
@@ -5089,7 +5134,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
@@ -5106,7 +5151,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>3</v>
       </c>
@@ -5123,7 +5168,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>3</v>
       </c>
@@ -5140,7 +5185,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>3</v>
       </c>
@@ -5157,7 +5202,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>3</v>
       </c>
@@ -5174,7 +5219,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>3</v>
       </c>
@@ -5191,7 +5236,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>104</v>
       </c>
@@ -5208,7 +5253,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>97</v>
       </c>
@@ -5225,7 +5270,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>97</v>
       </c>
@@ -5242,7 +5287,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>97</v>
       </c>
@@ -5274,9 +5319,10 @@
     <hyperlink ref="L4" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
     <hyperlink ref="M11" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
     <hyperlink ref="L6" r:id="rId12" xr:uid="{28D0DE1C-48A6-42F2-8E88-DAC27E2438A1}"/>
+    <hyperlink ref="Q17" r:id="rId13" xr:uid="{9EC32125-7A81-4C54-87CC-8B89C467AC0B}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId14"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC59114C-F792-46C6-A483-5866E474E0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C4D1F7-778A-4DF9-8D4F-34E211765A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="150" windowWidth="17730" windowHeight="20550" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="463">
   <si>
     <t>Nr</t>
   </si>
@@ -1422,6 +1422,9 @@
   </si>
   <si>
     <t>https://www.linkedin.com/pulse/regulators-board-estimands-kaspar-rufibach/</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/19466315.2026.2656249</t>
   </si>
 </sst>
 </file>
@@ -1881,32 +1884,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T126"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.453125" style="2" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="97.81640625" style="2" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="16.453125" style="2" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="2" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="43" style="2" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="23.26953125" style="2" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" style="2" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="25.81640625" style="2" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="29.54296875" style="2" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="24.1796875" style="2" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="25.54296875" style="2" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.54296875" style="1"/>
+    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="95" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="204.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1968,7 +1971,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>369</v>
       </c>
@@ -2001,7 +2004,7 @@
       </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>369</v>
       </c>
@@ -2025,7 +2028,7 @@
       </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>369</v>
       </c>
@@ -2055,7 +2058,7 @@
       </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>369</v>
       </c>
@@ -2079,7 +2082,7 @@
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="70" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="90" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>174</v>
       </c>
@@ -2101,7 +2104,9 @@
       <c r="G6" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3" t="s">
+        <v>462</v>
+      </c>
       <c r="L6" s="4" t="s">
         <v>449</v>
       </c>
@@ -2110,7 +2115,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>174</v>
       </c>
@@ -2143,7 +2148,7 @@
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="40" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>174</v>
       </c>
@@ -2191,7 +2196,7 @@
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>174</v>
       </c>
@@ -2230,7 +2235,7 @@
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
@@ -2278,7 +2283,7 @@
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
@@ -2328,7 +2333,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -2370,7 +2375,7 @@
       </c>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
@@ -2418,7 +2423,7 @@
       </c>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>174</v>
       </c>
@@ -2453,7 +2458,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
@@ -2497,7 +2502,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>174</v>
       </c>
@@ -2553,7 +2558,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
@@ -2591,7 +2596,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>174</v>
       </c>
@@ -2626,7 +2631,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
@@ -2661,7 +2666,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>174</v>
       </c>
@@ -2699,7 +2704,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>174</v>
       </c>
@@ -2731,7 +2736,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>174</v>
       </c>
@@ -2784,7 +2789,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>174</v>
       </c>
@@ -2828,7 +2833,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
@@ -2866,7 +2871,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>174</v>
       </c>
@@ -2901,7 +2906,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>174</v>
       </c>
@@ -2948,7 +2953,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>174</v>
       </c>
@@ -2980,7 +2985,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>174</v>
       </c>
@@ -3021,7 +3026,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>174</v>
       </c>
@@ -3059,7 +3064,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>174</v>
       </c>
@@ -3097,7 +3102,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>174</v>
       </c>
@@ -3132,7 +3137,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>174</v>
       </c>
@@ -3167,7 +3172,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>174</v>
       </c>
@@ -3205,7 +3210,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>174</v>
       </c>
@@ -3240,7 +3245,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>174</v>
       </c>
@@ -3272,7 +3277,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>174</v>
       </c>
@@ -3310,7 +3315,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>174</v>
       </c>
@@ -3348,7 +3353,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>174</v>
       </c>
@@ -3389,7 +3394,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>174</v>
       </c>
@@ -3431,7 +3436,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>174</v>
       </c>
@@ -3472,7 +3477,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>174</v>
       </c>
@@ -3511,7 +3516,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>174</v>
       </c>
@@ -3546,7 +3551,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>174</v>
       </c>
@@ -3587,7 +3592,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
@@ -3625,7 +3630,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>174</v>
       </c>
@@ -3663,7 +3668,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>174</v>
       </c>
@@ -3698,7 +3703,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>174</v>
       </c>
@@ -3736,7 +3741,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>174</v>
       </c>
@@ -3774,7 +3779,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>174</v>
       </c>
@@ -3812,7 +3817,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>174</v>
       </c>
@@ -3847,7 +3852,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>174</v>
       </c>
@@ -3882,7 +3887,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>174</v>
       </c>
@@ -3920,7 +3925,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>174</v>
       </c>
@@ -3955,7 +3960,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>436</v>
       </c>
@@ -3984,7 +3989,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>436</v>
       </c>
@@ -4013,7 +4018,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>359</v>
       </c>
@@ -4045,7 +4050,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>361</v>
       </c>
@@ -4080,7 +4085,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>361</v>
       </c>
@@ -4115,7 +4120,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>361</v>
       </c>
@@ -4150,7 +4155,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>364</v>
       </c>
@@ -4173,7 +4178,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>364</v>
       </c>
@@ -4199,7 +4204,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>3</v>
       </c>
@@ -4216,7 +4221,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>3</v>
       </c>
@@ -4233,7 +4238,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4250,7 +4255,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -4267,7 +4272,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -4284,7 +4289,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
@@ -4301,7 +4306,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4318,7 +4323,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -4335,7 +4340,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -4352,7 +4357,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
@@ -4369,7 +4374,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -4386,7 +4391,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -4403,7 +4408,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -4420,7 +4425,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -4437,7 +4442,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -4454,7 +4459,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -4471,7 +4476,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -4488,7 +4493,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -4505,7 +4510,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -4522,7 +4527,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -4539,7 +4544,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -4556,7 +4561,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -4573,7 +4578,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -4590,7 +4595,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -4607,7 +4612,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -4624,7 +4629,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -4641,7 +4646,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -4658,7 +4663,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -4675,7 +4680,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -4692,7 +4697,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -4709,7 +4714,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -4726,7 +4731,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -4743,7 +4748,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4760,7 +4765,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
@@ -4777,7 +4782,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -4794,7 +4799,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -4811,7 +4816,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
@@ -4828,7 +4833,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
@@ -4845,7 +4850,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
@@ -4862,7 +4867,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
@@ -4879,7 +4884,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
@@ -4896,7 +4901,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
@@ -4913,7 +4918,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
@@ -4930,7 +4935,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
@@ -4947,7 +4952,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
@@ -4964,7 +4969,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
@@ -4981,7 +4986,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
@@ -4998,7 +5003,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
@@ -5015,7 +5020,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
@@ -5032,7 +5037,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
@@ -5049,7 +5054,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -5066,7 +5071,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>3</v>
       </c>
@@ -5083,7 +5088,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
@@ -5100,7 +5105,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>3</v>
       </c>
@@ -5117,7 +5122,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
@@ -5134,7 +5139,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
@@ -5151,7 +5156,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>3</v>
       </c>
@@ -5168,7 +5173,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>3</v>
       </c>
@@ -5185,7 +5190,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>3</v>
       </c>
@@ -5202,7 +5207,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>3</v>
       </c>
@@ -5219,7 +5224,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>3</v>
       </c>
@@ -5236,7 +5241,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>104</v>
       </c>
@@ -5253,7 +5258,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>97</v>
       </c>
@@ -5270,7 +5275,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>97</v>
       </c>
@@ -5287,7 +5292,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>97</v>
       </c>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C4D1F7-778A-4DF9-8D4F-34E211765A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DD532B-88DA-4470-9727-B631E8459F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$T$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$T$127</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="465">
   <si>
     <t>Nr</t>
   </si>
@@ -1425,6 +1425,12 @@
   </si>
   <si>
     <t>https://doi.org/10.1080/19466315.2026.2656249</t>
+  </si>
+  <si>
+    <t>Guidance for best practice in the analysis of harm outcomes in randomised controlled trials (GUIDE-HARM)</t>
+  </si>
+  <si>
+    <t>Phillips, R., Bi, D., Tan, X.X., Creanor, S., Gamble, C., Hewitt, C., Hooper, R., Harbron, C., Janani, L., Julious, S., Kirkham, J., MacLennan, G., Morris, T., Pearse, R., Ramnarayan, P., **Rufibach, K.**, Thirard, R., Cornelius, V.</t>
   </si>
 </sst>
 </file>
@@ -1883,7 +1889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T126"/>
+  <dimension ref="A1:T127"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1976,16 +1982,16 @@
         <v>369</v>
       </c>
       <c r="B2" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>440</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -1993,32 +1999,23 @@
       <c r="G2" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>455</v>
-      </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B3" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>440</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>149</v>
@@ -2026,23 +2023,32 @@
       <c r="G3" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="L3" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>455</v>
+      </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B4" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>149</v>
@@ -2050,29 +2056,23 @@
       <c r="G4" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>456</v>
-      </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B5" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>418</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>149</v>
@@ -2080,56 +2080,53 @@
       <c r="G5" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="L5" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>456</v>
+      </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="90" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="B6" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>448</v>
+        <v>419</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>383</v>
+        <v>149</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>450</v>
+        <v>171</v>
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B7" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="D7" s="2">
-        <v>2026</v>
+        <v>448</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>440</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>383</v>
@@ -2137,442 +2134,419 @@
       <c r="G7" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="K7" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>411</v>
+      <c r="K7" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B8" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D8" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>150</v>
+        <v>383</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H8" s="2">
-        <v>47</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>423</v>
+        <v>158</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>445</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q8" t="s">
         <v>411</v>
       </c>
-      <c r="R8" s="5" t="s">
-        <v>425</v>
-      </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="90" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B9" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="D9" s="2">
         <v>2025</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H9" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>457</v>
+        <v>406</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>411</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>425</v>
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B10" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D10" s="2">
         <v>2025</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>413</v>
+        <v>233</v>
       </c>
       <c r="H10" s="2">
-        <v>34</v>
-      </c>
-      <c r="I10" s="2">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>412</v>
+        <v>396</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>457</v>
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B11" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>168</v>
+        <v>393</v>
       </c>
       <c r="D11" s="2">
         <v>2025</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>147</v>
+        <v>392</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>245</v>
+        <v>413</v>
       </c>
       <c r="H11" s="2">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="I11" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="T11" s="2"/>
+    </row>
+    <row r="12" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B12" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>373</v>
+        <v>168</v>
       </c>
       <c r="D12" s="2">
         <v>2025</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>372</v>
+        <v>147</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>158</v>
+        <v>245</v>
       </c>
       <c r="H12" s="2">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>458</v>
-      </c>
-      <c r="T12" s="2"/>
-    </row>
-    <row r="13" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B13" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="D13" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="H13" s="2">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>292</v>
+        <v>384</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>458</v>
       </c>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B14" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>175</v>
+        <v>381</v>
       </c>
       <c r="D14" s="2">
         <v>2024</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>146</v>
+        <v>380</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>378</v>
+        <v>237</v>
       </c>
       <c r="H14" s="2">
-        <v>15</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1223858</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>377</v>
+        <v>25</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+        <v>382</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="T14" s="2"/>
+    </row>
+    <row r="15" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B15" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D15" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>154</v>
+        <v>378</v>
       </c>
       <c r="H15" s="2">
-        <v>22</v>
-      </c>
-      <c r="I15" s="2">
-        <v>4</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>173</v>
+        <v>15</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1223858</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>377</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B16" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="D16" s="2">
         <v>2023</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H16" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I16" s="2">
         <v>4</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>289</v>
+        <v>160</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>290</v>
+        <v>180</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>386</v>
+        <v>181</v>
       </c>
       <c r="Q16" t="s">
-        <v>388</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B17" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="D17" s="2">
         <v>2023</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>150</v>
@@ -2584,33 +2558,51 @@
         <v>15</v>
       </c>
       <c r="I17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+        <v>289</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>388</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B18" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D18" s="2">
         <v>2023</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>150</v>
@@ -2622,118 +2614,124 @@
         <v>15</v>
       </c>
       <c r="I18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>159</v>
+        <v>370</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B19" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D19" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="H19" s="2">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="I19" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B20" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D20" s="2">
         <v>2022</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="H20" s="2">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="I20" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B21" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D21" s="2">
         <v>2022</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H21" s="2">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="I21" s="2">
+        <v>5</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
@@ -2741,151 +2739,145 @@
         <v>174</v>
       </c>
       <c r="B22" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D22" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H22" s="2">
-        <v>22</v>
-      </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2">
-        <v>420</v>
+        <v>21</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>460</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B23" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D23" s="2">
         <v>2021</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H23" s="2">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="I23" s="2">
-        <v>4</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>242</v>
+        <v>1</v>
+      </c>
+      <c r="J23" s="2">
+        <v>420</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+        <v>387</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>460</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B24" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D24" s="2">
         <v>2021</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H24" s="2">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="I24" s="2">
+        <v>4</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B25" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D25" s="2">
         <v>2021</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>150</v>
@@ -2897,92 +2889,98 @@
         <v>20</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B26" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D26" s="2">
         <v>2021</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H26" s="2">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B27" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D27" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H27" s="2">
-        <v>4</v>
-      </c>
-      <c r="I27" s="2">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
@@ -2990,116 +2988,110 @@
         <v>174</v>
       </c>
       <c r="B28" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="D28" s="2">
         <v>2020</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>158</v>
+        <v>247</v>
       </c>
       <c r="H28" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I28" s="2">
-        <v>4</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>248</v>
+        <v>68</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B29" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="D29" s="2">
         <v>2020</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>235</v>
+        <v>158</v>
       </c>
       <c r="H29" s="2">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="I29" s="2">
+        <v>4</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+        <v>309</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B30" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D30" s="2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H30" s="2">
-        <v>62</v>
-      </c>
-      <c r="I30" s="2">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
@@ -3107,34 +3099,37 @@
         <v>174</v>
       </c>
       <c r="B31" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D31" s="2">
         <v>2019</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="H31" s="2">
-        <v>38</v>
+        <v>62</v>
+      </c>
+      <c r="I31" s="2">
+        <v>3</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
@@ -3142,34 +3137,34 @@
         <v>174</v>
       </c>
       <c r="B32" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D32" s="2">
         <v>2019</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H32" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3177,16 +3172,16 @@
         <v>174</v>
       </c>
       <c r="B33" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D33" s="2">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>150</v>
@@ -3195,19 +3190,16 @@
         <v>235</v>
       </c>
       <c r="H33" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3215,34 +3207,37 @@
         <v>174</v>
       </c>
       <c r="B34" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D34" s="2">
         <v>2016</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H34" s="2">
-        <v>58</v>
-      </c>
-      <c r="I34" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3250,31 +3245,34 @@
         <v>174</v>
       </c>
       <c r="B35" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D35" s="2">
         <v>2016</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H35" s="2">
-        <v>47</v>
+        <v>58</v>
+      </c>
+      <c r="I35" s="2">
+        <v>6</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3282,37 +3280,31 @@
         <v>174</v>
       </c>
       <c r="B36" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D36" s="2">
         <v>2016</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H36" s="2">
-        <v>26</v>
-      </c>
-      <c r="I36" s="2">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3320,37 +3312,37 @@
         <v>174</v>
       </c>
       <c r="B37" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D37" s="2">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H37" s="2">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="I37" s="2">
+        <v>2</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3358,40 +3350,37 @@
         <v>174</v>
       </c>
       <c r="B38" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D38" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H38" s="2">
-        <v>75</v>
-      </c>
-      <c r="I38" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3399,41 +3388,40 @@
         <v>174</v>
       </c>
       <c r="B39" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D39" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H39" s="2">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="I39" s="2">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="str">
-        <f>"1-29"</f>
-        <v>1-29</v>
+        <v>4</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3441,40 +3429,41 @@
         <v>174</v>
       </c>
       <c r="B40" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D40" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="H40" s="2">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="I40" s="2">
-        <v>4</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>264</v>
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="str">
+        <f>"1-29"</f>
+        <v>1-29</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3482,38 +3471,40 @@
         <v>174</v>
       </c>
       <c r="B41" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D41" s="2">
         <v>2011</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="H41" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="I41" s="2">
-        <v>6</v>
-      </c>
-      <c r="J41" s="2" t="str">
-        <f>"1-28"</f>
-        <v>1-28</v>
+        <v>4</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3521,75 +3512,73 @@
         <v>174</v>
       </c>
       <c r="B42" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D42" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H42" s="2">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="I42" s="2">
-        <v>4</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>267</v>
+        <v>6</v>
+      </c>
+      <c r="J42" s="2" t="str">
+        <f>"1-28"</f>
+        <v>1-28</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B43" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D43" s="2">
         <v>2010</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H43" s="2">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I43" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3597,37 +3586,40 @@
         <v>174</v>
       </c>
       <c r="B44" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D44" s="2">
         <v>2010</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H44" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I44" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>340</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3635,37 +3627,37 @@
         <v>174</v>
       </c>
       <c r="B45" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D45" s="2">
         <v>2010</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H45" s="2">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="I45" s="2">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3673,34 +3665,37 @@
         <v>174</v>
       </c>
       <c r="B46" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D46" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="H46" s="2">
-        <v>31</v>
-      </c>
-      <c r="I46" s="2">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3708,37 +3703,34 @@
         <v>174</v>
       </c>
       <c r="B47" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D47" s="2">
         <v>2009</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="H47" s="2">
-        <v>79</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>275</v>
+        <v>31</v>
+      </c>
+      <c r="I47" s="2">
+        <v>1</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3746,37 +3738,37 @@
         <v>174</v>
       </c>
       <c r="B48" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>288</v>
+        <v>211</v>
       </c>
       <c r="D48" s="2">
         <v>2009</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H48" s="2">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3784,34 +3776,34 @@
         <v>174</v>
       </c>
       <c r="B49" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="D49" s="2">
         <v>2009</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H49" s="2">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>333</v>
@@ -3822,51 +3814,54 @@
         <v>174</v>
       </c>
       <c r="B50" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D50" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H50" s="2">
-        <v>78</v>
-      </c>
-      <c r="I50" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+        <v>354</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B51" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D51" s="2">
         <v>2008</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>150</v>
@@ -3878,115 +3873,121 @@
         <v>78</v>
       </c>
       <c r="I51" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B52" s="2">
+        <v>3</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2008</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H52" s="2">
+        <v>78</v>
+      </c>
+      <c r="I52" s="2">
         <v>2</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D52" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="H52" s="2">
-        <v>77</v>
-      </c>
-      <c r="I52" s="2">
-        <v>7</v>
-      </c>
       <c r="J52" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="O52" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="D53" s="2">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H53" s="2">
-        <v>2001</v>
+        <v>77</v>
       </c>
       <c r="I53" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>436</v>
+        <v>174</v>
       </c>
       <c r="B54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>434</v>
+        <v>212</v>
       </c>
       <c r="D54" s="2">
-        <v>2026</v>
+        <v>2001</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>435</v>
+        <v>218</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>432</v>
+        <v>285</v>
+      </c>
+      <c r="H54" s="2">
+        <v>2001</v>
+      </c>
+      <c r="I54" s="2">
+        <v>1</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>437</v>
+        <v>286</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>439</v>
+        <v>368</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -3994,16 +3995,16 @@
         <v>436</v>
       </c>
       <c r="B55" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D55" s="2">
         <v>2026</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>150</v>
@@ -4012,77 +4013,71 @@
         <v>432</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>359</v>
+        <v>436</v>
       </c>
       <c r="B56" s="2">
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D56" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B57" s="2">
+        <v>1</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D57" s="2">
         <v>2010</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G56" s="2" t="s">
+      <c r="F57" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H57" s="2">
         <v>72</v>
       </c>
-      <c r="I56" s="2">
+      <c r="I57" s="2">
         <v>5</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="J57" s="2" t="s">
         <v>360</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B57" s="2">
-        <v>3</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D57" s="2">
-        <v>2023</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H57" s="2">
-        <v>15</v>
-      </c>
-      <c r="I57" s="2">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -4090,16 +4085,16 @@
         <v>361</v>
       </c>
       <c r="B58" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D58" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>150</v>
@@ -4108,16 +4103,16 @@
         <v>158</v>
       </c>
       <c r="H58" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I58" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -4125,57 +4120,69 @@
         <v>361</v>
       </c>
       <c r="B59" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>199</v>
+        <v>376</v>
       </c>
       <c r="D59" s="2">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>398</v>
+        <v>139</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>399</v>
+        <v>158</v>
       </c>
       <c r="H59" s="2">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="I59" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B60" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D60" s="2">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>112</v>
+        <v>398</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>365</v>
+        <v>399</v>
+      </c>
+      <c r="H60" s="2">
+        <v>63</v>
+      </c>
+      <c r="I60" s="2">
+        <v>8</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -4183,42 +4190,48 @@
         <v>364</v>
       </c>
       <c r="B61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>367</v>
+        <v>207</v>
       </c>
       <c r="D61" s="2">
         <v>2007</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>401</v>
+        <v>365</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>3</v>
+        <v>364</v>
       </c>
       <c r="B62" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>136</v>
+        <v>367</v>
+      </c>
+      <c r="D62" s="2">
+        <v>2007</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -4226,13 +4239,13 @@
         <v>3</v>
       </c>
       <c r="B63" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>4</v>
+        <v>136</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>150</v>
@@ -4243,47 +4256,47 @@
         <v>3</v>
       </c>
       <c r="B64" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E64" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="2">
+        <v>58</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="2">
+      <c r="F65" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="2">
         <v>57</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B66" s="2">
-        <v>56</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>150</v>
@@ -4294,13 +4307,13 @@
         <v>3</v>
       </c>
       <c r="B67" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>150</v>
@@ -4311,13 +4324,13 @@
         <v>3</v>
       </c>
       <c r="B68" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>150</v>
@@ -4328,13 +4341,13 @@
         <v>3</v>
       </c>
       <c r="B69" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>150</v>
@@ -4345,13 +4358,13 @@
         <v>3</v>
       </c>
       <c r="B70" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>150</v>
@@ -4362,47 +4375,47 @@
         <v>3</v>
       </c>
       <c r="B71" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E71" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="2">
+        <v>51</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" s="2">
+      <c r="F72" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="2">
         <v>50</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B73" s="2">
-        <v>49</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>150</v>
@@ -4413,47 +4426,47 @@
         <v>3</v>
       </c>
       <c r="B74" s="2">
+        <v>49</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="2">
         <v>48</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="2">
+      <c r="F75" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="2">
         <v>47</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B76" s="2">
-        <v>46</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>150</v>
@@ -4464,13 +4477,13 @@
         <v>3</v>
       </c>
       <c r="B77" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>150</v>
@@ -4481,13 +4494,13 @@
         <v>3</v>
       </c>
       <c r="B78" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>150</v>
@@ -4498,13 +4511,13 @@
         <v>3</v>
       </c>
       <c r="B79" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>150</v>
@@ -4515,13 +4528,13 @@
         <v>3</v>
       </c>
       <c r="B80" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>150</v>
@@ -4532,13 +4545,13 @@
         <v>3</v>
       </c>
       <c r="B81" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>150</v>
@@ -4549,13 +4562,13 @@
         <v>3</v>
       </c>
       <c r="B82" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>150</v>
@@ -4566,13 +4579,13 @@
         <v>3</v>
       </c>
       <c r="B83" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>150</v>
@@ -4583,30 +4596,30 @@
         <v>3</v>
       </c>
       <c r="B84" s="2">
+        <v>39</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="2">
         <v>38</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B85" s="2">
-        <v>37</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>150</v>
@@ -4617,64 +4630,64 @@
         <v>3</v>
       </c>
       <c r="B86" s="2">
+        <v>37</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="2">
         <v>36</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F86" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B87" s="2">
+      <c r="F87" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="2">
         <v>35</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B88" s="2">
+      <c r="F88" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="2">
         <v>34</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B89" s="2">
-        <v>33</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>150</v>
@@ -4685,47 +4698,47 @@
         <v>3</v>
       </c>
       <c r="B90" s="2">
+        <v>33</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="2">
         <v>32</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B91" s="2">
+      <c r="F91" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="2">
         <v>31</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E92" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B92" s="2">
-        <v>30</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>150</v>
@@ -4736,13 +4749,13 @@
         <v>3</v>
       </c>
       <c r="B93" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>150</v>
@@ -4753,13 +4766,13 @@
         <v>3</v>
       </c>
       <c r="B94" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>150</v>
@@ -4770,13 +4783,13 @@
         <v>3</v>
       </c>
       <c r="B95" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>150</v>
@@ -4790,44 +4803,44 @@
         <v>27</v>
       </c>
       <c r="C96" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="2">
+        <v>27</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E97" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F96" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B97" s="2">
+      <c r="F97" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="2">
         <v>26</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B98" s="2">
-        <v>25</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>150</v>
@@ -4838,13 +4851,13 @@
         <v>3</v>
       </c>
       <c r="B99" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>150</v>
@@ -4855,13 +4868,13 @@
         <v>3</v>
       </c>
       <c r="B100" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>150</v>
@@ -4872,13 +4885,13 @@
         <v>3</v>
       </c>
       <c r="B101" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>150</v>
@@ -4889,13 +4902,13 @@
         <v>3</v>
       </c>
       <c r="B102" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>150</v>
@@ -4906,13 +4919,13 @@
         <v>3</v>
       </c>
       <c r="B103" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>150</v>
@@ -4923,13 +4936,13 @@
         <v>3</v>
       </c>
       <c r="B104" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>150</v>
@@ -4940,98 +4953,98 @@
         <v>3</v>
       </c>
       <c r="B105" s="2">
+        <v>19</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="2">
         <v>18</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F105" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B106" s="2">
+      <c r="F106" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="2">
         <v>17</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B107" s="2">
+      <c r="F107" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="2">
         <v>16</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E108" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F107" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B108" s="2">
+      <c r="F108" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="2">
         <v>15</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F108" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B109" s="2">
+      <c r="F109" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B110" s="2">
         <v>14</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B110" s="2">
-        <v>13</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>150</v>
@@ -5042,13 +5055,13 @@
         <v>3</v>
       </c>
       <c r="B111" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>150</v>
@@ -5059,13 +5072,13 @@
         <v>3</v>
       </c>
       <c r="B112" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>150</v>
@@ -5076,13 +5089,13 @@
         <v>3</v>
       </c>
       <c r="B113" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>150</v>
@@ -5093,64 +5106,64 @@
         <v>3</v>
       </c>
       <c r="B114" s="2">
+        <v>10</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" s="2">
         <v>9</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F114" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B115" s="2">
+      <c r="F115" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" s="2">
         <v>8</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F115" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B116" s="2">
+      <c r="F116" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B117" s="2">
         <v>7</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B117" s="2">
-        <v>6</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>150</v>
@@ -5161,47 +5174,47 @@
         <v>3</v>
       </c>
       <c r="B118" s="2">
+        <v>6</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B119" s="2">
         <v>5</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F118" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B119" s="2">
+      <c r="F119" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B120" s="2">
         <v>4</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C120" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B120" s="2">
-        <v>3</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>150</v>
@@ -5212,47 +5225,47 @@
         <v>3</v>
       </c>
       <c r="B121" s="2">
+        <v>3</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B122" s="2">
         <v>2</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C122" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="E122" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F121" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B122" s="2">
-        <v>1</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="F122" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="B123" s="2">
         <v>1</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>150</v>
@@ -5260,33 +5273,33 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B124" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B125" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>150</v>
@@ -5297,34 +5310,51 @@
         <v>97</v>
       </c>
       <c r="B126" s="2">
+        <v>2</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A127" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B127" s="2">
         <v>1</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C127" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="E127" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F126" s="2" t="s">
+      <c r="F127" s="2" t="s">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <hyperlinks>
-    <hyperlink ref="L23" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="L43" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="K46" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="L47" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="K15" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="O10" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="M8" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
-    <hyperlink ref="Q10" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
-    <hyperlink ref="R8" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
-    <hyperlink ref="L4" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
-    <hyperlink ref="M11" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
-    <hyperlink ref="L6" r:id="rId12" xr:uid="{28D0DE1C-48A6-42F2-8E88-DAC27E2438A1}"/>
-    <hyperlink ref="Q17" r:id="rId13" xr:uid="{9EC32125-7A81-4C54-87CC-8B89C467AC0B}"/>
+    <hyperlink ref="L24" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L44" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K47" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="L48" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M9" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
+    <hyperlink ref="Q11" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
+    <hyperlink ref="R9" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
+    <hyperlink ref="L5" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
+    <hyperlink ref="M12" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
+    <hyperlink ref="L7" r:id="rId12" xr:uid="{28D0DE1C-48A6-42F2-8E88-DAC27E2438A1}"/>
+    <hyperlink ref="Q18" r:id="rId13" xr:uid="{9EC32125-7A81-4C54-87CC-8B89C467AC0B}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId14"/>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DD532B-88DA-4470-9727-B631E8459F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0082BD27-58EA-448E-BCCC-9E82BCDFF7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="466">
   <si>
     <t>Nr</t>
   </si>
@@ -1187,9 +1187,6 @@
     <t>http://arxiv.org/abs/2402.17692</t>
   </si>
   <si>
-    <t>ta</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1080/19466315.2024.2327291</t>
   </si>
   <si>
@@ -1431,6 +1428,12 @@
   </si>
   <si>
     <t>Phillips, R., Bi, D., Tan, X.X., Creanor, S., Gamble, C., Hewitt, C., Hooper, R., Harbron, C., Janani, L., Julious, S., Kirkham, J., MacLennan, G., Morris, T., Pearse, R., Ramnarayan, P., **Rufibach, K.**, Thirard, R., Cornelius, V.</t>
+  </si>
+  <si>
+    <t>194--205</t>
+  </si>
+  <si>
+    <t>235--241</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1956,7 @@
         <v>374</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>162</v>
@@ -1985,13 +1988,13 @@
         <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -2009,13 +2012,13 @@
         <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>149</v>
@@ -2024,13 +2027,13 @@
         <v>171</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>454</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>455</v>
       </c>
       <c r="T3" s="2"/>
     </row>
@@ -2042,13 +2045,13 @@
         <v>51</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>149</v>
@@ -2066,13 +2069,13 @@
         <v>50</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>149</v>
@@ -2081,10 +2084,10 @@
         <v>171</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="T5" s="2"/>
     </row>
@@ -2096,13 +2099,13 @@
         <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>149</v>
@@ -2120,28 +2123,37 @@
         <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>383</v>
+        <v>150</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>158</v>
       </c>
+      <c r="H7" s="2">
+        <v>18</v>
+      </c>
+      <c r="I7" s="2">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>464</v>
+      </c>
       <c r="K7" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L7" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="T7" s="2"/>
     </row>
@@ -2153,28 +2165,37 @@
         <v>47</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D8" s="2">
         <v>2026</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>383</v>
+        <v>150</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>158</v>
       </c>
+      <c r="H8" s="2">
+        <v>18</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>465</v>
+      </c>
       <c r="K8" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="T8" s="2"/>
     </row>
@@ -2186,13 +2207,13 @@
         <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D9" s="2">
         <v>2025</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>150</v>
@@ -2204,25 +2225,25 @@
         <v>47</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>410</v>
+      </c>
+      <c r="R9" s="5" t="s">
         <v>424</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>411</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>425</v>
       </c>
       <c r="T9" s="2"/>
     </row>
@@ -2234,13 +2255,13 @@
         <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D10" s="2">
         <v>2025</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>150</v>
@@ -2252,16 +2273,16 @@
         <v>44</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T10" s="2"/>
     </row>
@@ -2273,19 +2294,19 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D11" s="2">
         <v>2025</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H11" s="2">
         <v>34</v>
@@ -2294,22 +2315,22 @@
         <v>5</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="T11" s="2"/>
     </row>
@@ -2342,16 +2363,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>172</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>179</v>
@@ -2392,16 +2413,16 @@
         <v>1</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>379</v>
       </c>
       <c r="Q13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T13" s="2"/>
     </row>
@@ -2431,22 +2452,22 @@
         <v>25</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>382</v>
       </c>
       <c r="N14" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q14" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>292</v>
@@ -2529,7 +2550,7 @@
         <v>181</v>
       </c>
       <c r="Q16" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
@@ -2573,13 +2594,13 @@
         <v>291</v>
       </c>
       <c r="N17" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q17" t="s">
         <v>387</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>388</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>292</v>
@@ -2623,7 +2644,7 @@
         <v>183</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
@@ -2807,13 +2828,13 @@
         <v>291</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q23" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="R23" s="2" t="s">
         <v>292</v>
@@ -2974,10 +2995,10 @@
         <v>291</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>292</v>
@@ -3992,60 +4013,60 @@
     </row>
     <row r="55" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B55" s="2">
         <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D55" s="2">
         <v>2026</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B56" s="2">
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D56" s="2">
         <v>2026</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>432</v>
-      </c>
       <c r="J56" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="K56" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
@@ -4112,7 +4133,7 @@
         <v>362</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -4147,7 +4168,7 @@
         <v>363</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -4164,13 +4185,13 @@
         <v>2010</v>
       </c>
       <c r="E60" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="H60" s="2">
         <v>63</v>
@@ -4179,10 +4200,10 @@
         <v>8</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
@@ -4231,7 +4252,7 @@
         <v>366</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0082BD27-58EA-448E-BCCC-9E82BCDFF7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6D5720-6B2B-4830-BF21-EF2885338545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="467">
   <si>
     <t>Nr</t>
   </si>
@@ -1434,6 +1434,9 @@
   </si>
   <si>
     <t>235--241</t>
+  </si>
+  <si>
+    <t>https://theeffectivestatistician.com/the-future-of-statistical-methodology-in-drug-development/</t>
   </si>
 </sst>
 </file>
@@ -1893,32 +1896,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T127"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="95" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="204.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.5703125" style="1"/>
+    <col min="8" max="8" width="4.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="204.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1980,7 +1983,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>369</v>
       </c>
@@ -2004,7 +2007,7 @@
       </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>369</v>
       </c>
@@ -2037,7 +2040,7 @@
       </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>369</v>
       </c>
@@ -2061,7 +2064,7 @@
       </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>369</v>
       </c>
@@ -2091,7 +2094,7 @@
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>369</v>
       </c>
@@ -2115,7 +2118,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>174</v>
       </c>
@@ -2155,9 +2158,12 @@
       <c r="Q7" s="2" t="s">
         <v>449</v>
       </c>
+      <c r="R7" s="2" t="s">
+        <v>466</v>
+      </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="20" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>174</v>
       </c>
@@ -2199,7 +2205,7 @@
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ht="40" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>174</v>
       </c>
@@ -2247,7 +2253,7 @@
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
@@ -2286,7 +2292,7 @@
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
@@ -2334,7 +2340,7 @@
       </c>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -2384,7 +2390,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
@@ -2426,7 +2432,7 @@
       </c>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>174</v>
       </c>
@@ -2474,7 +2480,7 @@
       </c>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
@@ -2509,7 +2515,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>174</v>
       </c>
@@ -2553,7 +2559,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
@@ -2609,7 +2615,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>174</v>
       </c>
@@ -2647,7 +2653,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
@@ -2682,7 +2688,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>174</v>
       </c>
@@ -2717,7 +2723,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>174</v>
       </c>
@@ -2755,7 +2761,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>174</v>
       </c>
@@ -2787,7 +2793,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>174</v>
       </c>
@@ -2840,7 +2846,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
@@ -2884,7 +2890,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>174</v>
       </c>
@@ -2922,7 +2928,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>174</v>
       </c>
@@ -2957,7 +2963,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>174</v>
       </c>
@@ -3004,7 +3010,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>174</v>
       </c>
@@ -3036,7 +3042,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>174</v>
       </c>
@@ -3077,7 +3083,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>174</v>
       </c>
@@ -3115,7 +3121,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>174</v>
       </c>
@@ -3153,7 +3159,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>174</v>
       </c>
@@ -3188,7 +3194,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>174</v>
       </c>
@@ -3223,7 +3229,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>174</v>
       </c>
@@ -3261,7 +3267,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>174</v>
       </c>
@@ -3296,7 +3302,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>174</v>
       </c>
@@ -3328,7 +3334,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>174</v>
       </c>
@@ -3366,7 +3372,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>174</v>
       </c>
@@ -3404,7 +3410,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>174</v>
       </c>
@@ -3445,7 +3451,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>174</v>
       </c>
@@ -3487,7 +3493,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>174</v>
       </c>
@@ -3528,7 +3534,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>174</v>
       </c>
@@ -3567,7 +3573,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>174</v>
       </c>
@@ -3602,7 +3608,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
@@ -3643,7 +3649,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>174</v>
       </c>
@@ -3681,7 +3687,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>174</v>
       </c>
@@ -3719,7 +3725,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>174</v>
       </c>
@@ -3754,7 +3760,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>174</v>
       </c>
@@ -3792,7 +3798,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>174</v>
       </c>
@@ -3830,7 +3836,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>174</v>
       </c>
@@ -3868,7 +3874,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>174</v>
       </c>
@@ -3903,7 +3909,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>174</v>
       </c>
@@ -3938,7 +3944,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>174</v>
       </c>
@@ -3976,7 +3982,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>174</v>
       </c>
@@ -4011,7 +4017,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>435</v>
       </c>
@@ -4040,7 +4046,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>435</v>
       </c>
@@ -4069,7 +4075,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>359</v>
       </c>
@@ -4101,7 +4107,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>361</v>
       </c>
@@ -4136,7 +4142,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>361</v>
       </c>
@@ -4171,7 +4177,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>361</v>
       </c>
@@ -4206,7 +4212,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>364</v>
       </c>
@@ -4229,7 +4235,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>364</v>
       </c>
@@ -4255,7 +4261,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>3</v>
       </c>
@@ -4272,7 +4278,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4289,7 +4295,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -4306,7 +4312,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -4323,7 +4329,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
@@ -4340,7 +4346,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4357,7 +4363,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -4374,7 +4380,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -4391,7 +4397,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
@@ -4408,7 +4414,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -4425,7 +4431,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -4442,7 +4448,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -4459,7 +4465,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -4476,7 +4482,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -4493,7 +4499,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -4510,7 +4516,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -4527,7 +4533,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -4544,7 +4550,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -4561,7 +4567,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -4578,7 +4584,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -4595,7 +4601,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -4612,7 +4618,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -4629,7 +4635,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -4646,7 +4652,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -4663,7 +4669,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -4680,7 +4686,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -4697,7 +4703,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -4714,7 +4720,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -4731,7 +4737,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -4748,7 +4754,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -4765,7 +4771,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -4782,7 +4788,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4799,7 +4805,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
@@ -4816,7 +4822,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -4833,7 +4839,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -4850,7 +4856,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
@@ -4867,7 +4873,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
@@ -4884,7 +4890,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
@@ -4901,7 +4907,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
@@ -4918,7 +4924,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
@@ -4935,7 +4941,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
@@ -4952,7 +4958,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
@@ -4969,7 +4975,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
@@ -4986,7 +4992,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
@@ -5003,7 +5009,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
@@ -5020,7 +5026,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
@@ -5037,7 +5043,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
@@ -5054,7 +5060,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
@@ -5071,7 +5077,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
@@ -5088,7 +5094,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -5105,7 +5111,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>3</v>
       </c>
@@ -5122,7 +5128,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
@@ -5139,7 +5145,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>3</v>
       </c>
@@ -5156,7 +5162,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
@@ -5173,7 +5179,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
@@ -5190,7 +5196,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>3</v>
       </c>
@@ -5207,7 +5213,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>3</v>
       </c>
@@ -5224,7 +5230,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>3</v>
       </c>
@@ -5241,7 +5247,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>3</v>
       </c>
@@ -5258,7 +5264,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>3</v>
       </c>
@@ -5275,7 +5281,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>3</v>
       </c>
@@ -5292,7 +5298,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>104</v>
       </c>
@@ -5309,7 +5315,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>97</v>
       </c>
@@ -5326,7 +5332,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>97</v>
       </c>
@@ -5343,7 +5349,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>97</v>
       </c>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6D5720-6B2B-4830-BF21-EF2885338545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE174CA-56E4-4192-9492-E63020F965BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$T$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$T$128</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="470">
   <si>
     <t>Nr</t>
   </si>
@@ -1437,6 +1437,15 @@
   </si>
   <si>
     <t>https://theeffectivestatistician.com/the-future-of-statistical-methodology-in-drug-development/</t>
+  </si>
+  <si>
+    <t>Vandemeulebroecke, M., Akacha, M., Kähler Holst, K., Krams, M., Magnusson, B., Perperoglu, A., **Rufibach, K.**, Wright, D.</t>
+  </si>
+  <si>
+    <t>Towards a value proposition for statisticians and other quantitative scientists in AI-enhanced drug development</t>
+  </si>
+  <si>
+    <t>https://osf.io/2kebj/files/a7qgy</t>
   </si>
 </sst>
 </file>
@@ -1895,33 +1904,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T127"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T128"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="95" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="204.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.54296875" style="1"/>
+    <col min="8" max="8" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="204.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1983,21 +1992,21 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B2" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>439</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -2005,23 +2014,26 @@
       <c r="G2" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>469</v>
+      </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B3" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>439</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>149</v>
@@ -2029,32 +2041,23 @@
       <c r="G3" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>454</v>
-      </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B4" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>439</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>149</v>
@@ -2062,23 +2065,32 @@
       <c r="G4" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="L4" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>454</v>
+      </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B5" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>149</v>
@@ -2086,29 +2098,23 @@
       <c r="G5" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>455</v>
-      </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B6" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>417</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>149</v>
@@ -2116,68 +2122,53 @@
       <c r="G6" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="L6" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>455</v>
+      </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="B7" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H7" s="2">
-        <v>18</v>
-      </c>
-      <c r="I7" s="2">
-        <v>2</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>466</v>
+        <v>171</v>
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B8" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2026</v>
+        <v>447</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>439</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>406</v>
+        <v>446</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>150</v>
@@ -2192,444 +2183,433 @@
         <v>2</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>410</v>
+        <v>464</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>466</v>
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="40" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B9" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D9" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="H9" s="2">
-        <v>47</v>
+        <v>18</v>
+      </c>
+      <c r="I9" s="2">
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>422</v>
+        <v>465</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>444</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="Q9" t="s">
         <v>410</v>
       </c>
-      <c r="R9" s="5" t="s">
-        <v>424</v>
-      </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="45" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B10" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="D10" s="2">
         <v>2025</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H10" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>456</v>
+        <v>405</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>410</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>424</v>
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B11" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D11" s="2">
         <v>2025</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>412</v>
+        <v>233</v>
       </c>
       <c r="H11" s="2">
-        <v>34</v>
-      </c>
-      <c r="I11" s="2">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>456</v>
       </c>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B12" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>168</v>
+        <v>392</v>
       </c>
       <c r="D12" s="2">
         <v>2025</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>147</v>
+        <v>391</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>245</v>
+        <v>412</v>
       </c>
       <c r="H12" s="2">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="I12" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>429</v>
+        <v>396</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="T12" s="2"/>
+    </row>
+    <row r="13" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B13" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>373</v>
+        <v>168</v>
       </c>
       <c r="D13" s="2">
         <v>2025</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>372</v>
+        <v>147</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>158</v>
+        <v>245</v>
       </c>
       <c r="H13" s="2">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>457</v>
-      </c>
-      <c r="T13" s="2"/>
-    </row>
-    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B14" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="D14" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="H14" s="2">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>292</v>
+        <v>383</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>457</v>
       </c>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B15" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>175</v>
+        <v>381</v>
       </c>
       <c r="D15" s="2">
         <v>2024</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>146</v>
+        <v>380</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>378</v>
+        <v>237</v>
       </c>
       <c r="H15" s="2">
-        <v>15</v>
-      </c>
-      <c r="J15" s="2">
-        <v>1223858</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>377</v>
+        <v>25</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="T15" s="2"/>
+    </row>
+    <row r="16" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B16" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D16" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>154</v>
+        <v>378</v>
       </c>
       <c r="H16" s="2">
-        <v>22</v>
-      </c>
-      <c r="I16" s="2">
-        <v>4</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>173</v>
+        <v>15</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1223858</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>377</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B17" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="D17" s="2">
         <v>2023</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H17" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I17" s="2">
         <v>4</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>289</v>
+        <v>160</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>290</v>
+        <v>180</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>385</v>
+        <v>181</v>
       </c>
       <c r="Q17" t="s">
-        <v>387</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B18" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="D18" s="2">
         <v>2023</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>150</v>
@@ -2641,33 +2621,51 @@
         <v>15</v>
       </c>
       <c r="I18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>387</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B19" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D19" s="2">
         <v>2023</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>150</v>
@@ -2679,270 +2677,270 @@
         <v>15</v>
       </c>
       <c r="I19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>159</v>
+        <v>370</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B20" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D20" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="H20" s="2">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="I20" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B21" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D21" s="2">
         <v>2022</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="H21" s="2">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="I21" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B22" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D22" s="2">
         <v>2022</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H22" s="2">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="I22" s="2">
+        <v>5</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B23" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D23" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H23" s="2">
-        <v>22</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2">
-        <v>420</v>
+        <v>21</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>459</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B24" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D24" s="2">
         <v>2021</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H24" s="2">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="I24" s="2">
-        <v>4</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>242</v>
+        <v>1</v>
+      </c>
+      <c r="J24" s="2">
+        <v>420</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>459</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B25" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D25" s="2">
         <v>2021</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H25" s="2">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="I25" s="2">
+        <v>4</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B26" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D26" s="2">
         <v>2021</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>150</v>
@@ -2954,296 +2952,299 @@
         <v>20</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B27" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D27" s="2">
         <v>2021</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H27" s="2">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B28" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D28" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H28" s="2">
-        <v>4</v>
-      </c>
-      <c r="I28" s="2">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B29" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="D29" s="2">
         <v>2020</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>158</v>
+        <v>247</v>
       </c>
       <c r="H29" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I29" s="2">
-        <v>4</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>248</v>
+        <v>68</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B30" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="D30" s="2">
         <v>2020</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>235</v>
+        <v>158</v>
       </c>
       <c r="H30" s="2">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="I30" s="2">
+        <v>4</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B31" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D31" s="2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H31" s="2">
-        <v>62</v>
-      </c>
-      <c r="I31" s="2">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B32" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D32" s="2">
         <v>2019</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="H32" s="2">
-        <v>38</v>
+        <v>62</v>
+      </c>
+      <c r="I32" s="2">
+        <v>3</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B33" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D33" s="2">
         <v>2019</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H33" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B34" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D34" s="2">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>150</v>
@@ -3252,678 +3253,678 @@
         <v>235</v>
       </c>
       <c r="H34" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B35" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D35" s="2">
         <v>2016</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H35" s="2">
-        <v>58</v>
-      </c>
-      <c r="I35" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B36" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D36" s="2">
         <v>2016</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H36" s="2">
-        <v>47</v>
+        <v>58</v>
+      </c>
+      <c r="I36" s="2">
+        <v>6</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B37" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D37" s="2">
         <v>2016</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H37" s="2">
-        <v>26</v>
-      </c>
-      <c r="I37" s="2">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B38" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D38" s="2">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H38" s="2">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="I38" s="2">
+        <v>2</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B39" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D39" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H39" s="2">
-        <v>75</v>
-      </c>
-      <c r="I39" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B40" s="2">
+        <v>16</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2013</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H40" s="2">
+        <v>75</v>
+      </c>
+      <c r="I40" s="2">
+        <v>4</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B41" s="2">
         <v>15</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D41" s="2">
         <v>2012</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G40" s="2" t="s">
+      <c r="F41" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H41" s="2">
         <v>8</v>
       </c>
-      <c r="I40" s="2">
+      <c r="I41" s="2">
         <v>1</v>
       </c>
-      <c r="J40" s="2" t="str">
+      <c r="J41" s="2" t="str">
         <f>"1-29"</f>
         <v>1-29</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="K41" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="L40" s="2" t="s">
+      <c r="L41" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="O40" s="2" t="s">
+      <c r="O41" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B41" s="2">
-        <v>14</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D41" s="2">
-        <v>2011</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="H41" s="2">
-        <v>53</v>
-      </c>
-      <c r="I41" s="2">
-        <v>4</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B42" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D42" s="2">
         <v>2011</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H42" s="2">
+        <v>53</v>
+      </c>
+      <c r="I42" s="2">
+        <v>4</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B43" s="2">
+        <v>13</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2011</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G42" s="2" t="s">
+      <c r="F43" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H43" s="2">
         <v>39</v>
       </c>
-      <c r="I42" s="2">
+      <c r="I43" s="2">
         <v>6</v>
       </c>
-      <c r="J42" s="2" t="str">
+      <c r="J43" s="2" t="str">
         <f>"1-28"</f>
         <v>1-28</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="K43" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="O42" s="2" t="s">
+      <c r="O43" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B43" s="2">
-        <v>12</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D43" s="2">
-        <v>2010</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="H43" s="2">
-        <v>66</v>
-      </c>
-      <c r="I43" s="2">
-        <v>4</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B44" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D44" s="2">
         <v>2010</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H44" s="2">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I44" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B45" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D45" s="2">
         <v>2010</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H45" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I45" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>340</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B46" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D46" s="2">
         <v>2010</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H46" s="2">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="I46" s="2">
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B47" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D47" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="H47" s="2">
-        <v>31</v>
-      </c>
-      <c r="I47" s="2">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B48" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D48" s="2">
         <v>2009</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="H48" s="2">
-        <v>79</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>275</v>
+        <v>31</v>
+      </c>
+      <c r="I48" s="2">
+        <v>1</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B49" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>288</v>
+        <v>211</v>
       </c>
       <c r="D49" s="2">
         <v>2009</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H49" s="2">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B50" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="D50" s="2">
         <v>2009</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H50" s="2">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B51" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D51" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H51" s="2">
-        <v>78</v>
-      </c>
-      <c r="I51" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B52" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D52" s="2">
         <v>2008</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>150</v>
@@ -3935,132 +3936,138 @@
         <v>78</v>
       </c>
       <c r="I52" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B53" s="2">
+        <v>3</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2008</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H53" s="2">
+        <v>78</v>
+      </c>
+      <c r="I53" s="2">
         <v>2</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D53" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="H53" s="2">
-        <v>77</v>
-      </c>
-      <c r="I53" s="2">
-        <v>7</v>
-      </c>
       <c r="J53" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B54" s="2">
+        <v>2</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2007</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H54" s="2">
+        <v>77</v>
+      </c>
+      <c r="I54" s="2">
+        <v>7</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B55" s="2">
         <v>1</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D55" s="2">
         <v>2001</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G54" s="2" t="s">
+      <c r="F55" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H55" s="2">
         <v>2001</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I55" s="2">
         <v>1</v>
       </c>
-      <c r="J54" s="2" t="s">
+      <c r="J55" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="K54" s="2" t="s">
+      <c r="K55" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="B55" s="2">
-        <v>2</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="D55" s="2">
-        <v>2026</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>435</v>
       </c>
       <c r="B56" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D56" s="2">
         <v>2026</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>150</v>
@@ -4069,94 +4076,88 @@
         <v>431</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>359</v>
+        <v>435</v>
       </c>
       <c r="B57" s="2">
         <v>1</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B58" s="2">
+        <v>1</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D58" s="2">
         <v>2010</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="F58" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H58" s="2">
         <v>72</v>
       </c>
-      <c r="I57" s="2">
+      <c r="I58" s="2">
         <v>5</v>
       </c>
-      <c r="J57" s="2" t="s">
+      <c r="J58" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B58" s="2">
-        <v>3</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D58" s="2">
-        <v>2023</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H58" s="2">
-        <v>15</v>
-      </c>
-      <c r="I58" s="2">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>361</v>
       </c>
       <c r="B59" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D59" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>150</v>
@@ -4165,681 +4166,699 @@
         <v>158</v>
       </c>
       <c r="H59" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I59" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>361</v>
       </c>
       <c r="B60" s="2">
+        <v>2</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D60" s="2">
+        <v>2021</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H60" s="2">
+        <v>13</v>
+      </c>
+      <c r="I60" s="2">
+        <v>4</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B61" s="2">
         <v>1</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D61" s="2">
         <v>2010</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G60" s="2" t="s">
+      <c r="F61" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H61" s="2">
         <v>63</v>
       </c>
-      <c r="I60" s="2">
+      <c r="I61" s="2">
         <v>8</v>
       </c>
-      <c r="J60" s="2" t="s">
+      <c r="J61" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="K60" s="2" t="s">
+      <c r="K61" s="2" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B61" s="2">
-        <v>2</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D61" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>364</v>
       </c>
       <c r="B62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>367</v>
+        <v>207</v>
       </c>
       <c r="D62" s="2">
         <v>2007</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G62" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B63" s="2">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D63" s="2">
+        <v>2007</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="K63" s="2" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63" s="2">
+    <row r="64" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="2">
         <v>60</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B64" s="2">
+      <c r="F64" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="2">
         <v>59</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="2">
-        <v>58</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E65" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="2">
+        <v>58</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B66" s="2">
+      <c r="F66" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="2">
         <v>57</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B67" s="2">
+      <c r="F67" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="2">
         <v>56</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B68" s="2">
+      <c r="F68" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="2">
         <v>55</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B69" s="2">
-        <v>54</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="2">
+        <v>54</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" s="2">
+      <c r="F70" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="2">
         <v>53</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" s="2">
+      <c r="F71" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="2">
         <v>52</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" s="2">
-        <v>51</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E72" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="2">
+        <v>51</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B73" s="2">
+      <c r="F73" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="2">
         <v>50</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B74" s="2">
+      <c r="F74" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="2">
         <v>49</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="2">
+      <c r="F75" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="2">
         <v>48</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F75" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B76" s="2">
+      <c r="F76" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="2">
         <v>47</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C77" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B77" s="2">
+      <c r="F77" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="2">
         <v>46</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B78" s="2">
+      <c r="F78" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="2">
         <v>45</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B79" s="2">
+      <c r="F79" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="2">
         <v>44</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B80" s="2">
+      <c r="F80" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="2">
         <v>43</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B81" s="2">
+      <c r="F81" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="2">
         <v>42</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F81" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B82" s="2">
+      <c r="F82" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="2">
         <v>41</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B83" s="2">
+      <c r="F83" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="2">
         <v>40</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B84" s="2">
+      <c r="F84" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="2">
         <v>39</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F84" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B85" s="2">
+      <c r="F85" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="2">
         <v>38</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F85" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B86" s="2">
+      <c r="F86" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="2">
         <v>37</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F86" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B87" s="2">
+      <c r="F87" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="2">
         <v>36</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B88" s="2">
+      <c r="F88" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="2">
         <v>35</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B89" s="2">
+      <c r="F89" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="2">
         <v>34</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B90" s="2">
+      <c r="F90" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="2">
         <v>33</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B91" s="2">
+      <c r="F91" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="2">
         <v>32</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E92" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B92" s="2">
+      <c r="F92" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="2">
         <v>31</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E93" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F92" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B93" s="2">
+      <c r="F93" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="2">
         <v>30</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E94" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F93" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B94" s="2">
+      <c r="F94" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" s="2">
         <v>29</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E95" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B95" s="2">
+      <c r="F95" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="2">
         <v>28</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B96" s="2">
-        <v>27</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="F96" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -4847,544 +4866,562 @@
         <v>27</v>
       </c>
       <c r="C97" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="2">
+        <v>27</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B98" s="2">
+      <c r="F98" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="2">
         <v>26</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E99" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F98" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B99" s="2">
+      <c r="F99" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="2">
         <v>25</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F99" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B100" s="2">
+      <c r="F100" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="2">
         <v>24</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E101" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F100" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B101" s="2">
+      <c r="F101" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="2">
         <v>23</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F101" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B102" s="2">
+      <c r="F102" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="2">
         <v>22</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F102" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B103" s="2">
+      <c r="F103" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="2">
         <v>21</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E104" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F103" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B104" s="2">
+      <c r="F104" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="2">
         <v>20</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F104" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B105" s="2">
+      <c r="F105" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="2">
         <v>19</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F105" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B106" s="2">
+      <c r="F106" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="2">
         <v>18</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B107" s="2">
+      <c r="F107" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="2">
         <v>17</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E108" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F107" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B108" s="2">
+      <c r="F108" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="2">
         <v>16</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F108" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B109" s="2">
+      <c r="F109" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B110" s="2">
         <v>15</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F109" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B110" s="2">
+      <c r="F110" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B111" s="2">
         <v>14</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="E111" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F110" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B111" s="2">
+      <c r="F111" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B112" s="2">
         <v>13</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E112" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F111" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B112" s="2">
+      <c r="F112" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" s="2">
         <v>12</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B113" s="2">
-        <v>11</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B114" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E114" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" s="2">
+        <v>10</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F114" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B115" s="2">
+      <c r="F115" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" s="2">
         <v>9</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F115" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B116" s="2">
+      <c r="F116" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B117" s="2">
         <v>8</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F116" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B117" s="2">
+      <c r="F117" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" s="2">
         <v>7</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C118" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F117" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B118" s="2">
+      <c r="F118" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B119" s="2">
         <v>6</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F118" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B119" s="2">
+      <c r="F119" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B120" s="2">
         <v>5</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C120" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F119" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B120" s="2">
+      <c r="F120" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B121" s="2">
         <v>4</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="E121" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F120" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B121" s="2">
-        <v>3</v>
-      </c>
-      <c r="C121" s="1" t="s">
+      <c r="F121" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B122" s="2">
+        <v>3</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="E122" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F121" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B122" s="2">
+      <c r="F122" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B123" s="2">
         <v>2</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C123" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="E123" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F122" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="20" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B123" s="2">
-        <v>1</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="F123" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="B124" s="2">
         <v>1</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B125" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B126" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B127" s="2">
+        <v>2</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A128" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B128" s="2">
         <v>1</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C128" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F127" s="2" t="s">
+      <c r="F128" s="2" t="s">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <hyperlinks>
-    <hyperlink ref="L24" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="L44" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="K47" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="L48" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="K16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="O11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="M9" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
-    <hyperlink ref="Q11" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
-    <hyperlink ref="R9" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
-    <hyperlink ref="L5" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
-    <hyperlink ref="M12" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
-    <hyperlink ref="L7" r:id="rId12" xr:uid="{28D0DE1C-48A6-42F2-8E88-DAC27E2438A1}"/>
-    <hyperlink ref="Q18" r:id="rId13" xr:uid="{9EC32125-7A81-4C54-87CC-8B89C467AC0B}"/>
+    <hyperlink ref="L25" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L45" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K48" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="L49" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O12" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M10" r:id="rId7" xr:uid="{E1B66905-DADF-47A4-8243-F40016C7E8FB}"/>
+    <hyperlink ref="Q12" r:id="rId8" xr:uid="{4C08C193-4413-4403-AC10-DF11BF421AE0}"/>
+    <hyperlink ref="R10" r:id="rId9" xr:uid="{12CE3AE1-E6F3-4E8E-8531-D2F2438AE636}"/>
+    <hyperlink ref="L6" r:id="rId10" xr:uid="{06B5CEDF-ED6D-47FC-912C-78024FF343B5}"/>
+    <hyperlink ref="M13" r:id="rId11" xr:uid="{0C48A38D-AE4D-4273-899B-C696D0DF23B8}"/>
+    <hyperlink ref="L8" r:id="rId12" xr:uid="{28D0DE1C-48A6-42F2-8E88-DAC27E2438A1}"/>
+    <hyperlink ref="Q19" r:id="rId13" xr:uid="{9EC32125-7A81-4C54-87CC-8B89C467AC0B}"/>
+    <hyperlink ref="L2" r:id="rId14" xr:uid="{F2E8DC75-DE18-42C5-AAF3-2ECAE78BEDC8}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId15"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE174CA-56E4-4192-9492-E63020F965BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -1905,32 +1905,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T128"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="95" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="204.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.5703125" style="1"/>
+    <col min="8" max="8" width="4.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="204.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>369</v>
       </c>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>369</v>
       </c>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>369</v>
       </c>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>369</v>
       </c>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>369</v>
       </c>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>369</v>
       </c>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>174</v>
       </c>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="20" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>174</v>
       </c>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="45" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="40" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="25" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>174</v>
       </c>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="T15" s="2"/>
     </row>
-    <row r="16" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>174</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>174</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>174</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>174</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>174</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>174</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" ht="50" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>174</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>174</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>174</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>174</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>174</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>174</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>174</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>174</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>174</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>174</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>174</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>174</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>174</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>174</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>174</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>174</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>174</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>174</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>174</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>174</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>174</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>174</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>174</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>174</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>174</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>174</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>174</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>174</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>174</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>174</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>435</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>435</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>359</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>361</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>361</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>361</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>364</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>364</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>3</v>
       </c>
@@ -5147,7 +5147,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>3</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>3</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>3</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>3</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>3</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>3</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>3</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>3</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>104</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>97</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>97</v>
       </c>
@@ -5385,7 +5385,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>97</v>
       </c>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE174CA-56E4-4192-9492-E63020F965BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2E7340-1B2B-4517-ABC2-EFE283E62926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -1358,9 +1358,6 @@
     <t>2026+</t>
   </si>
   <si>
-    <t>Uncertainty intervals for covariate adjusted marginal treatment effects in randomized clinical trials with time-to-event endpoint</t>
-  </si>
-  <si>
     <t>Götte, H., **Rufibach, K.**</t>
   </si>
   <si>
@@ -1376,9 +1373,6 @@
     <t>quarto</t>
   </si>
   <si>
-    <t>Statistical Methodology Groups in the Pharmaceutical Industry</t>
-  </si>
-  <si>
     <t>Devenport, J., Mielke, T., Akacha, M., **Rufibach, K.**, Ocampo, A., Lanius, V., Vandemeulebroecke, M., Hougaard, P., Colin, P., Wright, D., Hummel, Jürgen, Kunz, C.U., Krams, M.</t>
   </si>
   <si>
@@ -1446,6 +1440,12 @@
   </si>
   <si>
     <t>https://osf.io/2kebj/files/a7qgy</t>
+  </si>
+  <si>
+    <t>Statistical Methodology Groups in the Pharmaceutical Industry (discussion paper)</t>
+  </si>
+  <si>
+    <t>Is it worth investing into borrowing external control data when complimentary covariates already provide precision gains for randomized trials?</t>
   </si>
 </sst>
 </file>
@@ -1905,32 +1905,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T128"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="10" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="95" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="204.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.54296875" style="1"/>
+    <col min="8" max="8" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="204.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>374</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>162</v>
@@ -1992,7 +1992,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>369</v>
       </c>
@@ -2000,13 +2000,13 @@
         <v>54</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>439</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -2015,11 +2015,11 @@
         <v>171</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>369</v>
       </c>
@@ -2027,13 +2027,13 @@
         <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>439</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>149</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>369</v>
       </c>
@@ -2051,13 +2051,13 @@
         <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>439</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>149</v>
@@ -2066,17 +2066,17 @@
         <v>171</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q4" t="s">
         <v>452</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>454</v>
-      </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>369</v>
       </c>
@@ -2084,13 +2084,13 @@
         <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>439</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>440</v>
+        <v>469</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>149</v>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>369</v>
       </c>
@@ -2126,11 +2126,11 @@
         <v>428</v>
       </c>
       <c r="Q6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>369</v>
       </c>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>174</v>
       </c>
@@ -2162,13 +2162,13 @@
         <v>48</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>439</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>150</v>
@@ -2183,23 +2183,23 @@
         <v>2</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="R8" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>174</v>
       </c>
@@ -2228,10 +2228,10 @@
         <v>2</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>407</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="40" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="45" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>44</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>420</v>
@@ -2324,11 +2324,11 @@
         <v>395</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:20" ht="25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>174</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>413</v>
@@ -2426,7 +2426,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>174</v>
       </c>
@@ -2464,11 +2464,11 @@
         <v>379</v>
       </c>
       <c r="Q14" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="T15" s="2"/>
     </row>
-    <row r="16" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>174</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
@@ -2592,10 +2592,10 @@
         <v>181</v>
       </c>
       <c r="Q17" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>174</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>174</v>
       </c>
@@ -2686,10 +2686,10 @@
         <v>183</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>174</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>174</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>174</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>174</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
@@ -2876,13 +2876,13 @@
         <v>385</v>
       </c>
       <c r="Q24" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="R24" s="2" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="50" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>174</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>174</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>174</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>174</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>174</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>174</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>174</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>174</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>174</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>174</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>174</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>174</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>174</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>174</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>174</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>174</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>174</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>174</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>174</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>174</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>174</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>174</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>174</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>174</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>174</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>174</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>174</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>174</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>174</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>174</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>435</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>435</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>359</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>361</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>361</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>361</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>364</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>364</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>3</v>
       </c>
@@ -5147,7 +5147,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>3</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>3</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>3</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>3</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>3</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>3</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>3</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>3</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>104</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>97</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>97</v>
       </c>
@@ -5385,7 +5385,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>97</v>
       </c>
